--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{886BE765-35F0-42A0-8B63-8D2ADAE84808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0108D6FF-577A-4BE9-9D3A-77869DCE9F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="513">
   <si>
     <t>Option 1</t>
   </si>
@@ -384,9 +384,6 @@
   </si>
   <si>
     <t>(E) : $a&gt;0$ et $b=0$</t>
-  </si>
-  <si>
-    <t>MEDECINE 2020</t>
   </si>
   <si>
     <t>CHIMIE</t>
@@ -1658,6 +1655,9 @@
   </si>
   <si>
     <t>Numéro de concours</t>
+  </si>
+  <si>
+    <t>Concours Blanc 1</t>
   </si>
 </sst>
 </file>
@@ -1722,7 +1722,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1747,9 +1747,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2086,8 +2083,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>512</v>
+      <c r="A1" s="12" t="s">
+        <v>511</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>14</v>
@@ -2127,754 +2124,794 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>331</v>
+      <c r="C2" s="11" t="s">
+        <v>330</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>235</v>
+      <c r="J2" s="11" t="s">
+        <v>234</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="5"/>
+      <c r="L2" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M2" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>332</v>
+      <c r="C3" s="11" t="s">
+        <v>331</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="I3" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="I3" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>238</v>
+      <c r="J3" s="11" t="s">
+        <v>237</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="5"/>
+      <c r="L3" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M3" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="13">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>333</v>
+      <c r="C4" s="11" t="s">
+        <v>332</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>242</v>
+      <c r="J4" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="5"/>
+      <c r="L4" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M4" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="13">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>334</v>
+      <c r="C5" s="11" t="s">
+        <v>333</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="I5" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="I5" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>246</v>
+      <c r="J5" s="11" t="s">
+        <v>245</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="5"/>
+      <c r="L5" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M5" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="13">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>335</v>
+      <c r="C6" s="11" t="s">
+        <v>334</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="I6" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>255</v>
+      <c r="J6" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M6" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="13">
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>336</v>
+      <c r="C7" s="11" t="s">
+        <v>335</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="I7" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>258</v>
+      <c r="J7" s="11" t="s">
+        <v>257</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="5"/>
+      <c r="L7" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="120" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="13">
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>337</v>
+      <c r="C8" s="11" t="s">
+        <v>336</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="I8" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="I8" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>265</v>
+      <c r="J8" s="11" t="s">
+        <v>264</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="5"/>
+      <c r="L8" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M8" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="13">
         <v>1</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>338</v>
+      <c r="C9" s="11" t="s">
+        <v>337</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="G9" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="I9" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>270</v>
+      <c r="J9" s="11" t="s">
+        <v>269</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="5"/>
+      <c r="L9" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M9" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="13">
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>339</v>
+      <c r="C10" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="G10" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="I10" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>271</v>
+      <c r="J10" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L10" s="5"/>
+      <c r="L10" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M10" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="13">
         <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>340</v>
+      <c r="C11" s="11" t="s">
+        <v>339</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="I11" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="I11" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>280</v>
+      <c r="J11" s="11" t="s">
+        <v>279</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L11" s="5"/>
+      <c r="L11" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M11" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="345" x14ac:dyDescent="0.25">
-      <c r="A12" s="14">
+      <c r="A12" s="13">
         <v>1</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>464</v>
+      <c r="C12" s="11" t="s">
+        <v>463</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="G12" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="I12" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>283</v>
+      <c r="J12" s="11" t="s">
+        <v>282</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="5"/>
+      <c r="L12" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M12" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="90" x14ac:dyDescent="0.25">
-      <c r="A13" s="14">
+      <c r="A13" s="13">
         <v>1</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>458</v>
+      <c r="C13" s="11" t="s">
+        <v>457</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="G13" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="H13" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="I13" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>289</v>
+      <c r="J13" s="11" t="s">
+        <v>288</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="5"/>
+      <c r="L13" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M13" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
+      <c r="A14" s="13">
         <v>1</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>459</v>
+      <c r="C14" s="11" t="s">
+        <v>458</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="I14" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>291</v>
+      <c r="J14" s="11" t="s">
+        <v>290</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L14" s="5"/>
+      <c r="L14" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M14" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="14">
+      <c r="A15" s="13">
         <v>1</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>341</v>
+      <c r="C15" s="11" t="s">
+        <v>340</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="G15" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="I15" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="I15" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>299</v>
+      <c r="J15" s="11" t="s">
+        <v>298</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L15" s="5"/>
+      <c r="L15" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M15" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A16" s="14">
+      <c r="A16" s="13">
         <v>1</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>460</v>
+      <c r="C16" s="11" t="s">
+        <v>459</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="G16" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="I16" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="I16" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>301</v>
+      <c r="J16" s="11" t="s">
+        <v>300</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L16" s="5"/>
+      <c r="L16" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M16" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
+      <c r="A17" s="13">
         <v>1</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>342</v>
+      <c r="C17" s="11" t="s">
+        <v>341</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="G17" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="I17" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="I17" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>310</v>
+      <c r="J17" s="11" t="s">
+        <v>309</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L17" s="5"/>
+      <c r="L17" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M17" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="135" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
+      <c r="A18" s="13">
         <v>1</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>461</v>
+      <c r="C18" s="11" t="s">
+        <v>460</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="G18" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="H18" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="I18" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="I18" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>313</v>
+      <c r="J18" s="11" t="s">
+        <v>312</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="5"/>
+      <c r="L18" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M18" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="120" x14ac:dyDescent="0.25">
-      <c r="A19" s="14">
+      <c r="A19" s="13">
         <v>1</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>462</v>
+      <c r="C19" s="11" t="s">
+        <v>461</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="G19" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="H19" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="I19" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="I19" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>316</v>
+      <c r="J19" s="11" t="s">
+        <v>315</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L19" s="5"/>
+      <c r="L19" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M19" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="180" x14ac:dyDescent="0.25">
-      <c r="A20" s="14">
+      <c r="A20" s="13">
         <v>1</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>457</v>
+      <c r="C20" s="11" t="s">
+        <v>456</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="G20" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="H20" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="I20" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="I20" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>321</v>
+      <c r="J20" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="5"/>
+      <c r="L20" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M20" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A21" s="14">
+      <c r="A21" s="13">
         <v>1</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>463</v>
+      <c r="C21" s="11" t="s">
+        <v>462</v>
       </c>
       <c r="D21" s="2"/>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="G21" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="H21" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="I21" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="I21" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>330</v>
+      <c r="J21" s="11" t="s">
+        <v>329</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L21" s="5"/>
+      <c r="L21" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M21" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="165" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+      <c r="A22" s="13">
         <v>1</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="2"/>
@@ -2886,123 +2923,131 @@
       <c r="K22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L22" s="5"/>
+      <c r="L22" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="14">
+      <c r="A23" s="13">
         <v>1</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
+      <c r="L23" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M23" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="14">
+      <c r="A24" s="13">
         <v>1</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
+      <c r="L24" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M24" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="14">
+      <c r="A25" s="13">
         <v>1</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
+      <c r="L25" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M25" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A26" s="14">
+      <c r="A26" s="13">
         <v>1</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -3015,89 +3060,93 @@
         <v>9</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M26" s="5"/>
     </row>
     <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="14">
+      <c r="A27" s="13">
         <v>1</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
+      <c r="L27" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M27" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="14">
+      <c r="A28" s="13">
         <v>1</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M28" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="210" x14ac:dyDescent="0.25">
-      <c r="A29" s="14">
+      <c r="A29" s="13">
         <v>1</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -3110,124 +3159,130 @@
         <v>9</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M29" s="5"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="14">
+      <c r="A30" s="13">
         <v>1</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M30" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="14">
+      <c r="A31" s="13">
         <v>1</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="I31" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M31" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="135" x14ac:dyDescent="0.25">
-      <c r="A32" s="14">
+      <c r="A32" s="13">
         <v>1</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="J32" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
+      <c r="L32" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M32" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="165" x14ac:dyDescent="0.25">
-      <c r="A33" s="14">
+      <c r="A33" s="13">
         <v>1</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -3240,89 +3295,93 @@
         <v>9</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M33" s="5"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="14">
+      <c r="A34" s="13">
         <v>1</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="H34" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="I34" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="J34" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M34" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="14">
+      <c r="A35" s="13">
         <v>1</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="J35" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M35" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="240" x14ac:dyDescent="0.25">
-      <c r="A36" s="14">
+      <c r="A36" s="13">
         <v>1</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -3335,89 +3394,93 @@
         <v>9</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M36" s="5"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="14">
+      <c r="A37" s="13">
         <v>1</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="I37" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="J37" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
+      <c r="L37" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M37" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="14">
+      <c r="A38" s="13">
         <v>1</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="H38" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="I38" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="J38" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
+      <c r="L38" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M38" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="135" x14ac:dyDescent="0.25">
-      <c r="A39" s="14">
+      <c r="A39" s="13">
         <v>1</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -3430,124 +3493,128 @@
         <v>9</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M39" s="5"/>
     </row>
     <row r="40" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="14">
+      <c r="A40" s="13">
         <v>1</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="I40" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
+      <c r="L40" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M40" s="5"/>
     </row>
     <row r="41" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="14">
+      <c r="A41" s="13">
         <v>1</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="I41" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
+      <c r="L41" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M41" s="5"/>
     </row>
     <row r="42" spans="1:13" ht="135" x14ac:dyDescent="0.25">
-      <c r="A42" s="14">
+      <c r="A42" s="13">
         <v>1</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="H42" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>487</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M42" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="135" x14ac:dyDescent="0.25">
-      <c r="A43" s="14">
+      <c r="A43" s="13">
         <v>1</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -3560,124 +3627,130 @@
         <v>9</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M43" s="5"/>
     </row>
     <row r="44" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="14">
+      <c r="A44" s="13">
         <v>1</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="I44" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="J44" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
+      <c r="L44" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M44" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="14">
+      <c r="A45" s="13">
         <v>1</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="I45" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="J45" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
+      <c r="L45" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M45" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="14">
+      <c r="A46" s="13">
         <v>1</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="G46" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="I46" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="I46" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="J46" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
+      <c r="L46" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M46" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A47" s="14">
+      <c r="A47" s="13">
         <v>1</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -3690,89 +3763,93 @@
         <v>9</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M47" s="5"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="14">
+      <c r="A48" s="13">
         <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="G48" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="H48" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="I48" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="J48" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
+      <c r="L48" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M48" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="14">
+      <c r="A49" s="13">
         <v>1</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="G49" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="H49" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
+      <c r="L49" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M49" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="270" x14ac:dyDescent="0.25">
-      <c r="A50" s="14">
+      <c r="A50" s="13">
         <v>1</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>503</v>
+      <c r="C50" s="11" t="s">
+        <v>502</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -3782,127 +3859,133 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M50" s="5"/>
     </row>
     <row r="51" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="14">
+      <c r="A51" s="13">
         <v>1</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>437</v>
+      <c r="C51" s="11" t="s">
+        <v>436</v>
       </c>
       <c r="D51" s="2"/>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="F51" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="G51" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="H51" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="H51" s="12" t="s">
+      <c r="I51" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="I51" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>343</v>
+      <c r="J51" s="11" t="s">
+        <v>342</v>
       </c>
       <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
+      <c r="L51" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M51" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="14">
+      <c r="A52" s="13">
         <v>1</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>438</v>
+      <c r="C52" s="11" t="s">
+        <v>437</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="F52" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="G52" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="H52" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="I52" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="I52" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="J52" s="12" t="s">
-        <v>349</v>
+      <c r="J52" s="11" t="s">
+        <v>348</v>
       </c>
       <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
+      <c r="L52" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M52" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="14">
+      <c r="A53" s="13">
         <v>1</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>439</v>
+      <c r="C53" s="11" t="s">
+        <v>438</v>
       </c>
       <c r="D53" s="2"/>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="F53" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="G53" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="G53" s="12" t="s">
+      <c r="H53" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="H53" s="12" t="s">
+      <c r="I53" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="I53" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>357</v>
+      <c r="J53" s="11" t="s">
+        <v>356</v>
       </c>
       <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
+      <c r="L53" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M53" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="405" x14ac:dyDescent="0.25">
-      <c r="A54" s="14">
+      <c r="A54" s="13">
         <v>1</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>497</v>
+      <c r="C54" s="11" t="s">
+        <v>496</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -3912,162 +3995,170 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L54" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M54" s="5"/>
     </row>
     <row r="55" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A55" s="14">
+      <c r="A55" s="13">
         <v>1</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>440</v>
+      <c r="C55" s="11" t="s">
+        <v>439</v>
       </c>
       <c r="D55" s="2"/>
-      <c r="E55" s="12" t="s">
+      <c r="E55" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="F55" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="F55" s="12" t="s">
+      <c r="G55" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="G55" s="12" t="s">
+      <c r="H55" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="H55" s="12" t="s">
+      <c r="I55" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="I55" s="12" t="s">
-        <v>502</v>
-      </c>
-      <c r="J55" s="12" t="s">
-        <v>499</v>
+      <c r="J55" s="11" t="s">
+        <v>498</v>
       </c>
       <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
+      <c r="L55" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M55" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A56" s="14">
+      <c r="A56" s="13">
         <v>1</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>442</v>
+      <c r="C56" s="11" t="s">
+        <v>441</v>
       </c>
       <c r="D56" s="2"/>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="F56" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="F56" s="12" t="s">
+      <c r="G56" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="H56" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="H56" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="J56" s="12" t="s">
-        <v>359</v>
+      <c r="I56" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>358</v>
       </c>
       <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
+      <c r="L56" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M56" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A57" s="14">
+      <c r="A57" s="13">
         <v>1</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>443</v>
+      <c r="C57" s="11" t="s">
+        <v>442</v>
       </c>
       <c r="D57" s="2"/>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="F57" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="F57" s="12" t="s">
+      <c r="G57" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="H57" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="H57" s="12" t="s">
+      <c r="I57" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="I57" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>366</v>
+      <c r="J57" s="11" t="s">
+        <v>365</v>
       </c>
       <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
+      <c r="L57" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M57" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="14">
+      <c r="A58" s="13">
         <v>1</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>441</v>
+      <c r="C58" s="11" t="s">
+        <v>440</v>
       </c>
       <c r="D58" s="2"/>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="F58" s="12" t="s">
+      <c r="G58" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="H58" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="H58" s="12" t="s">
+      <c r="I58" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="I58" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="J58" s="12" t="s">
-        <v>369</v>
+      <c r="J58" s="11" t="s">
+        <v>368</v>
       </c>
       <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
+      <c r="L58" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M58" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="165" x14ac:dyDescent="0.25">
-      <c r="A59" s="14">
+      <c r="A59" s="13">
         <v>1</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>496</v>
+      <c r="C59" s="11" t="s">
+        <v>495</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
@@ -4077,166 +4168,172 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L59" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M59" s="5"/>
     </row>
     <row r="60" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="14">
+      <c r="A60" s="13">
         <v>1</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>444</v>
+      <c r="C60" s="11" t="s">
+        <v>443</v>
       </c>
       <c r="D60" s="2"/>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="G60" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="G60" s="12" t="s">
+      <c r="H60" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="H60" s="12" t="s">
+      <c r="I60" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="I60" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="J60" s="12" t="s">
-        <v>373</v>
+      <c r="J60" s="11" t="s">
+        <v>372</v>
       </c>
       <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
+      <c r="L60" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M60" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="14">
+      <c r="A61" s="13">
         <v>1</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>445</v>
+      <c r="C61" s="11" t="s">
+        <v>444</v>
       </c>
       <c r="D61" s="2"/>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="F61" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="G61" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="H61" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="H61" s="12" t="s">
+      <c r="I61" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="I61" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="J61" s="12" t="s">
-        <v>378</v>
+      <c r="J61" s="11" t="s">
+        <v>377</v>
       </c>
       <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
+      <c r="L61" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M61" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="14">
+      <c r="A62" s="13">
         <v>1</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="12" t="s">
-        <v>446</v>
+      <c r="C62" s="11" t="s">
+        <v>445</v>
       </c>
       <c r="D62" s="2"/>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="F62" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="G62" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="H62" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="I62" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="I62" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="J62" s="12" t="s">
-        <v>382</v>
+      <c r="J62" s="11" t="s">
+        <v>381</v>
       </c>
       <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
+      <c r="L62" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M62" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="165" x14ac:dyDescent="0.25">
-      <c r="A63" s="14">
+      <c r="A63" s="13">
         <v>1</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>495</v>
+      <c r="C63" s="11" t="s">
+        <v>494</v>
       </c>
       <c r="D63" s="2"/>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="F63" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="F63" s="12" t="s">
+      <c r="G63" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="G63" s="12" t="s">
+      <c r="H63" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="H63" s="12" t="s">
+      <c r="I63" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="I63" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>390</v>
+      <c r="J63" s="11" t="s">
+        <v>389</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L63" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M63" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="255" x14ac:dyDescent="0.25">
-      <c r="A64" s="14">
+      <c r="A64" s="13">
         <v>1</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C64" s="12" t="s">
-        <v>494</v>
+      <c r="C64" s="11" t="s">
+        <v>493</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
@@ -4246,92 +4343,96 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L64" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M64" s="5"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="14">
+      <c r="A65" s="13">
         <v>1</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C65" s="12" t="s">
-        <v>447</v>
+      <c r="C65" s="11" t="s">
+        <v>446</v>
       </c>
       <c r="D65" s="2"/>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="F65" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="F65" s="12" t="s">
+      <c r="G65" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="G65" s="12" t="s">
+      <c r="H65" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="H65" s="12" t="s">
+      <c r="I65" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="I65" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="J65" s="12" t="s">
-        <v>393</v>
+      <c r="J65" s="11" t="s">
+        <v>392</v>
       </c>
       <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
+      <c r="L65" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M65" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="14">
+      <c r="A66" s="13">
         <v>1</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>448</v>
+      <c r="C66" s="11" t="s">
+        <v>447</v>
       </c>
       <c r="D66" s="2"/>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="F66" s="12" t="s">
+      <c r="G66" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="G66" s="12" t="s">
+      <c r="H66" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="H66" s="12" t="s">
+      <c r="I66" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="I66" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="J66" s="12" t="s">
-        <v>401</v>
+      <c r="J66" s="11" t="s">
+        <v>400</v>
       </c>
       <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
+      <c r="L66" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M66" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A67" s="14">
+      <c r="A67" s="13">
         <v>1</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>493</v>
+      <c r="C67" s="11" t="s">
+        <v>492</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
@@ -4341,127 +4442,133 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L67" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M67" s="5"/>
     </row>
     <row r="68" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="14">
+      <c r="A68" s="13">
         <v>1</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>449</v>
+      <c r="C68" s="11" t="s">
+        <v>448</v>
       </c>
       <c r="D68" s="2"/>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="F68" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="F68" s="12" t="s">
+      <c r="G68" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="G68" s="12" t="s">
+      <c r="H68" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="H68" s="12" t="s">
+      <c r="I68" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="I68" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="J68" s="12" t="s">
-        <v>402</v>
+      <c r="J68" s="11" t="s">
+        <v>401</v>
       </c>
       <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
+      <c r="L68" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M68" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A69" s="14">
+      <c r="A69" s="13">
         <v>1</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C69" s="12" t="s">
-        <v>450</v>
+      <c r="C69" s="11" t="s">
+        <v>449</v>
       </c>
       <c r="D69" s="2"/>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="F69" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="G69" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="G69" s="12" t="s">
+      <c r="H69" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="H69" s="12" t="s">
+      <c r="I69" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="I69" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="J69" s="12" t="s">
-        <v>409</v>
+      <c r="J69" s="11" t="s">
+        <v>408</v>
       </c>
       <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
+      <c r="L69" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M69" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="14">
+      <c r="A70" s="13">
         <v>1</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="12" t="s">
-        <v>451</v>
+      <c r="C70" s="11" t="s">
+        <v>450</v>
       </c>
       <c r="D70" s="2"/>
-      <c r="E70" s="12" t="s">
+      <c r="E70" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="G70" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="G70" s="12" t="s">
+      <c r="H70" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="H70" s="12" t="s">
+      <c r="I70" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="I70" s="12" t="s">
-        <v>416</v>
-      </c>
-      <c r="J70" s="12" t="s">
-        <v>413</v>
+      <c r="J70" s="11" t="s">
+        <v>412</v>
       </c>
       <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
+      <c r="L70" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M70" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A71" s="14">
+      <c r="A71" s="13">
         <v>1</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C71" s="12" t="s">
-        <v>504</v>
+      <c r="C71" s="11" t="s">
+        <v>503</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
@@ -4471,92 +4578,96 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L71" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M71" s="5"/>
     </row>
     <row r="72" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="14">
+      <c r="A72" s="13">
         <v>1</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>452</v>
+      <c r="C72" s="11" t="s">
+        <v>451</v>
       </c>
       <c r="D72" s="2"/>
-      <c r="E72" s="12" t="s">
+      <c r="E72" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="F72" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="F72" s="12" t="s">
+      <c r="G72" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="G72" s="12" t="s">
+      <c r="H72" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="H72" s="12" t="s">
+      <c r="I72" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="I72" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="J72" s="12" t="s">
-        <v>420</v>
+      <c r="J72" s="11" t="s">
+        <v>419</v>
       </c>
       <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
+      <c r="L72" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M72" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A73" s="14">
+      <c r="A73" s="13">
         <v>1</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C73" s="12" t="s">
-        <v>453</v>
+      <c r="C73" s="11" t="s">
+        <v>452</v>
       </c>
       <c r="D73" s="2"/>
-      <c r="E73" s="12" t="s">
+      <c r="E73" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="F73" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="G73" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="G73" s="12" t="s">
+      <c r="H73" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="H73" s="12" t="s">
+      <c r="I73" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="I73" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="J73" s="12" t="s">
-        <v>426</v>
+      <c r="J73" s="11" t="s">
+        <v>425</v>
       </c>
       <c r="K73" s="5"/>
-      <c r="L73" s="5"/>
+      <c r="L73" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M73" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="135" x14ac:dyDescent="0.25">
-      <c r="A74" s="14">
+      <c r="A74" s="13">
         <v>1</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C74" s="12" t="s">
-        <v>492</v>
+      <c r="C74" s="11" t="s">
+        <v>491</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
@@ -4566,92 +4677,96 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L74" s="5" t="s">
-        <v>116</v>
+        <v>512</v>
       </c>
       <c r="M74" s="5"/>
     </row>
     <row r="75" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A75" s="14">
+      <c r="A75" s="13">
         <v>1</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>454</v>
+      <c r="C75" s="11" t="s">
+        <v>453</v>
       </c>
       <c r="D75" s="2"/>
-      <c r="E75" s="12" t="s">
+      <c r="E75" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="F75" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="F75" s="12" t="s">
+      <c r="G75" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="G75" s="12" t="s">
+      <c r="H75" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="H75" s="12" t="s">
+      <c r="I75" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="I75" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="J75" s="12" t="s">
-        <v>427</v>
+      <c r="J75" s="11" t="s">
+        <v>426</v>
       </c>
       <c r="K75" s="5"/>
-      <c r="L75" s="5"/>
+      <c r="L75" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M75" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="14">
+      <c r="A76" s="13">
         <v>1</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C76" s="12" t="s">
-        <v>455</v>
+      <c r="C76" s="11" t="s">
+        <v>454</v>
       </c>
       <c r="D76" s="2"/>
-      <c r="E76" s="12" t="s">
+      <c r="E76" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="F76" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="F76" s="12" t="s">
+      <c r="G76" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="G76" s="12" t="s">
+      <c r="H76" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="H76" s="12" t="s">
+      <c r="I76" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="I76" s="12" t="s">
-        <v>436</v>
-      </c>
-      <c r="J76" s="12" t="s">
-        <v>435</v>
+      <c r="J76" s="11" t="s">
+        <v>434</v>
       </c>
       <c r="K76" s="5"/>
-      <c r="L76" s="5"/>
+      <c r="L76" s="5" t="s">
+        <v>512</v>
+      </c>
       <c r="M76" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A77" s="14">
+      <c r="A77" s="13">
         <v>1</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="3" t="s">
@@ -4672,25 +4787,25 @@
       <c r="J77" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="K77" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L77" s="10" t="s">
-        <v>116</v>
+      <c r="L77" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M77" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A78" s="14">
+      <c r="A78" s="13">
         <v>1</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="3" t="s">
@@ -4711,25 +4826,25 @@
       <c r="J78" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K78" s="11" t="s">
+      <c r="K78" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L78" s="10" t="s">
-        <v>116</v>
+      <c r="L78" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M78" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A79" s="14">
+      <c r="A79" s="13">
         <v>1</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="3" t="s">
@@ -4750,25 +4865,25 @@
       <c r="J79" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="K79" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L79" s="10" t="s">
-        <v>116</v>
+      <c r="L79" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M79" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A80" s="14">
+      <c r="A80" s="13">
         <v>1</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="3" t="s">
@@ -4789,25 +4904,25 @@
       <c r="J80" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K80" s="11" t="s">
+      <c r="K80" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L80" s="10" t="s">
-        <v>116</v>
+      <c r="L80" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M80" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A81" s="14">
+      <c r="A81" s="13">
         <v>1</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="3" t="s">
@@ -4828,25 +4943,25 @@
       <c r="J81" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="K81" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L81" s="10" t="s">
-        <v>116</v>
+      <c r="L81" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M81" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A82" s="14">
+      <c r="A82" s="13">
         <v>1</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="3" t="s">
@@ -4867,25 +4982,25 @@
       <c r="J82" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="K82" s="11" t="s">
+      <c r="K82" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L82" s="10" t="s">
-        <v>116</v>
+      <c r="L82" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M82" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="14">
+      <c r="A83" s="13">
         <v>1</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="3" t="s">
@@ -4906,25 +5021,25 @@
       <c r="J83" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="K83" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L83" s="10" t="s">
-        <v>116</v>
+      <c r="L83" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M83" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="14">
+      <c r="A84" s="13">
         <v>1</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="3" t="s">
@@ -4945,25 +5060,25 @@
       <c r="J84" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="K84" s="11" t="s">
+      <c r="K84" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L84" s="10" t="s">
-        <v>116</v>
+      <c r="L84" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M84" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A85" s="14">
+      <c r="A85" s="13">
         <v>1</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="3" t="s">
@@ -4984,25 +5099,25 @@
       <c r="J85" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="K85" s="11" t="s">
+      <c r="K85" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L85" s="10" t="s">
-        <v>116</v>
+      <c r="L85" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M85" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="14">
+      <c r="A86" s="13">
         <v>1</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="3" t="s">
@@ -5023,25 +5138,25 @@
       <c r="J86" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K86" s="11" t="s">
+      <c r="K86" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L86" s="10" t="s">
-        <v>116</v>
+      <c r="L86" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M86" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A87" s="14">
+      <c r="A87" s="13">
         <v>1</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="3" t="s">
@@ -5062,25 +5177,25 @@
       <c r="J87" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="K87" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L87" s="10" t="s">
-        <v>116</v>
+      <c r="L87" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M87" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="14">
+      <c r="A88" s="13">
         <v>1</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="3" t="s">
@@ -5101,25 +5216,25 @@
       <c r="J88" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="K88" s="11" t="s">
+      <c r="K88" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L88" s="10" t="s">
-        <v>116</v>
+      <c r="L88" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M88" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A89" s="14">
+      <c r="A89" s="13">
         <v>1</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="3" t="s">
@@ -5140,25 +5255,25 @@
       <c r="J89" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K89" s="11" t="s">
+      <c r="K89" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L89" s="10" t="s">
-        <v>116</v>
+      <c r="L89" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M89" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A90" s="14">
+      <c r="A90" s="13">
         <v>1</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="3" t="s">
@@ -5179,25 +5294,25 @@
       <c r="J90" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K90" s="11" t="s">
+      <c r="K90" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L90" s="10" t="s">
-        <v>116</v>
+      <c r="L90" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M90" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A91" s="14">
+      <c r="A91" s="13">
         <v>1</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="3" t="s">
@@ -5218,25 +5333,25 @@
       <c r="J91" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="K91" s="11" t="s">
+      <c r="K91" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="10" t="s">
-        <v>116</v>
+      <c r="L91" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M91" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A92" s="14">
+      <c r="A92" s="13">
         <v>1</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="3" t="s">
@@ -5257,25 +5372,25 @@
       <c r="J92" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="K92" s="11" t="s">
+      <c r="K92" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L92" s="10" t="s">
-        <v>116</v>
+      <c r="L92" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M92" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A93" s="14">
+      <c r="A93" s="13">
         <v>1</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="3" t="s">
@@ -5296,25 +5411,25 @@
       <c r="J93" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="K93" s="11" t="s">
+      <c r="K93" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L93" s="10" t="s">
-        <v>116</v>
+      <c r="L93" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M93" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A94" s="14">
+      <c r="A94" s="13">
         <v>1</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="3" t="s">
@@ -5335,25 +5450,25 @@
       <c r="J94" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K94" s="11" t="s">
+      <c r="K94" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L94" s="10" t="s">
-        <v>116</v>
+      <c r="L94" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M94" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A95" s="14">
+      <c r="A95" s="13">
         <v>1</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="3" t="s">
@@ -5374,25 +5489,25 @@
       <c r="J95" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K95" s="11" t="s">
+      <c r="K95" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L95" s="10" t="s">
-        <v>116</v>
+      <c r="L95" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M95" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A96" s="14">
+      <c r="A96" s="13">
         <v>1</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="3" t="s">
@@ -5413,11 +5528,11 @@
       <c r="J96" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="K96" s="11" t="s">
+      <c r="K96" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="10" t="s">
-        <v>116</v>
+      <c r="L96" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="M96" s="6">
         <v>1</v>

--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C174BEA-B831-4918-B235-7ACE5BCAB3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47292892-FD96-4212-B6FD-65C4D4311B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="465">
   <si>
     <t>Option 1</t>
   </si>
@@ -96,46 +96,6 @@
   </si>
   <si>
     <t>Au cours de la contraction:</t>
-  </si>
-  <si>
-    <t>Des mitochondries isolées sont placées dans un milieu convenable en présence de différentes substances.
-On mesure la quantité d' ATP et le taux du dioxygène dans le milieu au cours du temps. le document suivant
-traduit les résultats obtenus Ces résultats montrent que:</t>
-  </si>
-  <si>
-    <t>Le document ci-contre résume la dégradation du glucose au cours de la respiration cellulaire (Voie
-A). Selon  la biochimie de stayer 6-ème édition », l'oxydation d'une molécule de (NADH, $H^{+}$) par la
-phosphorylation oxydative libère 2,5 ATP alors que l'oxydation d'une molécule de $FADH_{2}$ libère 1,5 ATP.
-Le bilan énergétique de l'oxydation complète d'une molécule de glucose par respiration cellule produit :</t>
-  </si>
-  <si>
-    <t>Soit les deux croisements suivants :
-Croisement 1 Des mâles de race pure à plumage bleu et yeux noirs avec des femelles de race pure à plumage
-brin et yeux orange. La première génération $F_{1}$ est constituée uniquement d'individus à plumage bleu et yeux
-noirs. Croisement 2: Des mâles de race pure à plumage brin et yeux orange avec des femelles de race pure
-à plumage bleu et yeux noirs. La génération $F_{1}^{\prime}$ obtenue est composée de 50% d'individus mâles à plumage
-bleu et yeux noirs et 50% d'individus femelles à plumage brin et yeux noirs. Chez les pigeons, la femelle est
-hétérogamète ZW et le mâle est homogamète ZZ. Dans le cas de croisement des mâles de $F_{1}$ avec des femelles
-à plumage brin et yeux orange. A probabilité des femelles à yeux noirs et plumage brin est de :</t>
-  </si>
-  <si>
-    <t>La synthèse des protéines exige la présence de ribosomes, des ARNt et des acides aminés. Le document
-suivant présente le dosage de quelques composant d'une cellule active. Le document présente la succession le
-phénomène suivants:
-A réplication, division puis transcription.</t>
-  </si>
-  <si>
-    <t>Le document ci-contre montre les résultats de l'analyse des fragments d'ADN d'un gène à deux allèles,
-par électrophorèse, chez une famille dont l'un des parents porte l'allèle muté responsable d'une maladie
-héréditaire. L'allèle responsable de cette maladie est :</t>
-  </si>
-  <si>
-    <t>Au sein d'une population européenne, la fréquence de l'allèle récessif autosomal responsable de la
-myopathie et de $q=0,05$. La population étudiée obéit à la loi de Hardy-Weinberg. La probabilité d'avoir un
-enfant malade en cas de mariage entre deux individus porteur sain de cette maladie et de:</t>
-  </si>
-  <si>
-    <t>Le document suivant présente deux caryotype des gamètes qui sont à l'origine d'un individu précis:</t>
   </si>
   <si>
     <t>la réplication de l'ADN:</t>
@@ -149,34 +109,15 @@
 séquence suivante :</t>
   </si>
   <si>
-    <t>On conclut que l'allèle responsable de cette maladie est:</t>
-  </si>
-  <si>
     <t>D'après ces résultats. on peut dire que :</t>
   </si>
   <si>
-    <t>Le document suivant représente l'arbre généalogique d'une famille dont certains membres sont atteints
-de la maladie de Kennedy. A partir de l'analyse de cette arbre généalogique, on peut affirmer que :</t>
-  </si>
-  <si>
     <t>Pour rechercher la trisomie 21 chez le fœtus, on se base sur :</t>
   </si>
   <si>
-    <t>Au cours de la gamétogenèse, une cellule mère des gamètes subit une méiose. Le schéma ci-contre de
-cette cellule correspond :</t>
-  </si>
-  <si>
     <t>L'information juste est:</t>
   </si>
   <si>
-    <t>La probabilité pour que le couple 7 de la population et sa femme 8 donne naissance à un enfant malade
-est de:</t>
-  </si>
-  <si>
-    <t>La digestion d'un DNA par une enzyme de restriction a permis l'obtention de 3 fragments A, B et C de
-tailles différentes -voir figure-. Séparés par électrophorèse le profile attendu correspondra à :</t>
-  </si>
-  <si>
     <t>Le phénomène qui apparaît lorsque les deux ondes se rencontre est:</t>
   </si>
   <si>
@@ -206,22 +147,9 @@
 $</t>
   </si>
   <si>
-    <t>Nombre d'émissions a et $_x0008_eta^{-1}$ respectivement est :</t>
-  </si>
-  <si>
-    <t>L'expression de $m_x0008_inom{206}{82}Pb)(t)$ s'écrit sous forme :
-$</t>
-  </si>
-  <si>
-    <t>La date lorsque $_x000C_rac{m_x0008_inom{206}{82}}Pb)(t)}{m_x0008_inom{238}{92}}^{238}U)(t)}=2,6$ en fonction de $t_{1/2}$ est :</t>
-  </si>
-  <si>
     <t>La valeur de la constante de désintégration est:</t>
   </si>
   <si>
-    <t>La date lorsque $N(Ca)(t)=_x000C_rac{7}{8}.N_{0}$ est:</t>
-  </si>
-  <si>
     <t>L'expression de $Y(t)$ s'écrit sous forme:</t>
   </si>
   <si>
@@ -232,9 +160,6 @@
   </si>
   <si>
     <t>At $t=2s$, on place K en position (2) et l'expression de $ln[q(t)]$ devient :</t>
-  </si>
-  <si>
-    <t>La valeur de la constante de temps équivalente est:</t>
   </si>
   <si>
     <t>Les courbes qui représentent les variations de $Uc1(t)$ et $Ur2(t)$ sont respectivement</t>
@@ -1526,6 +1451,160 @@
   <si>
     <t xml:space="preserve">La réduction de l'acide pyruvique:
 </t>
+  </si>
+  <si>
+    <t>GROUP</t>
+  </si>
+  <si>
+    <t>QUESTION</t>
+  </si>
+  <si>
+    <t>Soit les deux croisements suivants :
+&lt;br&gt;&lt;b&gt;Croisement 1&lt;/b&gt; : Des mâles de race pure à plumage bleu et yeux noirs avec des femelles de race pure à plumage brin et yeux orange. La première génération $F_{1}$ est constituée uniquement d'individus à plumage bleu et yeux noirs. 
+&lt;br&gt;&lt;b&gt;Croisement 2 &lt;*b&gt;: Des mâles de race pure à plumage brin et yeux orange avec des femelles de race pure à plumage bleu et yeux noirs. La génération $F_{1}^{\prime}$ obtenue est composée de 50% d'individus mâles à plumage bleu et yeux noirs et 50% d'individus femelles à plumage brin et yeux noirs. 
+Chez les pigeons, la femelle est hétérogamète ZW et le mâle est homogamète ZZ. Dans le cas de croisement des mâles de $F_{1}$ avec des femelles à plumage brin et yeux orange. 
+La probabilité des femelles à yeux noirs et plumage brin est de :</t>
+  </si>
+  <si>
+    <t>Au sein d'une population européenne, la fréquence de l'allèle récessif autosomal responsable de la
+myopathie et de $q=0,05$. La population étudiée obéit à la loi de Hardy-Weinberg. La probabilité d'avoir un
+enfant malade en cas de mariage entre deux individus porteur sain de cette maladie est de:</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 4 &lt;/b&gt;:   $\quad$Datation à l’aide de l’Uranium-Plomb.&lt;br&gt;
+Le nucléide Uranium ${}_{92}^{238}U$ est radioactif, il se transforme en nucléide de Plomb ${}_{82}^{206}Pb$ par une succession d’émissions de type \alpha et \beta^-.
+&lt;br&gt;On donne : $\frac{103}{119} = 0.865$; $\quad$ $\frac{865}{2600} =\frac{1}{3}$</t>
+  </si>
+  <si>
+    <t>Nombre d'émissions $\alpha$ et $\beta^{-1}$ respectivement est :</t>
+  </si>
+  <si>
+    <t>L'expression de $m({}_{82}^{206}Pb)$ s'écrit sous forme :
+$</t>
+  </si>
+  <si>
+    <t>La date lorsque $\fracm{m({}_{82}^{206}Pb)(t)}{m({}_{82}^{206}Pb)(t)} =2.6$ en fonction de t_{1/2} est:</t>
+  </si>
+  <si>
+    <t>La date lorsque $\frac{m{206}{82}}Pb)(t)}{m{238}{92}}^{238}U)(t)}=2,6$ en fonction de $t_{1/2}$ est :</t>
+  </si>
+  <si>
+    <t>Des mitochondries isolées sont placées dans un milieu convenable en présence de différentes substances.
+&lt;br&gt;On mesure la quantité d' ATP et le taux du dioxygène dans le milieu au cours du temps. 
+&lt;br&gt;Le document suivant traduit les résultats obtenus. 
+&lt;br&gt;&lt;img src="/images/CB1_Q1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+Ces résultats montrent que:</t>
+  </si>
+  <si>
+    <t>Le document ci-contre résume la dégradation du glucose au cours de la respiration cellulaire (Voie  A). 
+&lt;br&gt;&lt;img src="/images/CB1_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+Selon  la biochimie de "stayer 6-ème édition ", l'oxydation d'une molécule de (NADH, $H^{+}$) par la
+phosphorylation oxydative libère 2,5 ATP alors que l'oxydation d'une molécule de $FADH_{2}$ libère 1,5 ATP.
+&lt;br&gt;Le bilan énergétique de l'oxydation complète d'une molécule de glucose par respiration cellule produit :</t>
+  </si>
+  <si>
+    <t>La synthèse des protéines exige la présence de ribosomes, des ARNt et des acides aminés. Le document suivant présente le dosage de quelques composant d'une cellule active. 
+&lt;br&gt;&lt;img src="/images/CB1_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Le document présente la succession de phénomènes suivants:
+A réplication, division puis transcription.</t>
+  </si>
+  <si>
+    <t>Le document ci-contre montre les résultats de l'analyse des fragments d'ADN d'un gène à deux allèles,
+par électrophorèse, chez une famille dont l'un des parents porte l'allèle muté responsable d'une maladie
+héréditaire. 
+&lt;br&gt;&lt;img src="/images/CB1_Q4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+L'allèle responsable de cette maladie est :</t>
+  </si>
+  <si>
+    <t>Le document suivant présente deux caryotype des gamètes qui sont à l'origine d'un individu précis:
+&lt;br&gt;&lt;img src="/images/CB1_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>Une femme et son conjoint sont atteints d’une maladie héréditaire. Elle est inquiète quant à l’état de santé de son 
+foetus, elle procède à un diagnostic prénatal. Ledocument ci-contre représente les résultats de la séparation par 
+électrophorèse des fragments d’ADN des allèles (A1 et A2) du gène étudié, appartenant à la mère et son foetus 
+ainsi que le caryotype du foetus.
+&lt;br&gt;&lt;img src="/images/CB1_Q6.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;&lt;b&gt;On conclut que l'allèle responsable de cette maladie est:&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Le document suivant représente l'arbre généalogique d'une famille dont certains membres sont atteints
+de la maladie de Kennedy. 
+&lt;br&gt;&lt;img src="/images/CB1_Q7.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+A partir de l'analyse de cette arbre généalogique, on peut affirmer que :</t>
+  </si>
+  <si>
+    <t>Au cours de la gamétogenèse, une cellule mère des gamètes subit une méiose. Le schéma ci-contre de
+cette cellule correspond :
+&lt;br&gt;&lt;img src="/images/CB1_Q8.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>La probabilité pour que le couple 7 de la population et sa femme 8 donne naissance à un enfant malade
+est de:
+&lt;br&gt;&lt;img src="/images/CB1_Q9.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>La digestion d'un DNA par une enzyme de restriction a permis l'obtention de 3 fragments A, B et C de
+tailles différentes -voir figure-.
+&lt;br&gt;&lt;img src="/images/CB1_Q10.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+ Séparés par électrophorèse le profile attendu correspondra à :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Exercice 1 :   $\quad$ Rencontre de deux ondes progressives&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Une onde transversale d’amplitude $Y_1 = 2cm$ se propage à la vitesse $V_1 = 30cm.s^{−1}$ le long d’un axe OX. 
+Une deuxième onde d’amplitude $Y_2 = −3cm$ se propage à la vitesse $V_2 = 20cm.s^{−1}$ en sens contraire, sur le même axe. 
+A l’instant t=0s les deux ondes (1) et (2) se trouvent respectivement en position O et A.
+&lt;br&gt;&lt;img src="/images/CB1_Q11.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;On donne : d = OA = 50cm .</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 2 &lt;/b&gt; :   $\quad$ Deux milieux transparents&lt;br&gt;
+Un faisceau laser de la lumière rouge, de longueur d’onde dans le vide $\lambda_0$, et se propageant dans 
+deux milieux l’aire et le verre en même temps, est dirigé vers un trou de côté a .
+&lt;br&gt;&lt;img src="/images/CB1_Q12.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;On donne : $L = \frac{5}{3} cm$ , $\quad$ $L_1 = 1 cm$ $\quad$ et $\quad$ $C = 3.10^8 m.s^{−1}$ .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Exercice 3 &lt;/b&gt;:   $\quad$ Ondes à la surface d’un liquide&lt;br&gt;
+Les ondes de surface des liquides ont été étudiées en 1871 par Sir William Thomson, lord Kelvin. 
+L’onde se propage parallèlement à la surface qui oscille transversalement. La célérité de ces ondes s’écrit :
+$V =[\frac{a \cdot \lambda}{2 \PI} + \frac{2 \PI \cdot b}{\rho \cdot \lambda}]^\frac{1}{12}$
+où a et b des coefficients positives.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+&lt;br&gt;La valeur de la constante de temps équivalente est:
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Exercice 5&lt;/b&gt; :   $\quad$ Désintégration du potassium 40&lt;br&gt;
+88% des noyaux de potassium ${}_{19}^{40}K$ se transforment en calcium ${}_{20}^{40}Ca. C’est une désintégration 
+radioactive de type $\beta^-$. La figure ci-dessous représente les variation de potassium et calcium en fonction du temps. 
+&lt;br&gt;&lt;img src="/images/CB1_Q13.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;On donne : ln(2)=0,7.
+</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 6 &lt;/b&gt; : $\quad$ L’activité du radon 222 &lt;br&gt;
+Un noyau radioactif de radon ${}_[86}^{222}Rn$ se désintègre en émettant une particule $\alpha$ et noyau fils  ${}_[84}^{218}Po$. 
+La figure ci-dessous représente les variations de la fonction Y(t) tel que : $Y(t) = N_{Pₒ}(t) − N_{Rn}(t)$.
+&lt;br&gt;&lt;img src="/images/CB1_Q14.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;On donne :   $5.8.10^[-4} = \frac{50}{3600x24}$, $\quad$ In(2) = 0, 7 $\quad$ et $\quad$ 0,18x5,8 = 1,044 .</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 7 &lt;/b&gt;:  $\quad$ Charge et décharge du condensateur&lt;br&gt;
+On considère le circuit ci-dessous tel que : q(Os) = 2C , $I_0 = 4A$ , R = 2OkQ et C = 1.µF.
+&lt;br&gt;&lt;img src="/images/CB1_Q15.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+On donne : ln(100)=4,6 .
+On donne : ln(100)=4,6.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 8 &lt;/b&gt;:   $\quad$ Deux condensateurs et deux résistances.&lt;br&gt;
+On considère le circuit suivant : 
+&lt;br&gt;&lt;img src="/images/CB1_Q16.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+A l’instant t=0, on ferme l’interrupteur K durant une durée $t_0 = 2ms$. On charge alors 2 condensateurs idéaux (sans résistance de fuite) à l’aide d’un générateur de tension E = 24V. 
+On enregistre les 4 courbes ci-dessous. On donne : $24^2x11 = 6336$ , 11x33,33 = 366,63.</t>
   </si>
 </sst>
 </file>
@@ -1927,7 +2006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1993,23 +2072,23 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="4" t="s">
@@ -2034,19 +2113,19 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="3" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="4" t="s">
@@ -2059,7 +2138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1</v>
       </c>
@@ -2067,23 +2146,23 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="4" t="s">
@@ -2096,7 +2175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1</v>
       </c>
@@ -2104,23 +2183,23 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="J5" s="10"/>
       <c r="K5" s="4" t="s">
@@ -2133,7 +2212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -2141,23 +2220,23 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
+        <v>440</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="4" t="s">
@@ -2170,7 +2249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -2178,21 +2257,21 @@
         <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>449</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="4" t="s">
@@ -2205,7 +2284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1</v>
       </c>
@@ -2213,23 +2292,23 @@
         <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>450</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="4" t="s">
@@ -2250,23 +2329,23 @@
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>441</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="3" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="4" t="s">
@@ -2287,23 +2366,23 @@
         <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>26</v>
+        <v>451</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="3" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="4" t="s">
@@ -2324,23 +2403,23 @@
         <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="3" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="4" t="s">
@@ -2361,23 +2440,23 @@
         <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="3" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="4" t="s">
@@ -2398,23 +2477,23 @@
         <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="3" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="4" t="s">
@@ -2427,7 +2506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>1</v>
       </c>
@@ -2435,23 +2514,23 @@
         <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>30</v>
+        <v>452</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="3" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="4" t="s">
@@ -2472,23 +2551,23 @@
         <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="3" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="4" t="s">
@@ -2501,7 +2580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>1</v>
       </c>
@@ -2509,23 +2588,23 @@
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>32</v>
+        <v>453</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="J16" s="10"/>
       <c r="K16" s="4" t="s">
@@ -2546,23 +2625,23 @@
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="3" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="J17" s="10"/>
       <c r="K17" s="4" t="s">
@@ -2575,7 +2654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>1</v>
       </c>
@@ -2583,23 +2662,23 @@
         <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>34</v>
+        <v>454</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="3" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J18" s="10"/>
       <c r="K18" s="4" t="s">
@@ -2620,23 +2699,23 @@
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="4" t="s">
@@ -2649,7 +2728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>1</v>
       </c>
@@ -2657,23 +2736,23 @@
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>36</v>
+        <v>455</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="J20" s="10"/>
       <c r="K20" s="4" t="s">
@@ -2686,7 +2765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>1</v>
       </c>
@@ -2694,23 +2773,23 @@
         <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>37</v>
+        <v>456</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="J21" s="10"/>
       <c r="K21" s="4" t="s">
@@ -2723,31 +2802,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
-        <v>1</v>
-      </c>
+    <row r="22" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
       <c r="B22" s="5" t="s">
-        <v>15</v>
+        <v>438</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>196</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J22" s="2"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="10"/>
       <c r="K22" s="4" t="s">
         <v>9</v>
       </c>
@@ -2761,180 +2830,146 @@
         <v>1</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>201</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M23" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="M23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>1</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="J24" s="3"/>
-      <c r="K24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
       <c r="M24" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>1</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="3" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="J25" s="3"/>
-      <c r="K25" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
       <c r="M25" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <v>1</v>
-      </c>
+    <row r="26" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+      <c r="A26" s="11"/>
       <c r="B26" s="5" t="s">
-        <v>15</v>
+        <v>438</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>42</v>
+        <v>458</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J26" s="2"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
       <c r="K26" s="4" t="s">
         <v>9</v>
       </c>
       <c r="L26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M26" s="4"/>
-    </row>
-    <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="M26" s="5"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>1</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="3" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="J27" s="3"/>
-      <c r="K27" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="M27" s="5">
         <v>1</v>
       </c>
@@ -2944,64 +2979,48 @@
         <v>1</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="3" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M28" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
-        <v>1</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
       <c r="B29" s="5" t="s">
-        <v>15</v>
+        <v>438</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>45</v>
+        <v>459</v>
       </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>233</v>
-      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
       <c r="J29" s="2"/>
       <c r="K29" s="4" t="s">
         <v>9</v>
@@ -3011,70 +3030,68 @@
       </c>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>1</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>202</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="G30" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="H30" s="3"/>
+        <v>204</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="I30" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
       <c r="M30" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>1</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="3" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="H31" s="3"/>
+        <v>209</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="I31" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
       <c r="M31" s="5">
         <v>1</v>
       </c>
@@ -3084,64 +3101,48 @@
         <v>1</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="3" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="J32" s="2"/>
-      <c r="K32" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M32" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>1</v>
-      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
       <c r="B33" s="5" t="s">
-        <v>15</v>
+        <v>438</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>49</v>
+        <v>442</v>
       </c>
       <c r="D33" s="2"/>
-      <c r="E33" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>250</v>
-      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
       <c r="J33" s="2"/>
       <c r="K33" s="4" t="s">
         <v>9</v>
@@ -3151,138 +3152,122 @@
       </c>
       <c r="M33" s="4"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>1</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>50</v>
+        <v>443</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3" t="s">
-        <v>253</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="J34" s="2"/>
-      <c r="K34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="M34" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>51</v>
+        <v>444</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>258</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="H35" s="3"/>
       <c r="I35" s="3" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="J35" s="2"/>
-      <c r="K35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
       <c r="M35" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>1</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>52</v>
+        <v>446</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="3" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="J36" s="2"/>
-      <c r="K36" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M36" s="4"/>
-    </row>
-    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>1</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>15</v>
+        <v>438</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>53</v>
+        <v>461</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="3" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="4" t="s">
@@ -3291,210 +3276,164 @@
       <c r="L37" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M37" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
-        <v>1</v>
-      </c>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="11"/>
       <c r="B38" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="3" t="s">
-        <v>270</v>
-      </c>
+      <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>273</v>
-      </c>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M38" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>1</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>55</v>
+        <v>445</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>234</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>235</v>
+      </c>
       <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="H39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="J39" s="2"/>
-      <c r="K39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M39" s="4"/>
-    </row>
-    <row r="40" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
-        <v>1</v>
-      </c>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+      <c r="A40" s="11"/>
       <c r="B40" s="5" t="s">
-        <v>15</v>
+        <v>438</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>56</v>
+        <v>462</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="3" t="s">
-        <v>275</v>
-      </c>
+      <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-      <c r="G40" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="J40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="2"/>
       <c r="K40" s="4" t="s">
         <v>9</v>
       </c>
       <c r="L40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M40" s="4"/>
+      <c r="M40" s="5"/>
     </row>
     <row r="41" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>1</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="3" t="s">
-        <v>279</v>
+        <v>238</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>281</v>
+        <v>240</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>282</v>
+        <v>241</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M41" s="4"/>
+        <v>242</v>
+      </c>
+      <c r="J41" s="2"/>
+      <c r="M41" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>1</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="3" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>285</v>
+        <v>244</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
       <c r="M42" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="11">
-        <v>1</v>
-      </c>
+    <row r="43" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+      <c r="A43" s="11"/>
       <c r="B43" s="5" t="s">
-        <v>15</v>
+        <v>438</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>59</v>
+        <v>463</v>
       </c>
       <c r="D43" s="2"/>
-      <c r="E43" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>293</v>
-      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
       <c r="M43" s="4"/>
     </row>
     <row r="44" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -3502,35 +3441,35 @@
         <v>1</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="3" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>296</v>
+        <v>250</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>297</v>
+        <v>251</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M44" s="4">
+      <c r="M44" s="5">
         <v>1</v>
       </c>
     </row>
@@ -3539,174 +3478,142 @@
         <v>1</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>300</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M45" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
-        <v>1</v>
-      </c>
+      <c r="M45" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+      <c r="A46" s="11"/>
       <c r="B46" s="5" t="s">
-        <v>15</v>
+        <v>438</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>62</v>
+        <v>464</v>
       </c>
       <c r="D46" s="2"/>
-      <c r="E46" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>306</v>
-      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="2"/>
       <c r="K46" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M46" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="M46" s="5"/>
+    </row>
+    <row r="47" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>1</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>63</v>
+        <v>460</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>311</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
       <c r="J47" s="2"/>
-      <c r="K47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M47" s="4"/>
+      <c r="M47" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>1</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>313</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>314</v>
+        <v>259</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>316</v>
+        <v>261</v>
       </c>
       <c r="J48" s="3"/>
-      <c r="K48" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
       <c r="M48" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>1</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="3" t="s">
-        <v>317</v>
+        <v>262</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>318</v>
+        <v>263</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>319</v>
+        <v>264</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="I49" s="3"/>
+        <v>265</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="J49" s="3"/>
-      <c r="K49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
       <c r="M49" s="4">
         <v>1</v>
       </c>
@@ -3719,32 +3626,36 @@
         <v>15</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="3" t="s">
-        <v>321</v>
+        <v>267</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>322</v>
+        <v>268</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>323</v>
+        <v>269</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I50" s="3"/>
-      <c r="J50" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J50" s="3"/>
       <c r="K50" s="4" t="s">
         <v>16</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M50" s="4"/>
-    </row>
-    <row r="51" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M50" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>1</v>
       </c>
@@ -3752,28 +3663,32 @@
         <v>15</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="3" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="10"/>
+        <v>273</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J51" s="2"/>
       <c r="K51" s="4" t="s">
         <v>16</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M51" s="4">
-        <v>1</v>
-      </c>
+      <c r="M51" s="4"/>
     </row>
     <row r="52" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
@@ -3783,25 +3698,25 @@
         <v>15</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="3" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="J52" s="10"/>
+        <v>281</v>
+      </c>
+      <c r="J52" s="2"/>
       <c r="K52" s="4" t="s">
         <v>16</v>
       </c>
@@ -3812,7 +3727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>1</v>
       </c>
@@ -3820,25 +3735,25 @@
         <v>15</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="3" t="s">
-        <v>332</v>
+        <v>282</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="J53" s="10"/>
+        <v>286</v>
+      </c>
+      <c r="J53" s="2"/>
       <c r="K53" s="4" t="s">
         <v>16</v>
       </c>
@@ -3849,7 +3764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>1</v>
       </c>
@@ -3857,24 +3772,20 @@
         <v>15</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="3" t="s">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>338</v>
+        <v>288</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>341</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
       <c r="J54" s="2"/>
       <c r="K54" s="4" t="s">
         <v>16</v>
@@ -3882,9 +3793,11 @@
       <c r="L54" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M54" s="4"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>1</v>
       </c>
@@ -3892,34 +3805,32 @@
         <v>15</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="3" t="s">
-        <v>342</v>
+        <v>290</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>343</v>
+        <v>291</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>344</v>
+        <v>292</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="J55" s="10"/>
+        <v>294</v>
+      </c>
+      <c r="J55" s="2"/>
       <c r="K55" s="4" t="s">
         <v>16</v>
       </c>
       <c r="L55" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M55" s="4">
-        <v>1</v>
-      </c>
+      <c r="M55" s="4"/>
     </row>
     <row r="56" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
@@ -3929,23 +3840,25 @@
         <v>15</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="3" t="s">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G56" s="3"/>
+        <v>296</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="H56" s="3" t="s">
-        <v>349</v>
+        <v>298</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="J56" s="10"/>
+        <v>299</v>
+      </c>
+      <c r="J56" s="3"/>
       <c r="K56" s="4" t="s">
         <v>16</v>
       </c>
@@ -3964,25 +3877,23 @@
         <v>15</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="3" t="s">
-        <v>351</v>
+        <v>300</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>352</v>
+        <v>301</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="J57" s="10"/>
+        <v>303</v>
+      </c>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
       <c r="K57" s="4" t="s">
         <v>16</v>
       </c>
@@ -3993,7 +3904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>1</v>
       </c>
@@ -4001,36 +3912,32 @@
         <v>15</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="3" t="s">
-        <v>356</v>
+        <v>304</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>357</v>
+        <v>305</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>358</v>
+        <v>306</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="J58" s="10"/>
+        <v>307</v>
+      </c>
+      <c r="I58" s="3"/>
+      <c r="J58" s="2"/>
       <c r="K58" s="4" t="s">
         <v>16</v>
       </c>
       <c r="L58" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M58" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M58" s="4"/>
+    </row>
+    <row r="59" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
         <v>1</v>
       </c>
@@ -4038,30 +3945,30 @@
         <v>15</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="F59" s="3"/>
+        <v>308</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="G59" s="3"/>
-      <c r="H59" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="J59" s="2"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="10"/>
       <c r="K59" s="4" t="s">
         <v>16</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M59" s="4"/>
-    </row>
-    <row r="60" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M59" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>1</v>
       </c>
@@ -4069,23 +3976,23 @@
         <v>15</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="3" t="s">
-        <v>363</v>
+        <v>310</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>364</v>
+        <v>311</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>365</v>
+        <v>312</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>366</v>
+        <v>313</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>367</v>
+        <v>314</v>
       </c>
       <c r="J60" s="10"/>
       <c r="K60" s="4" t="s">
@@ -4098,7 +4005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
         <v>1</v>
       </c>
@@ -4106,23 +4013,23 @@
         <v>15</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="3" t="s">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>120</v>
+        <v>316</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>368</v>
+        <v>318</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>119</v>
+        <v>319</v>
       </c>
       <c r="J61" s="10"/>
       <c r="K61" s="4" t="s">
@@ -4135,7 +4042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>1</v>
       </c>
@@ -4143,36 +4050,34 @@
         <v>15</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="3" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>371</v>
+        <v>322</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>372</v>
+        <v>323</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="J62" s="10"/>
-      <c r="K62" s="9" t="s">
-        <v>10</v>
+        <v>324</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L62" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M62" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M62" s="4"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
         <v>1</v>
       </c>
@@ -4180,23 +4085,27 @@
         <v>15</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D63" s="2"/>
-      <c r="E63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="F63" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="G63" s="3"/>
+        <v>326</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>327</v>
+      </c>
       <c r="H63" s="3" t="s">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>375</v>
+        <v>329</v>
       </c>
       <c r="J63" s="10"/>
-      <c r="K63" s="9" t="s">
-        <v>10</v>
+      <c r="K63" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L63" s="4" t="s">
         <v>18</v>
@@ -4205,7 +4114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
         <v>1</v>
       </c>
@@ -4213,34 +4122,34 @@
         <v>15</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="3" t="s">
-        <v>376</v>
+        <v>330</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>378</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
-        <v>379</v>
+        <v>332</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="J64" s="2"/>
-      <c r="K64" s="9" t="s">
-        <v>10</v>
+        <v>333</v>
+      </c>
+      <c r="J64" s="10"/>
+      <c r="K64" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L64" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M64" s="4"/>
-    </row>
-    <row r="65" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="M64" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
         <v>1</v>
       </c>
@@ -4248,27 +4157,27 @@
         <v>15</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3" t="s">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>382</v>
+        <v>335</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>383</v>
+        <v>336</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>384</v>
+        <v>337</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="J65" s="10"/>
-      <c r="K65" s="9" t="s">
-        <v>10</v>
+      <c r="K65" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>18</v>
@@ -4277,7 +4186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>1</v>
       </c>
@@ -4285,27 +4194,27 @@
         <v>15</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="3" t="s">
-        <v>386</v>
+        <v>339</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>387</v>
+        <v>340</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>388</v>
+        <v>341</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>389</v>
+        <v>102</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="J66" s="10"/>
-      <c r="K66" s="9" t="s">
-        <v>10</v>
+      <c r="K66" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L66" s="4" t="s">
         <v>18</v>
@@ -4314,7 +4223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
         <v>1</v>
       </c>
@@ -4322,25 +4231,23 @@
         <v>15</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3" t="s">
-        <v>391</v>
+        <v>343</v>
       </c>
       <c r="F67" s="3"/>
-      <c r="G67" s="3" t="s">
-        <v>392</v>
-      </c>
+      <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="J67" s="2"/>
-      <c r="K67" s="9" t="s">
-        <v>10</v>
+      <c r="K67" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L67" s="4" t="s">
         <v>18</v>
@@ -4355,27 +4262,27 @@
         <v>15</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="3" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>397</v>
+        <v>348</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="J68" s="10"/>
-      <c r="K68" s="9" t="s">
-        <v>10</v>
+      <c r="K68" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L68" s="4" t="s">
         <v>18</v>
@@ -4384,7 +4291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
         <v>1</v>
       </c>
@@ -4392,25 +4299,27 @@
         <v>15</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="3" t="s">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="G69" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>341</v>
+      </c>
       <c r="H69" s="3" t="s">
-        <v>402</v>
+        <v>351</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>403</v>
+        <v>102</v>
       </c>
       <c r="J69" s="10"/>
-      <c r="K69" s="9" t="s">
-        <v>10</v>
+      <c r="K69" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="L69" s="4" t="s">
         <v>18</v>
@@ -4419,7 +4328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
         <v>1</v>
       </c>
@@ -4427,23 +4336,23 @@
         <v>15</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="3" t="s">
-        <v>404</v>
+        <v>352</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>405</v>
+        <v>353</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>406</v>
+        <v>354</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>407</v>
+        <v>355</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>408</v>
+        <v>356</v>
       </c>
       <c r="J70" s="10"/>
       <c r="K70" s="9" t="s">
@@ -4456,7 +4365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
         <v>1</v>
       </c>
@@ -4464,32 +4373,30 @@
         <v>15</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D71" s="2"/>
-      <c r="E71" s="3" t="s">
-        <v>409</v>
-      </c>
+      <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>411</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>400</v>
+        <v>344</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="J71" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="J71" s="10"/>
       <c r="K71" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M71" s="4"/>
+      <c r="M71" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
@@ -4499,36 +4406,34 @@
         <v>15</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="3" t="s">
-        <v>413</v>
+        <v>359</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>414</v>
+        <v>360</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>415</v>
+        <v>361</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="J72" s="10"/>
+        <v>363</v>
+      </c>
+      <c r="J72" s="2"/>
       <c r="K72" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M72" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M72" s="4"/>
+    </row>
+    <row r="73" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
         <v>1</v>
       </c>
@@ -4536,21 +4441,23 @@
         <v>15</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="3" t="s">
-        <v>418</v>
+        <v>364</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="G73" s="3"/>
+        <v>365</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>366</v>
+      </c>
       <c r="H73" s="3" t="s">
-        <v>420</v>
+        <v>367</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="J73" s="10"/>
       <c r="K73" s="9" t="s">
@@ -4563,7 +4470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
         <v>1</v>
       </c>
@@ -4571,34 +4478,36 @@
         <v>15</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="3" t="s">
-        <v>422</v>
+        <v>369</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>423</v>
+        <v>370</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>424</v>
+        <v>371</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>425</v>
+        <v>372</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="J74" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="J74" s="10"/>
       <c r="K74" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L74" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M74" s="4"/>
-    </row>
-    <row r="75" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="M74" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
         <v>1</v>
       </c>
@@ -4606,36 +4515,32 @@
         <v>15</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>428</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>429</v>
+        <v>375</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>430</v>
+        <v>376</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="J75" s="10"/>
+        <v>377</v>
+      </c>
+      <c r="J75" s="2"/>
       <c r="K75" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L75" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M75" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M75" s="4"/>
+    </row>
+    <row r="76" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A76" s="11">
         <v>1</v>
       </c>
@@ -4643,23 +4548,23 @@
         <v>15</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="3" t="s">
-        <v>432</v>
+        <v>378</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>433</v>
+        <v>379</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>434</v>
+        <v>380</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="J76" s="10"/>
       <c r="K76" s="9" t="s">
@@ -4672,7 +4577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="11">
         <v>1</v>
       </c>
@@ -4680,34 +4585,34 @@
         <v>15</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="3" t="s">
-        <v>436</v>
+        <v>383</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="H77" s="3"/>
+        <v>384</v>
+      </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3" t="s">
+        <v>385</v>
+      </c>
       <c r="I77" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="J77" s="3"/>
+        <v>386</v>
+      </c>
+      <c r="J77" s="10"/>
       <c r="K77" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M77" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M77" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A78" s="11">
         <v>1</v>
       </c>
@@ -4715,36 +4620,36 @@
         <v>15</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="3" t="s">
-        <v>440</v>
+        <v>387</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>441</v>
+        <v>388</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>442</v>
+        <v>389</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>443</v>
+        <v>390</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="J78" s="3"/>
+        <v>391</v>
+      </c>
+      <c r="J78" s="10"/>
       <c r="K78" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L78" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M78" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="M78" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="11">
         <v>1</v>
       </c>
@@ -4752,36 +4657,34 @@
         <v>15</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="3" t="s">
-        <v>445</v>
+        <v>392</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>446</v>
+        <v>393</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>448</v>
+        <v>383</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="J79" s="3"/>
+        <v>395</v>
+      </c>
+      <c r="J79" s="2"/>
       <c r="K79" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L79" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M79" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="M79" s="4"/>
+    </row>
+    <row r="80" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
         <v>1</v>
       </c>
@@ -4789,32 +4692,322 @@
         <v>15</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="3" t="s">
-        <v>450</v>
+        <v>396</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>451</v>
+        <v>397</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>452</v>
+        <v>398</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>453</v>
+        <v>399</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="J80" s="3"/>
+        <v>400</v>
+      </c>
+      <c r="J80" s="10"/>
       <c r="K80" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L80" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M80" s="5">
+      <c r="M80" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="11">
+        <v>1</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J81" s="10"/>
+      <c r="K81" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M81" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A82" s="11">
+        <v>1</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="J82" s="2"/>
+      <c r="K82" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M82" s="4"/>
+    </row>
+    <row r="83" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="A83" s="11">
+        <v>1</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J83" s="10"/>
+      <c r="K83" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M83" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A84" s="11">
+        <v>1</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="J84" s="10"/>
+      <c r="K84" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M84" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A85" s="11">
+        <v>1</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="J85" s="3"/>
+      <c r="K85" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M85" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A86" s="11">
+        <v>1</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="J86" s="3"/>
+      <c r="K86" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M86" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A87" s="11">
+        <v>1</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D87" s="2"/>
+      <c r="E87" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="J87" s="3"/>
+      <c r="K87" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M87" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A88" s="11">
+        <v>1</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D88" s="2"/>
+      <c r="E88" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J88" s="3"/>
+      <c r="K88" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M88" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47292892-FD96-4212-B6FD-65C4D4311B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6C143D-A016-417C-B11D-3A1AF39B2E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="471">
   <si>
     <t>Option 1</t>
   </si>
@@ -124,45 +124,19 @@
     <t>Les valeurs de (X,Y),abscisse et amplitude du point M lieu de rencontre des deux ondes,sont égales à :</t>
   </si>
   <si>
-    <t>La valeur $t_{M}$ la date de rencontre des deux ondes au point M, est égale à :
-$</t>
-  </si>
-  <si>
     <t>L'expression de l'indice de réfraction du verre est :</t>
   </si>
   <si>
-    <t>La vitesse de la lumière rouge dans le verre est :
-$</t>
-  </si>
-  <si>
-    <t>La dimension du coefficient b est:
-$</t>
-  </si>
-  <si>
-    <t>La célérité d'onde pour liquide (1) est:
-$</t>
-  </si>
-  <si>
-    <t>Pour liquide (2) on a $\lambda_{2}=2.\lambda_{1},$ la valeur de la célérité $V_{2}$ vaut :
-$</t>
-  </si>
-  <si>
     <t>La valeur de la constante de désintégration est:</t>
   </si>
   <si>
     <t>L'expression de $Y(t)$ s'écrit sous forme:</t>
   </si>
   <si>
-    <t>l'activité initiale de cet échantillon vaut :</t>
-  </si>
-  <si>
     <t>$A\mathfrak{t}=0s$, on place K en position (1) et l'expression de $q(\mathfrak{t})$ devient :</t>
   </si>
   <si>
     <t>At $t=2s$, on place K en position (2) et l'expression de $ln[q(t)]$ devient :</t>
-  </si>
-  <si>
-    <t>Les courbes qui représentent les variations de $Uc1(t)$ et $Ur2(t)$ sont respectivement</t>
   </si>
   <si>
     <t>l'énergie totale $E_{T}$ emmagasinée par les deux condensateurs en régime permanent vaut :</t>
@@ -560,9 +534,6 @@
     <t>l'échographie.</t>
   </si>
   <si>
-    <t>$	ilde{A}$ l'anaphase 1 d'une cellule à $2n=12$.</t>
-  </si>
-  <si>
     <t>À l'anaphase 1 d'une cellule à $2n=6.$</t>
   </si>
   <si>
@@ -647,137 +618,9 @@
     <t>$X=20cm$ et $Y=5cm.$</t>
   </si>
   <si>
-    <t>5s,$
-$</t>
-  </si>
-  <si>
-    <t>3s.$</t>
-  </si>
-  <si>
-    <t>2s.</t>
-  </si>
-  <si>
-    <t>1s. $</t>
-  </si>
-  <si>
-    <t>4s.$</t>
-  </si>
-  <si>
-    <t>$_x000C_rac{L_{1}}{L}$ $</t>
-  </si>
-  <si>
-    <t>rac{L}{L_{1}}$</t>
-  </si>
-  <si>
-    <t>$_x000C_rac{L_{1}-L}{L_{1}}$ $</t>
-  </si>
-  <si>
-    <t>rac{L}{L-L1}$ $</t>
-  </si>
-  <si>
-    <t>rac{L_{1}}{L-L_{1}}$</t>
-  </si>
-  <si>
-    <t>3.10^{7}m.s^{-1}$ $</t>
-  </si>
-  <si>
-    <t>15.10^{7}m.s^{-1}$</t>
-  </si>
-  <si>
-    <t>17,5.107m.s ¹. $</t>
-  </si>
-  <si>
-    <t>20.10^{7}m.s^{-1}$ $</t>
-  </si>
-  <si>
-    <t>25.10^{7}m.s^{-1}$</t>
-  </si>
-  <si>
-    <t>M.T^{2}$ $</t>
-  </si>
-  <si>
-    <t>M.T^{-2}.$ $</t>
-  </si>
-  <si>
-    <t>M.T^{-1}$ $</t>
-  </si>
-  <si>
-    <t>M.T^{1}$ $</t>
-  </si>
-  <si>
-    <t>M.T$</t>
-  </si>
-  <si>
-    <t>1,29~m/s$ $</t>
-  </si>
-  <si>
-    <t>1,31~m/s$ $</t>
-  </si>
-  <si>
-    <t>1.3m/s$ $</t>
-  </si>
-  <si>
-    <t>1,28m/s$ $</t>
-  </si>
-  <si>
-    <t>1,32m/s$</t>
-  </si>
-  <si>
-    <t>1,5m/s$. $</t>
-  </si>
-  <si>
-    <t>1,3m/s.$ $</t>
-  </si>
-  <si>
-    <t>1.4m/s$ $</t>
-  </si>
-  <si>
-    <t>1,6m/s$
-$</t>
-  </si>
-  <si>
-    <t>1,7m/s.$</t>
-  </si>
-  <si>
-    <t>8 et 6. B 6 et 8. $</t>
-  </si>
-  <si>
-    <t>8$ et 4. D 4 et 8.</t>
-  </si>
-  <si>
-    <t>7 et 7.</t>
-  </si>
-  <si>
-    <t>0,865.m_{0}(pb).(1-e^{-\lambda.t})$ $</t>
-  </si>
-  <si>
-    <t>0,865.m_{0}(U).e^{-\lambda.t}.$ D $:m_{0}(U).(1-e^{-\lambda I}).$
-$</t>
-  </si>
-  <si>
-    <t>m_{0}(pb).(1-e^{-\lambda.t}).$
-$</t>
-  </si>
-  <si>
-    <t>0,865.m_{0}(U).(1-e^{-i.t})$</t>
-  </si>
-  <si>
     <t>$t_{1/2}$</t>
   </si>
   <si>
-    <t>$4.t_{1/2}$
-$</t>
-  </si>
-  <si>
-    <t>2.t_{1/2}$ $</t>
-  </si>
-  <si>
-    <t>5t_{1/2}$ $</t>
-  </si>
-  <si>
-    <t>3x_{1}/2,$</t>
-  </si>
-  <si>
     <t>$2.10^{-10}ans^{-1}$ $</t>
   </si>
   <si>
@@ -808,95 +651,19 @@
     <t>$N_{0}.(1-2e^{\lambda.t})$.</t>
   </si>
   <si>
-    <t>$N_{0}.(2-e^{-\lambda.t})$.
-$</t>
-  </si>
-  <si>
-    <t>$N_{0}.(1-2e^{-\lambda.t}).$</t>
-  </si>
-  <si>
-    <t>N_{0}.(2e^{\lambda.t}-1)$</t>
-  </si>
-  <si>
     <t>$N_{0}.(2e^{-\lambda x}-1)$.</t>
   </si>
   <si>
-    <t>$10^{2}Bq$ $</t>
-  </si>
-  <si>
-    <t>10^{3}Bq$ $</t>
-  </si>
-  <si>
-    <t>10^{4}Bq$</t>
-  </si>
-  <si>
-    <t>$10^{5}Bq.$
-$</t>
-  </si>
-  <si>
-    <t>10^{6}Bq.$</t>
-  </si>
-  <si>
-    <t>4.1.</t>
-  </si>
-  <si>
-    <t>$2t+4$
-$</t>
-  </si>
-  <si>
     <t>$4t+2.$</t>
   </si>
   <si>
-    <t>2t.$
-$</t>
-  </si>
-  <si>
-    <t>-4t+2$</t>
-  </si>
-  <si>
-    <t>$50(t-2)+2,3.$
-B
-$-50(t-2)+4,6.$</t>
-  </si>
-  <si>
-    <t>$50(2-t)-2,3.$
-$</t>
-  </si>
-  <si>
-    <t>-50t+102,3$</t>
-  </si>
-  <si>
     <t>$-50t+104,6$</t>
   </si>
   <si>
     <t>6,33ms. B 30.30ms C 16,5ms. D 33,33ms E 3,67ms.</t>
   </si>
   <si>
-    <t>A et D. B A et B.</t>
-  </si>
-  <si>
-    <t>Cet D.</t>
-  </si>
-  <si>
-    <t>Det B.</t>
-  </si>
-  <si>
-    <t>Bet C.</t>
-  </si>
-  <si>
     <t>20mj.</t>
-  </si>
-  <si>
-    <t>31,68mj.</t>
-  </si>
-  <si>
-    <t>64,22mj.</t>
-  </si>
-  <si>
-    <t>7,12mj.</t>
-  </si>
-  <si>
-    <t>44.22mj.</t>
   </si>
   <si>
     <t>$(Al^{3+}/Al)$ et $(H_{3}O^{+}/H_{2})$. $</t>
@@ -1459,34 +1226,12 @@
     <t>QUESTION</t>
   </si>
   <si>
-    <t>Soit les deux croisements suivants :
-&lt;br&gt;&lt;b&gt;Croisement 1&lt;/b&gt; : Des mâles de race pure à plumage bleu et yeux noirs avec des femelles de race pure à plumage brin et yeux orange. La première génération $F_{1}$ est constituée uniquement d'individus à plumage bleu et yeux noirs. 
-&lt;br&gt;&lt;b&gt;Croisement 2 &lt;*b&gt;: Des mâles de race pure à plumage brin et yeux orange avec des femelles de race pure à plumage bleu et yeux noirs. La génération $F_{1}^{\prime}$ obtenue est composée de 50% d'individus mâles à plumage bleu et yeux noirs et 50% d'individus femelles à plumage brin et yeux noirs. 
-Chez les pigeons, la femelle est hétérogamète ZW et le mâle est homogamète ZZ. Dans le cas de croisement des mâles de $F_{1}$ avec des femelles à plumage brin et yeux orange. 
-La probabilité des femelles à yeux noirs et plumage brin est de :</t>
-  </si>
-  <si>
     <t>Au sein d'une population européenne, la fréquence de l'allèle récessif autosomal responsable de la
 myopathie et de $q=0,05$. La population étudiée obéit à la loi de Hardy-Weinberg. La probabilité d'avoir un
 enfant malade en cas de mariage entre deux individus porteur sain de cette maladie est de:</t>
   </si>
   <si>
-    <t>&lt;b&gt;Exercice 4 &lt;/b&gt;:   $\quad$Datation à l’aide de l’Uranium-Plomb.&lt;br&gt;
-Le nucléide Uranium ${}_{92}^{238}U$ est radioactif, il se transforme en nucléide de Plomb ${}_{82}^{206}Pb$ par une succession d’émissions de type \alpha et \beta^-.
-&lt;br&gt;On donne : $\frac{103}{119} = 0.865$; $\quad$ $\frac{865}{2600} =\frac{1}{3}$</t>
-  </si>
-  <si>
     <t>Nombre d'émissions $\alpha$ et $\beta^{-1}$ respectivement est :</t>
-  </si>
-  <si>
-    <t>L'expression de $m({}_{82}^{206}Pb)$ s'écrit sous forme :
-$</t>
-  </si>
-  <si>
-    <t>La date lorsque $\fracm{m({}_{82}^{206}Pb)(t)}{m({}_{82}^{206}Pb)(t)} =2.6$ en fonction de t_{1/2} est:</t>
-  </si>
-  <si>
-    <t>La date lorsque $\frac{m{206}{82}}Pb)(t)}{m{238}{92}}^{238}U)(t)}=2,6$ en fonction de $t_{1/2}$ est :</t>
   </si>
   <si>
     <t>Des mitochondries isolées sont placées dans un milieu convenable en présence de différentes substances.
@@ -1501,12 +1246,6 @@
 Selon  la biochimie de "stayer 6-ème édition ", l'oxydation d'une molécule de (NADH, $H^{+}$) par la
 phosphorylation oxydative libère 2,5 ATP alors que l'oxydation d'une molécule de $FADH_{2}$ libère 1,5 ATP.
 &lt;br&gt;Le bilan énergétique de l'oxydation complète d'une molécule de glucose par respiration cellule produit :</t>
-  </si>
-  <si>
-    <t>La synthèse des protéines exige la présence de ribosomes, des ARNt et des acides aminés. Le document suivant présente le dosage de quelques composant d'une cellule active. 
-&lt;br&gt;&lt;img src="/images/CB1_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-&lt;br&gt;Le document présente la succession de phénomènes suivants:
-A réplication, division puis transcription.</t>
   </si>
   <si>
     <t>Le document ci-contre montre les résultats de l'analyse des fragments d'ADN d'un gène à deux allèles,
@@ -1550,7 +1289,38 @@
  Séparés par électrophorèse le profile attendu correspondra à :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Exercice 1 :   $\quad$ Rencontre de deux ondes progressives&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+    <t>&lt;b&gt;Exercice 2 &lt;/b&gt; :   $\quad$ Deux milieux transparents&lt;br&gt;
+Un faisceau laser de la lumière rouge, de longueur d’onde dans le vide $\lambda_0$, et se propageant dans 
+deux milieux l’aire et le verre en même temps, est dirigé vers un trou de côté a .
+&lt;br&gt;&lt;img src="/images/CB1_Q12.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;On donne : $L = \frac{5}{3} cm$ , $\quad$ $L_1 = 1 cm$ $\quad$ et $\quad$ $C = 3.10^8 m.s^{−1}$ .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+&lt;br&gt;La valeur de la constante de temps équivalente est:
+</t>
+  </si>
+  <si>
+    <t>Soit les deux croisements suivants :
+&lt;br&gt;&lt;b&gt;Croisement 1&lt;/b&gt; : Des mâles de race pure à plumage bleu et yeux noirs avec des femelles de race pure à plumage brin et yeux orange. La première génération $F_{1}$ est constituée uniquement d'individus à plumage bleu et yeux noirs. 
+&lt;br&gt;&lt;b&gt;Croisement 2 &lt;/b&gt;: Des mâles de race pure à plumage brin et yeux orange avec des femelles de race pure à plumage bleu et yeux noirs. La génération $F_{1}^{\prime}$ obtenue est composée de 50% d'individus mâles à plumage bleu et yeux noirs et 50% d'individus femelles à plumage brin et yeux noirs. 
+Chez les pigeons, la femelle est hétérogamète ZW et le mâle est homogamète ZZ. Dans le cas de croisement des mâles de $F_{1}$ avec des femelles à plumage brin et yeux orange. 
+La probabilité des femelles à yeux noirs et plumage brin est de :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La synthèse des protéines exige la présence de ribosomes, des ARNt et des acides aminés. Le document suivant présente le dosage de quelques composant d'une cellule active. 
+&lt;br&gt;&lt;img src="/images/CB1_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;Le document présente la succession de phénomènes suivants:
+</t>
+  </si>
+  <si>
+    <t>A réplication, division puis transcription.</t>
+  </si>
+  <si>
+    <t>À l'anaphase 1 d'une cellule à $2n=12$.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 1 :   $\quad$ Rencontre de deux ondes progressives&lt;/b&gt;&lt;br&gt;
 &lt;br&gt;Une onde transversale d’amplitude $Y_1 = 2cm$ se propage à la vitesse $V_1 = 30cm.s^{−1}$ le long d’un axe OX. 
 Une deuxième onde d’amplitude $Y_2 = −3cm$ se propage à la vitesse $V_2 = 20cm.s^{−1}$ en sens contraire, sur le même axe. 
 A l’instant t=0s les deux ondes (1) et (2) se trouvent respectivement en position O et A.
@@ -1558,53 +1328,285 @@
 &lt;br&gt;On donne : d = OA = 50cm .</t>
   </si>
   <si>
-    <t>&lt;b&gt;Exercice 2 &lt;/b&gt; :   $\quad$ Deux milieux transparents&lt;br&gt;
-Un faisceau laser de la lumière rouge, de longueur d’onde dans le vide $\lambda_0$, et se propageant dans 
-deux milieux l’aire et le verre en même temps, est dirigé vers un trou de côté a .
-&lt;br&gt;&lt;img src="/images/CB1_Q12.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-&lt;br&gt;On donne : $L = \frac{5}{3} cm$ , $\quad$ $L_1 = 1 cm$ $\quad$ et $\quad$ $C = 3.10^8 m.s^{−1}$ .</t>
+    <t>La valeur $t_{M}$ la date de rencontre des deux ondes au point M, est égale à :</t>
+  </si>
+  <si>
+    <t>5s</t>
+  </si>
+  <si>
+    <t>3s</t>
+  </si>
+  <si>
+    <t>2s</t>
+  </si>
+  <si>
+    <t>1s</t>
+  </si>
+  <si>
+    <t>4s</t>
+  </si>
+  <si>
+    <t>La vitesse de la lumière rouge dans le verre est :</t>
+  </si>
+  <si>
+    <t>$\frac{L_1}{L}$</t>
+  </si>
+  <si>
+    <t>$\frac{L}{L_1}$</t>
+  </si>
+  <si>
+    <t>$\frac{L_1-L}{L_1}$</t>
+  </si>
+  <si>
+    <t>$\frac{L}{L-L_1}$</t>
+  </si>
+  <si>
+    <t>$\frac{L_1}{L-L_1}$</t>
+  </si>
+  <si>
+    <t>$3.10^{7}m.s^{-1}$</t>
+  </si>
+  <si>
+    <t>$15.10^{7}m.s^{-1}$</t>
+  </si>
+  <si>
+    <t>$17,5.10^7m.s^{-1} $</t>
+  </si>
+  <si>
+    <t>$20.10^{7}m.s^{-1}$</t>
+  </si>
+  <si>
+    <t>$25.10^{7}m.s^{-1}$</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Exercice 3 &lt;/b&gt;:   $\quad$ Ondes à la surface d’un liquide&lt;br&gt;
 Les ondes de surface des liquides ont été étudiées en 1871 par Sir William Thomson, lord Kelvin. 
 L’onde se propage parallèlement à la surface qui oscille transversalement. La célérité de ces ondes s’écrit :
-$V =[\frac{a \cdot \lambda}{2 \PI} + \frac{2 \PI \cdot b}{\rho \cdot \lambda}]^\frac{1}{12}$
+$V =[\frac{a \cdot \lambda}{2 \pi} + \frac{2 \pi \cdot b}{\rho \cdot \lambda}]^\frac{1}{12}$
 où a et b des coefficients positives.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">
-&lt;br&gt;La valeur de la constante de temps équivalente est:
-</t>
+    <t>La dimension du coefficient b est:</t>
+  </si>
+  <si>
+    <t>$M.T^{2}$</t>
+  </si>
+  <si>
+    <t>$M.T^{-2}.$</t>
+  </si>
+  <si>
+    <t>$M.T^{-1}$</t>
+  </si>
+  <si>
+    <t>$M.T^{1}$</t>
+  </si>
+  <si>
+    <t>$M.T$</t>
+  </si>
+  <si>
+    <t>La célérité d'onde pour liquide (1) est:</t>
+  </si>
+  <si>
+    <t>$1,29 m/s$</t>
+  </si>
+  <si>
+    <t>$1,31 m/s$</t>
+  </si>
+  <si>
+    <t>$1.3 m/s$</t>
+  </si>
+  <si>
+    <t>$1,28 m/s$</t>
+  </si>
+  <si>
+    <t>$1,32 m/s$</t>
+  </si>
+  <si>
+    <t>Pour liquide (2) on a $\lambda_{2}=2.\lambda_{1},$ la valeur de la célérité $V_{2}$ vaut :</t>
+  </si>
+  <si>
+    <t>$1,5 m/s$</t>
+  </si>
+  <si>
+    <t>$1,3 m/s$</t>
+  </si>
+  <si>
+    <t>$1,4 m/s$</t>
+  </si>
+  <si>
+    <t>$1,6 m/s$</t>
+  </si>
+  <si>
+    <t>$1,7 m/s$</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 4 &lt;/b&gt;:   $\quad$Datation à l’aide de l’Uranium-Plomb.&lt;br&gt;
+Le nucléide Uranium ${}_{92}^{238}U$ est radioactif, il se transforme en nucléide de Plomb ${}_{82}^{206}Pb$ par une succession d’émissions de type $\alpha$ et $\beta^-$
+&lt;br&gt;On donne : $\frac{103}{119} = 0.865$; $\quad$ $\frac{865}{2600} =\frac{1}{3}$</t>
+  </si>
+  <si>
+    <t>8 et 6</t>
+  </si>
+  <si>
+    <t>6 et 8</t>
+  </si>
+  <si>
+    <t>8 et 4</t>
+  </si>
+  <si>
+    <t>4 et 8</t>
+  </si>
+  <si>
+    <t>7 et 7</t>
+  </si>
+  <si>
+    <t>L'expression de $m({}_{82}^{206}Pb)$ s'écrit sous forme :</t>
+  </si>
+  <si>
+    <t>$0,865.m_{0}(pb).(1-e^{-\lambda.t})$</t>
+  </si>
+  <si>
+    <t>$0,865.m_{0}(U).e^{-\lambda.t}$</t>
+  </si>
+  <si>
+    <t>$m_{0}(U).(1-e^{-\lambda I})$</t>
+  </si>
+  <si>
+    <t>$m_{0}(pb).(1-e^{-\lambda.t})$
+$</t>
+  </si>
+  <si>
+    <t>$0,865.m_{0}(U).(1-e^{-i.t})$</t>
+  </si>
+  <si>
+    <t>La date lorsque $\frac{m{}_{206}^{82}}Pb(t)}{m{}_{238}^{92}}U(t)}=2,6$ en fonction de $t_{1/2}$ est :</t>
+  </si>
+  <si>
+    <t>$2.t_{1/2}$</t>
+  </si>
+  <si>
+    <t>$5.t_{1/2}$</t>
+  </si>
+  <si>
+    <t>$4.t_{1/2}$</t>
+  </si>
+  <si>
+    <t>$3. t_{1/2}$</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Exercice 5&lt;/b&gt; :   $\quad$ Désintégration du potassium 40&lt;br&gt;
 88% des noyaux de potassium ${}_{19}^{40}K$ se transforment en calcium ${}_{20}^{40}Ca. C’est une désintégration 
-radioactive de type $\beta^-$. La figure ci-dessous représente les variation de potassium et calcium en fonction du temps. 
+radioactive de type $\beta^-$. 
+&lt;br&gt;La figure ci-dessous représente les variation de potassium et calcium en fonction du temps. 
 &lt;br&gt;&lt;img src="/images/CB1_Q13.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;On donne : ln(2)=0,7.
 </t>
+  </si>
+  <si>
+    <t>La date lorsque $\frac {m{}_{82}^{206}Pb)(t)}{m({}_{82}^{206}Pb)(t)} =2.6$ en fonction de t_{1/2} est:</t>
   </si>
   <si>
     <t>&lt;b&gt;Exercice 6 &lt;/b&gt; : $\quad$ L’activité du radon 222 &lt;br&gt;
 Un noyau radioactif de radon ${}_[86}^{222}Rn$ se désintègre en émettant une particule $\alpha$ et noyau fils  ${}_[84}^{218}Po$. 
 La figure ci-dessous représente les variations de la fonction Y(t) tel que : $Y(t) = N_{Pₒ}(t) − N_{Rn}(t)$.
 &lt;br&gt;&lt;img src="/images/CB1_Q14.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-&lt;br&gt;On donne :   $5.8.10^[-4} = \frac{50}{3600x24}$, $\quad$ In(2) = 0, 7 $\quad$ et $\quad$ 0,18x5,8 = 1,044 .</t>
+&lt;br&gt;On donne :   $5,8.10^{-4} = \frac{50}{3600x24}$, $\quad$ In(2) = 0, 7 $\quad$ et $\quad$ 0,18x5,8 = 1,044 .</t>
+  </si>
+  <si>
+    <t>$N_{0}.(2-e^{-\lambda.t})$</t>
+  </si>
+  <si>
+    <t>$N_{0}.(1-2e^{-\lambda.t})$</t>
+  </si>
+  <si>
+    <t>$N_{0}.(2e^{\lambda.t}-1)$</t>
+  </si>
+  <si>
+    <t>L'activité initiale de cet échantillon vaut :</t>
+  </si>
+  <si>
+    <t>$10^{2}Bq$</t>
+  </si>
+  <si>
+    <t>$10^{3}Bq$</t>
+  </si>
+  <si>
+    <t>$10^{4}Bq$</t>
+  </si>
+  <si>
+    <t>$10^{5}Bq.$</t>
+  </si>
+  <si>
+    <t>$10^{6}Bq.$</t>
   </si>
   <si>
     <t>&lt;b&gt;Exercice 7 &lt;/b&gt;:  $\quad$ Charge et décharge du condensateur&lt;br&gt;
-On considère le circuit ci-dessous tel que : q(Os) = 2C , $I_0 = 4A$ , R = 2OkQ et C = 1.µF.
+On considère le circuit ci-dessous tel que : q(0s) = 2C , $I_0 = 4A$ , R = 2O kQ et C = 1.µF.
 &lt;br&gt;&lt;img src="/images/CB1_Q15.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-On donne : ln(100)=4,6 .
-On donne : ln(100)=4,6.</t>
+On donne : ln(100)=4,6</t>
+  </si>
+  <si>
+    <t>4.t</t>
+  </si>
+  <si>
+    <t>$2t+4$</t>
+  </si>
+  <si>
+    <t>$2t.$</t>
+  </si>
+  <si>
+    <t>$-4t+2$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$50(t-2)+2,3.$
+</t>
+  </si>
+  <si>
+    <t>$-50(t-2)+4,6.$</t>
+  </si>
+  <si>
+    <t>$50(2-t)-2,3.$</t>
+  </si>
+  <si>
+    <t>$-50t+102,3$</t>
   </si>
   <si>
     <t>&lt;b&gt;Exercice 8 &lt;/b&gt;:   $\quad$ Deux condensateurs et deux résistances.&lt;br&gt;
 On considère le circuit suivant : 
 &lt;br&gt;&lt;img src="/images/CB1_Q16.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 A l’instant t=0, on ferme l’interrupteur K durant une durée $t_0 = 2ms$. On charge alors 2 condensateurs idéaux (sans résistance de fuite) à l’aide d’un générateur de tension E = 24V. 
-On enregistre les 4 courbes ci-dessous. On donne : $24^2x11 = 6336$ , 11x33,33 = 366,63.</t>
+On enregistre les 4 courbes ci-dessous. On donne : $24^2. 11 = 6336$ , 11. 33,33 = 366,63</t>
+  </si>
+  <si>
+    <t>31,68 mj.</t>
+  </si>
+  <si>
+    <t>64,22 mj.</t>
+  </si>
+  <si>
+    <t>7,12 mj.</t>
+  </si>
+  <si>
+    <t>44.22 mj.</t>
+  </si>
+  <si>
+    <t>Les courbes qui représentent les variations de $U_{c1}(t)$ et $U_{r2}(t)$ sont respectivement :</t>
+  </si>
+  <si>
+    <t>A et D</t>
+  </si>
+  <si>
+    <t>A et B</t>
+  </si>
+  <si>
+    <t>C et D</t>
+  </si>
+  <si>
+    <t>D et B</t>
+  </si>
+  <si>
+    <t>B et C</t>
   </si>
 </sst>
 </file>
@@ -2072,23 +2074,23 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>437</v>
+        <v>365</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="4" t="s">
@@ -2113,19 +2115,19 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="4" t="s">
@@ -2146,23 +2148,23 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>447</v>
+        <v>370</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="4" t="s">
@@ -2183,23 +2185,23 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>448</v>
+        <v>371</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="J5" s="10"/>
       <c r="K5" s="4" t="s">
@@ -2220,23 +2222,23 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>440</v>
+        <v>381</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="4" t="s">
@@ -2257,21 +2259,23 @@
         <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>449</v>
+        <v>382</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="3"/>
+      <c r="E7" s="3" t="s">
+        <v>383</v>
+      </c>
       <c r="F7" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="4" t="s">
@@ -2292,23 +2296,23 @@
         <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>450</v>
+        <v>372</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="4" t="s">
@@ -2329,23 +2333,23 @@
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>441</v>
+        <v>368</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="4" t="s">
@@ -2366,23 +2370,23 @@
         <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>451</v>
+        <v>373</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="4" t="s">
@@ -2407,19 +2411,19 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="4" t="s">
@@ -2444,19 +2448,19 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="4" t="s">
@@ -2481,19 +2485,19 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="4" t="s">
@@ -2514,23 +2518,23 @@
         <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>452</v>
+        <v>374</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="4" t="s">
@@ -2555,19 +2559,19 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="4" t="s">
@@ -2588,23 +2592,23 @@
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>453</v>
+        <v>375</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J16" s="10"/>
       <c r="K16" s="4" t="s">
@@ -2629,19 +2633,19 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J17" s="10"/>
       <c r="K17" s="4" t="s">
@@ -2662,23 +2666,23 @@
         <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>454</v>
+        <v>376</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="3" t="s">
-        <v>158</v>
+        <v>384</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="J18" s="10"/>
       <c r="K18" s="4" t="s">
@@ -2703,19 +2707,19 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="4" t="s">
@@ -2736,23 +2740,23 @@
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>455</v>
+        <v>377</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J20" s="10"/>
       <c r="K20" s="4" t="s">
@@ -2773,23 +2777,23 @@
         <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>456</v>
+        <v>378</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="J21" s="10"/>
       <c r="K21" s="4" t="s">
@@ -2805,10 +2809,10 @@
     <row r="22" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="5" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="3"/>
@@ -2830,24 +2834,24 @@
         <v>1</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="J23" s="2"/>
       <c r="M23" s="4">
@@ -2859,26 +2863,26 @@
         <v>1</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="4"/>
@@ -2887,31 +2891,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>1</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>386</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="3" t="s">
-        <v>187</v>
+        <v>387</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>188</v>
+        <v>388</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>189</v>
+        <v>389</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>191</v>
+        <v>391</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="4"/>
@@ -2923,10 +2927,10 @@
     <row r="26" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="5" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>458</v>
+        <v>379</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="3"/>
@@ -2948,57 +2952,57 @@
         <v>1</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="3" t="s">
-        <v>192</v>
+        <v>393</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>193</v>
+        <v>394</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>194</v>
+        <v>395</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>195</v>
+        <v>396</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>196</v>
+        <v>397</v>
       </c>
       <c r="J27" s="3"/>
       <c r="M27" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>1</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>30</v>
+        <v>392</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="3" t="s">
-        <v>197</v>
+        <v>398</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>198</v>
+        <v>399</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>199</v>
+        <v>400</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>200</v>
+        <v>401</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>201</v>
+        <v>402</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="4"/>
@@ -3010,10 +3014,10 @@
     <row r="29" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="5" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>459</v>
+        <v>403</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="3"/>
@@ -3030,31 +3034,31 @@
       </c>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>1</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>31</v>
+        <v>404</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="3" t="s">
-        <v>202</v>
+        <v>405</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>203</v>
+        <v>406</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>204</v>
+        <v>407</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>205</v>
+        <v>408</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>206</v>
+        <v>409</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="4"/>
@@ -3063,31 +3067,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>1</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>32</v>
+        <v>410</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="3" t="s">
-        <v>207</v>
+        <v>411</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>208</v>
+        <v>412</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>209</v>
+        <v>413</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>210</v>
+        <v>414</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>211</v>
+        <v>415</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="4"/>
@@ -3096,31 +3100,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>1</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>33</v>
+        <v>416</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="3" t="s">
-        <v>212</v>
+        <v>417</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>213</v>
+        <v>418</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>214</v>
+        <v>419</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>215</v>
+        <v>420</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>216</v>
+        <v>421</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="4"/>
@@ -3132,10 +3136,10 @@
     <row r="33" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="5" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="3"/>
@@ -3157,51 +3161,57 @@
         <v>1</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>443</v>
+        <v>369</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>423</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>424</v>
+      </c>
       <c r="G34" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="H34" s="3"/>
+        <v>425</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="I34" s="3" t="s">
-        <v>219</v>
+        <v>427</v>
       </c>
       <c r="J34" s="2"/>
       <c r="M34" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="3" t="s">
-        <v>220</v>
+        <v>429</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>221</v>
+        <v>430</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="H35" s="3"/>
+        <v>432</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="I35" s="3" t="s">
-        <v>223</v>
+        <v>433</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="4"/>
@@ -3215,26 +3225,26 @@
         <v>1</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="3" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>225</v>
+        <v>437</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>226</v>
+        <v>435</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>227</v>
+        <v>436</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>228</v>
+        <v>438</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="4"/>
@@ -3243,32 +3253,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>1</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="D37" s="2"/>
-      <c r="E37" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="J37" s="2"/>
       <c r="K37" s="4" t="s">
         <v>9</v>
@@ -3281,17 +3276,27 @@
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="E38" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="J38" s="2"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -3304,24 +3309,24 @@
         <v>1</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="3" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="4"/>
@@ -3333,10 +3338,10 @@
     <row r="40" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="5" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>462</v>
+        <v>441</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="3"/>
@@ -3353,62 +3358,62 @@
       </c>
       <c r="M40" s="5"/>
     </row>
-    <row r="41" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>1</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="3" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>239</v>
+        <v>442</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>240</v>
+        <v>443</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>241</v>
+        <v>444</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="J41" s="2"/>
       <c r="M41" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>1</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>36</v>
+        <v>445</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="3" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>244</v>
+        <v>447</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>245</v>
+        <v>448</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>246</v>
+        <v>449</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>247</v>
+        <v>450</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="4"/>
@@ -3417,13 +3422,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="5" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="3"/>
@@ -3432,8 +3437,12 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
+      <c r="K43" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="M43" s="4"/>
     </row>
     <row r="44" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -3441,69 +3450,61 @@
         <v>1</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="3" t="s">
-        <v>248</v>
+        <v>452</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>249</v>
+        <v>453</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>250</v>
+        <v>191</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>251</v>
+        <v>454</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>252</v>
+        <v>455</v>
       </c>
       <c r="J44" s="2"/>
-      <c r="K44" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="M44" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>1</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F45" s="3"/>
+        <v>456</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>457</v>
+      </c>
       <c r="G45" s="3" t="s">
-        <v>254</v>
+        <v>458</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>255</v>
+        <v>459</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="J45" s="2"/>
-      <c r="K45" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
       <c r="M45" s="5">
         <v>1</v>
       </c>
@@ -3511,10 +3512,10 @@
     <row r="46" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="5" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="3"/>
@@ -3536,14 +3537,14 @@
         <v>1</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>460</v>
+        <v>380</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="3" t="s">
-        <v>257</v>
+        <v>193</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -3559,24 +3560,26 @@
         <v>1</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>39</v>
+        <v>465</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F48" s="3"/>
+        <v>466</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>467</v>
+      </c>
       <c r="G48" s="3" t="s">
-        <v>259</v>
+        <v>468</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>260</v>
+        <v>469</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>261</v>
+        <v>470</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="4"/>
@@ -3590,26 +3593,26 @@
         <v>1</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="3" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>263</v>
+        <v>461</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>264</v>
+        <v>462</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>265</v>
+        <v>463</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>266</v>
+        <v>464</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="4"/>
@@ -3626,23 +3629,23 @@
         <v>15</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="3" t="s">
-        <v>267</v>
+        <v>195</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="4" t="s">
@@ -3663,23 +3666,23 @@
         <v>15</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="3" t="s">
-        <v>272</v>
+        <v>200</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>274</v>
+        <v>202</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="4" t="s">
@@ -3698,23 +3701,23 @@
         <v>15</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="3" t="s">
-        <v>277</v>
+        <v>205</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>278</v>
+        <v>206</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>279</v>
+        <v>207</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>281</v>
+        <v>209</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="4" t="s">
@@ -3735,23 +3738,23 @@
         <v>15</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="3" t="s">
-        <v>282</v>
+        <v>210</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>283</v>
+        <v>211</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>284</v>
+        <v>212</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>285</v>
+        <v>213</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>286</v>
+        <v>214</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="4" t="s">
@@ -3772,17 +3775,17 @@
         <v>15</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="3" t="s">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>288</v>
+        <v>216</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>289</v>
+        <v>217</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -3805,23 +3808,23 @@
         <v>15</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="3" t="s">
-        <v>290</v>
+        <v>218</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>291</v>
+        <v>219</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>292</v>
+        <v>220</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>293</v>
+        <v>221</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>294</v>
+        <v>222</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="4" t="s">
@@ -3840,23 +3843,23 @@
         <v>15</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="3" t="s">
-        <v>295</v>
+        <v>223</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>296</v>
+        <v>224</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>298</v>
+        <v>226</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>299</v>
+        <v>227</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="4" t="s">
@@ -3877,20 +3880,20 @@
         <v>15</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="3" t="s">
-        <v>300</v>
+        <v>228</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>301</v>
+        <v>229</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>302</v>
+        <v>230</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>303</v>
+        <v>231</v>
       </c>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
@@ -3912,20 +3915,20 @@
         <v>15</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="3" t="s">
-        <v>304</v>
+        <v>232</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>305</v>
+        <v>233</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>306</v>
+        <v>234</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>307</v>
+        <v>235</v>
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="2"/>
@@ -3945,14 +3948,14 @@
         <v>15</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="3" t="s">
-        <v>308</v>
+        <v>236</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>309</v>
+        <v>237</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
@@ -3976,23 +3979,23 @@
         <v>15</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="3" t="s">
-        <v>310</v>
+        <v>238</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>312</v>
+        <v>240</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>313</v>
+        <v>241</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>314</v>
+        <v>242</v>
       </c>
       <c r="J60" s="10"/>
       <c r="K60" s="4" t="s">
@@ -4013,23 +4016,23 @@
         <v>15</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="3" t="s">
-        <v>315</v>
+        <v>243</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>316</v>
+        <v>244</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>317</v>
+        <v>245</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>318</v>
+        <v>246</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>319</v>
+        <v>247</v>
       </c>
       <c r="J61" s="10"/>
       <c r="K61" s="4" t="s">
@@ -4050,23 +4053,23 @@
         <v>15</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="3" t="s">
-        <v>320</v>
+        <v>248</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>322</v>
+        <v>250</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="4" t="s">
@@ -4085,23 +4088,23 @@
         <v>15</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="3" t="s">
-        <v>325</v>
+        <v>253</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>326</v>
+        <v>254</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>327</v>
+        <v>255</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>328</v>
+        <v>256</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>329</v>
+        <v>257</v>
       </c>
       <c r="J63" s="10"/>
       <c r="K63" s="4" t="s">
@@ -4122,21 +4125,21 @@
         <v>15</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="3" t="s">
-        <v>330</v>
+        <v>258</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>331</v>
+        <v>259</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
-        <v>332</v>
+        <v>260</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>333</v>
+        <v>261</v>
       </c>
       <c r="J64" s="10"/>
       <c r="K64" s="4" t="s">
@@ -4157,23 +4160,23 @@
         <v>15</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3" t="s">
-        <v>334</v>
+        <v>262</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>335</v>
+        <v>263</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>336</v>
+        <v>264</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>337</v>
+        <v>265</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="J65" s="10"/>
       <c r="K65" s="4" t="s">
@@ -4194,23 +4197,23 @@
         <v>15</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="3" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>340</v>
+        <v>268</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>341</v>
+        <v>269</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>342</v>
+        <v>270</v>
       </c>
       <c r="J66" s="10"/>
       <c r="K66" s="4" t="s">
@@ -4231,19 +4234,19 @@
         <v>15</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3" t="s">
-        <v>343</v>
+        <v>271</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
-        <v>344</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>345</v>
+        <v>273</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="4" t="s">
@@ -4262,23 +4265,23 @@
         <v>15</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="3" t="s">
-        <v>346</v>
+        <v>274</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>347</v>
+        <v>275</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>348</v>
+        <v>276</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>349</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>350</v>
+        <v>278</v>
       </c>
       <c r="J68" s="10"/>
       <c r="K68" s="4" t="s">
@@ -4299,23 +4302,23 @@
         <v>15</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="3" t="s">
-        <v>340</v>
+        <v>268</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>341</v>
+        <v>269</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J69" s="10"/>
       <c r="K69" s="4" t="s">
@@ -4336,23 +4339,23 @@
         <v>15</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="3" t="s">
-        <v>352</v>
+        <v>280</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>353</v>
+        <v>281</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>354</v>
+        <v>282</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>355</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>356</v>
+        <v>284</v>
       </c>
       <c r="J70" s="10"/>
       <c r="K70" s="9" t="s">
@@ -4373,19 +4376,19 @@
         <v>15</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>357</v>
+        <v>285</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>344</v>
+        <v>272</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="J71" s="10"/>
       <c r="K71" s="9" t="s">
@@ -4406,23 +4409,23 @@
         <v>15</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="3" t="s">
-        <v>359</v>
+        <v>287</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>360</v>
+        <v>288</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>361</v>
+        <v>289</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>362</v>
+        <v>290</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>363</v>
+        <v>291</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="9" t="s">
@@ -4441,23 +4444,23 @@
         <v>15</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="3" t="s">
-        <v>364</v>
+        <v>292</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>365</v>
+        <v>293</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>366</v>
+        <v>294</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>367</v>
+        <v>295</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>368</v>
+        <v>296</v>
       </c>
       <c r="J73" s="10"/>
       <c r="K73" s="9" t="s">
@@ -4478,23 +4481,23 @@
         <v>15</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="3" t="s">
-        <v>369</v>
+        <v>297</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>370</v>
+        <v>298</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>371</v>
+        <v>299</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>373</v>
+        <v>301</v>
       </c>
       <c r="J74" s="10"/>
       <c r="K74" s="9" t="s">
@@ -4515,21 +4518,21 @@
         <v>15</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="3" t="s">
-        <v>374</v>
+        <v>302</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>375</v>
+        <v>303</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>376</v>
+        <v>304</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>377</v>
+        <v>305</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="9" t="s">
@@ -4548,23 +4551,23 @@
         <v>15</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="3" t="s">
-        <v>378</v>
+        <v>306</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>380</v>
+        <v>308</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>381</v>
+        <v>309</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="J76" s="10"/>
       <c r="K76" s="9" t="s">
@@ -4585,21 +4588,21 @@
         <v>15</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="3" t="s">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>384</v>
+        <v>312</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>385</v>
+        <v>313</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>386</v>
+        <v>314</v>
       </c>
       <c r="J77" s="10"/>
       <c r="K77" s="9" t="s">
@@ -4620,23 +4623,23 @@
         <v>15</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="3" t="s">
-        <v>387</v>
+        <v>315</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>388</v>
+        <v>316</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>389</v>
+        <v>317</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>390</v>
+        <v>318</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>391</v>
+        <v>319</v>
       </c>
       <c r="J78" s="10"/>
       <c r="K78" s="9" t="s">
@@ -4657,23 +4660,23 @@
         <v>15</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="3" t="s">
-        <v>392</v>
+        <v>320</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>395</v>
+        <v>323</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="9" t="s">
@@ -4692,23 +4695,23 @@
         <v>15</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="3" t="s">
-        <v>396</v>
+        <v>324</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>397</v>
+        <v>325</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>398</v>
+        <v>326</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>399</v>
+        <v>327</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="J80" s="10"/>
       <c r="K80" s="9" t="s">
@@ -4729,21 +4732,21 @@
         <v>15</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="3" t="s">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
-        <v>403</v>
+        <v>331</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>404</v>
+        <v>332</v>
       </c>
       <c r="J81" s="10"/>
       <c r="K81" s="9" t="s">
@@ -4764,23 +4767,23 @@
         <v>15</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="3" t="s">
-        <v>405</v>
+        <v>333</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>406</v>
+        <v>334</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>407</v>
+        <v>335</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>408</v>
+        <v>336</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>409</v>
+        <v>337</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="9" t="s">
@@ -4799,23 +4802,23 @@
         <v>15</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="3" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>411</v>
+        <v>339</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>413</v>
+        <v>341</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>414</v>
+        <v>342</v>
       </c>
       <c r="J83" s="10"/>
       <c r="K83" s="9" t="s">
@@ -4836,23 +4839,23 @@
         <v>15</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="3" t="s">
-        <v>415</v>
+        <v>343</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>416</v>
+        <v>344</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>417</v>
+        <v>345</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>418</v>
+        <v>346</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>344</v>
+        <v>272</v>
       </c>
       <c r="J84" s="10"/>
       <c r="K84" s="9" t="s">
@@ -4873,21 +4876,21 @@
         <v>15</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="3" t="s">
-        <v>419</v>
+        <v>347</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>420</v>
+        <v>348</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>421</v>
+        <v>349</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="3" t="s">
-        <v>422</v>
+        <v>350</v>
       </c>
       <c r="J85" s="3"/>
       <c r="K85" s="9" t="s">
@@ -4908,23 +4911,23 @@
         <v>15</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="3" t="s">
-        <v>423</v>
+        <v>351</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>424</v>
+        <v>352</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>425</v>
+        <v>353</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>426</v>
+        <v>354</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>427</v>
+        <v>355</v>
       </c>
       <c r="J86" s="3"/>
       <c r="K86" s="9" t="s">
@@ -4945,23 +4948,23 @@
         <v>15</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="3" t="s">
-        <v>428</v>
+        <v>356</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>429</v>
+        <v>357</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>430</v>
+        <v>358</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>431</v>
+        <v>359</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="J87" s="3"/>
       <c r="K87" s="9" t="s">
@@ -4982,23 +4985,23 @@
         <v>15</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="3" t="s">
-        <v>433</v>
+        <v>361</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>434</v>
+        <v>362</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>435</v>
+        <v>363</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>436</v>
+        <v>364</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>386</v>
+        <v>314</v>
       </c>
       <c r="J88" s="3"/>
       <c r="K88" s="9" t="s">

--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6C143D-A016-417C-B11D-3A1AF39B2E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8055E08-9F83-4835-AAB5-4FA2D8AD901A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="473">
   <si>
     <t>Option 1</t>
   </si>
@@ -388,22 +388,6 @@
     <t>Porté par le chromosome Y.</t>
   </si>
   <si>
-    <t>0,009.</t>
-  </si>
-  <si>
-    <t>0,03.</t>
-  </si>
-  <si>
-    <t>0,13.
-$</t>
-  </si>
-  <si>
-    <t>0,02$</t>
-  </si>
-  <si>
-    <t>0,002.</t>
-  </si>
-  <si>
     <t>C'est individu est une fille.</t>
   </si>
   <si>
@@ -594,64 +578,19 @@
     <t>Distribution.</t>
   </si>
   <si>
-    <t>Diffraction. C Superposition.</t>
-  </si>
-  <si>
     <t>Diffusion.</t>
   </si>
   <si>
     <t>Dispersion.</t>
   </si>
   <si>
-    <t>$X=30cm$ et $Y=-10mm.$</t>
-  </si>
-  <si>
-    <t>$X=20cm$ et $Y=-50mm.$</t>
-  </si>
-  <si>
-    <t>$X=30m$ et $Y=lcm$</t>
-  </si>
-  <si>
-    <t>$X=40cm$ et $Y=50mm.$</t>
-  </si>
-  <si>
-    <t>$X=20cm$ et $Y=5cm.$</t>
-  </si>
-  <si>
     <t>$t_{1/2}$</t>
   </si>
   <si>
-    <t>$2.10^{-10}ans^{-1}$ $</t>
-  </si>
-  <si>
-    <t>2.10^{10}ans$. $</t>
-  </si>
-  <si>
-    <t>1,4.10^{9}ans$.</t>
-  </si>
-  <si>
     <t>$5.10^{-10}ans^{-1}$</t>
   </si>
   <si>
-    <t>$5.10^{10}$ ans.</t>
-  </si>
-  <si>
-    <t>4,2Gans.</t>
-  </si>
-  <si>
-    <t>4,1Gans. C 4Gans.</t>
-  </si>
-  <si>
-    <t>3Gans.</t>
-  </si>
-  <si>
-    <t>1.Gans.</t>
-  </si>
-  <si>
     <t>$N_{0}.(1-2e^{\lambda.t})$.</t>
-  </si>
-  <si>
-    <t>$N_{0}.(2e^{-\lambda x}-1)$.</t>
   </si>
   <si>
     <t>$4t+2.$</t>
@@ -1470,17 +1409,8 @@
     <t>$0,865.m_{0}(U).e^{-\lambda.t}$</t>
   </si>
   <si>
-    <t>$m_{0}(U).(1-e^{-\lambda I})$</t>
-  </si>
-  <si>
     <t>$m_{0}(pb).(1-e^{-\lambda.t})$
 $</t>
-  </si>
-  <si>
-    <t>$0,865.m_{0}(U).(1-e^{-i.t})$</t>
-  </si>
-  <si>
-    <t>La date lorsque $\frac{m{}_{206}^{82}}Pb(t)}{m{}_{238}^{92}}U(t)}=2,6$ en fonction de $t_{1/2}$ est :</t>
   </si>
   <si>
     <t>$2.t_{1/2}$</t>
@@ -1504,16 +1434,6 @@
 </t>
   </si>
   <si>
-    <t>La date lorsque $\frac {m{}_{82}^{206}Pb)(t)}{m({}_{82}^{206}Pb)(t)} =2.6$ en fonction de t_{1/2} est:</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Exercice 6 &lt;/b&gt; : $\quad$ L’activité du radon 222 &lt;br&gt;
-Un noyau radioactif de radon ${}_[86}^{222}Rn$ se désintègre en émettant une particule $\alpha$ et noyau fils  ${}_[84}^{218}Po$. 
-La figure ci-dessous représente les variations de la fonction Y(t) tel que : $Y(t) = N_{Pₒ}(t) − N_{Rn}(t)$.
-&lt;br&gt;&lt;img src="/images/CB1_Q14.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-&lt;br&gt;On donne :   $5,8.10^{-4} = \frac{50}{3600x24}$, $\quad$ In(2) = 0, 7 $\quad$ et $\quad$ 0,18x5,8 = 1,044 .</t>
-  </si>
-  <si>
     <t>$N_{0}.(2-e^{-\lambda.t})$</t>
   </si>
   <si>
@@ -1607,6 +1527,91 @@
   </si>
   <si>
     <t>B et C</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>0,009</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>0,002</t>
+  </si>
+  <si>
+    <t>Diffraction.</t>
+  </si>
+  <si>
+    <t>Superposition.</t>
+  </si>
+  <si>
+    <t>$X=30 cm$ et $Y=-10 mm.$</t>
+  </si>
+  <si>
+    <t>$X=20 cm$ et $Y=-50 mm.$</t>
+  </si>
+  <si>
+    <t>$X=30 m$ et $Y=1 cm$</t>
+  </si>
+  <si>
+    <t>$X=40 cm$ et $Y=50 mm.$</t>
+  </si>
+  <si>
+    <t>$X=20 cm$ et $Y=5 cm.$</t>
+  </si>
+  <si>
+    <t>$0,865.m_{0}(U).(1-e^{-\lambda.t})$</t>
+  </si>
+  <si>
+    <t>$m_{0}(U).(1-e^{-\lambda.t})$</t>
+  </si>
+  <si>
+    <t>La date lorsque $\frac{m({}_{206}^{82}})Pb(t)}{m({}_{238}^{92}})U(t)}=2,6$ en fonction de $t_{1/2}$ est :</t>
+  </si>
+  <si>
+    <t>La date lorsque $N(C_a)(t) = \frac {7}{8}. \cdot N_0$ est:</t>
+  </si>
+  <si>
+    <t>$2.10^{-10}ans^{-1}$</t>
+  </si>
+  <si>
+    <t>$2.10^{10}ans$</t>
+  </si>
+  <si>
+    <t>$1,4.10^{9}ans$</t>
+  </si>
+  <si>
+    <t>$5.10^{10}$ ans$</t>
+  </si>
+  <si>
+    <t>4,2 Gans</t>
+  </si>
+  <si>
+    <t>1 Gans</t>
+  </si>
+  <si>
+    <t>3 Gans</t>
+  </si>
+  <si>
+    <t>4 Gans</t>
+  </si>
+  <si>
+    <t>4,1 Gans</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 6 &lt;/b&gt; : $\quad$ L’activité du radon 222 &lt;br&gt;
+Un noyau radioactif de radon $({}_[86}^{222})Rn$ se désintègre en émettant une particule $\alpha$ et noyau fils  $({}_[84}^{218})Po$. 
+La figure ci-dessous représente les variations de la fonction Y(t) tel que : $Y(t) = N_{Pₒ}(t) − N_{Rn}(t)$.
+&lt;br&gt;&lt;img src="/images/CB1_Q14.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;On donne :   $5,8.10^{-4} = \frac{50}{3600 . 24}$, $\quad$ In(2) = 0, 7 $\quad$ et $\quad$ 0,18 . 5,8 = 1,044</t>
+  </si>
+  <si>
+    <t>$N_{0}.(2e^{-\lambda t}-1)$.</t>
   </si>
 </sst>
 </file>
@@ -2074,7 +2079,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="3" t="s">
@@ -2148,7 +2153,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="3" t="s">
@@ -2185,7 +2190,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
@@ -2222,7 +2227,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3" t="s">
@@ -2259,11 +2264,11 @@
         <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="3" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>98</v>
@@ -2296,7 +2301,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3" t="s">
@@ -2333,23 +2338,23 @@
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="3" t="s">
-        <v>106</v>
+        <v>448</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>107</v>
+        <v>447</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>108</v>
+        <v>446</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>109</v>
+        <v>449</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="4" t="s">
@@ -2370,23 +2375,23 @@
         <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="4" t="s">
@@ -2411,19 +2416,19 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="4" t="s">
@@ -2448,19 +2453,19 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="4" t="s">
@@ -2485,19 +2490,19 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="4" t="s">
@@ -2518,23 +2523,23 @@
         <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="4" t="s">
@@ -2559,19 +2564,19 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="4" t="s">
@@ -2592,23 +2597,23 @@
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="J16" s="10"/>
       <c r="K16" s="4" t="s">
@@ -2633,19 +2638,19 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="J17" s="10"/>
       <c r="K17" s="4" t="s">
@@ -2666,23 +2671,23 @@
         <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="3" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J18" s="10"/>
       <c r="K18" s="4" t="s">
@@ -2707,19 +2712,19 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="4" t="s">
@@ -2740,23 +2745,23 @@
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="J20" s="10"/>
       <c r="K20" s="4" t="s">
@@ -2777,23 +2782,23 @@
         <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J21" s="10"/>
       <c r="K21" s="4" t="s">
@@ -2809,10 +2814,10 @@
     <row r="22" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="5" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="3"/>
@@ -2834,24 +2839,26 @@
         <v>1</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G23" s="3"/>
+        <v>451</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>452</v>
+      </c>
       <c r="H23" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="J23" s="2"/>
       <c r="M23" s="4">
@@ -2863,26 +2870,26 @@
         <v>1</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="3" t="s">
-        <v>174</v>
+        <v>453</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>175</v>
+        <v>454</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>455</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>177</v>
+        <v>456</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>178</v>
+        <v>457</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="4"/>
@@ -2896,26 +2903,26 @@
         <v>1</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="3" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="4"/>
@@ -2927,10 +2934,10 @@
     <row r="26" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="5" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="3"/>
@@ -2952,26 +2959,26 @@
         <v>1</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="3" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="J27" s="3"/>
       <c r="M27" s="5">
@@ -2983,26 +2990,26 @@
         <v>1</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="3" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="4"/>
@@ -3014,10 +3021,10 @@
     <row r="29" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="5" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="3"/>
@@ -3039,26 +3046,26 @@
         <v>1</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="3" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="4"/>
@@ -3072,26 +3079,26 @@
         <v>1</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="3" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="4"/>
@@ -3105,26 +3112,26 @@
         <v>1</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="3" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="4"/>
@@ -3136,10 +3143,10 @@
     <row r="33" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="5" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="3"/>
@@ -3161,26 +3168,26 @@
         <v>1</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="3" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="J34" s="2"/>
       <c r="M34" s="5">
@@ -3192,26 +3199,26 @@
         <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="3" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="4"/>
@@ -3225,26 +3232,26 @@
         <v>1</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="4"/>
@@ -3258,10 +3265,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="D37" s="2"/>
       <c r="J37" s="2"/>
@@ -3276,26 +3283,26 @@
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="3" t="s">
-        <v>180</v>
+        <v>462</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>181</v>
+        <v>463</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>182</v>
+        <v>464</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>184</v>
+        <v>465</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="4"/>
@@ -3304,29 +3311,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>1</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="3" t="s">
-        <v>185</v>
+        <v>466</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G39" s="3"/>
+        <v>470</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>469</v>
+      </c>
       <c r="H39" s="3" t="s">
-        <v>187</v>
+        <v>468</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>188</v>
+        <v>467</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="4"/>
@@ -3338,10 +3347,10 @@
     <row r="40" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="5" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="3"/>
@@ -3363,26 +3372,26 @@
         <v>1</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="3" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>190</v>
+        <v>472</v>
       </c>
       <c r="J41" s="2"/>
       <c r="M41" s="5">
@@ -3394,26 +3403,26 @@
         <v>1</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="3" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="4"/>
@@ -3425,10 +3434,10 @@
     <row r="43" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="5" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="3"/>
@@ -3450,26 +3459,26 @@
         <v>1</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="3" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="J44" s="2"/>
       <c r="M44" s="5">
@@ -3481,26 +3490,26 @@
         <v>1</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="3" t="s">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="4"/>
@@ -3512,10 +3521,10 @@
     <row r="46" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="5" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="3"/>
@@ -3537,14 +3546,14 @@
         <v>1</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="3" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -3560,26 +3569,26 @@
         <v>1</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="3" t="s">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="4"/>
@@ -3593,26 +3602,26 @@
         <v>1</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="3" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="4"/>
@@ -3633,19 +3642,19 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="3" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="4" t="s">
@@ -3670,19 +3679,19 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="3" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="4" t="s">
@@ -3705,19 +3714,19 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="3" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="4" t="s">
@@ -3742,19 +3751,19 @@
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="4" t="s">
@@ -3779,13 +3788,13 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="3" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -3812,19 +3821,19 @@
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="4" t="s">
@@ -3847,19 +3856,19 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="3" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="4" t="s">
@@ -3884,16 +3893,16 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="3" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
@@ -3919,16 +3928,16 @@
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="3" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="2"/>
@@ -3952,10 +3961,10 @@
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="3" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
@@ -3983,19 +3992,19 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="3" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="J60" s="10"/>
       <c r="K60" s="4" t="s">
@@ -4020,19 +4029,19 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="3" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="J61" s="10"/>
       <c r="K61" s="4" t="s">
@@ -4057,19 +4066,19 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="3" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="4" t="s">
@@ -4092,19 +4101,19 @@
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="3" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="J63" s="10"/>
       <c r="K63" s="4" t="s">
@@ -4129,17 +4138,17 @@
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="3" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="J64" s="10"/>
       <c r="K64" s="4" t="s">
@@ -4164,19 +4173,19 @@
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="J65" s="10"/>
       <c r="K65" s="4" t="s">
@@ -4201,19 +4210,19 @@
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="3" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>95</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="J66" s="10"/>
       <c r="K66" s="4" t="s">
@@ -4238,15 +4247,15 @@
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="4" t="s">
@@ -4269,19 +4278,19 @@
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="3" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="J68" s="10"/>
       <c r="K68" s="4" t="s">
@@ -4306,16 +4315,16 @@
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="3" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>96</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>95</v>
@@ -4343,19 +4352,19 @@
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="3" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="J70" s="10"/>
       <c r="K70" s="9" t="s">
@@ -4381,14 +4390,14 @@
       <c r="D71" s="2"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="J71" s="10"/>
       <c r="K71" s="9" t="s">
@@ -4413,19 +4422,19 @@
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="9" t="s">
@@ -4448,19 +4457,19 @@
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="3" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="J73" s="10"/>
       <c r="K73" s="9" t="s">
@@ -4485,19 +4494,19 @@
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="3" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="J74" s="10"/>
       <c r="K74" s="9" t="s">
@@ -4522,17 +4531,17 @@
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="3" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="9" t="s">
@@ -4555,19 +4564,19 @@
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="3" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="J76" s="10"/>
       <c r="K76" s="9" t="s">
@@ -4592,17 +4601,17 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="3" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="J77" s="10"/>
       <c r="K77" s="9" t="s">
@@ -4627,19 +4636,19 @@
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="3" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="J78" s="10"/>
       <c r="K78" s="9" t="s">
@@ -4664,19 +4673,19 @@
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="3" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="9" t="s">
@@ -4699,19 +4708,19 @@
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="3" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="J80" s="10"/>
       <c r="K80" s="9" t="s">
@@ -4736,17 +4745,17 @@
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="3" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="J81" s="10"/>
       <c r="K81" s="9" t="s">
@@ -4771,19 +4780,19 @@
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="3" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="9" t="s">
@@ -4806,19 +4815,19 @@
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="3" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="J83" s="10"/>
       <c r="K83" s="9" t="s">
@@ -4843,19 +4852,19 @@
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="3" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="J84" s="10"/>
       <c r="K84" s="9" t="s">
@@ -4880,17 +4889,17 @@
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="3" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="3" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="J85" s="3"/>
       <c r="K85" s="9" t="s">
@@ -4915,19 +4924,19 @@
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="3" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="J86" s="3"/>
       <c r="K86" s="9" t="s">
@@ -4952,19 +4961,19 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="3" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="J87" s="3"/>
       <c r="K87" s="9" t="s">
@@ -4989,19 +4998,19 @@
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="3" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="J88" s="3"/>
       <c r="K88" s="9" t="s">

--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDD56B1-33DC-4BE7-B6D2-2471A68DDB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE120AA0-D392-419E-B670-20DC4F5B7E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="503">
   <si>
     <t>Option 1</t>
   </si>
@@ -1305,105 +1305,15 @@
     <t>E : $50\%$.</t>
   </si>
   <si>
-    <t>Q61 : Soient $a,b \in ]0,\pi[$, alors la forme exponentiel de $z = \frac{e^{ia} + e^{ib}}{e^{ia} - e^{ib}}$ est:</t>
-  </si>
-  <si>
-    <t>Q62 : Les nombres complexes $(1+i)^n + (1-i)^n$ et $(1+i)^n - (1-i)^n$ sont conjugué l’un à l’autre pour $n$ égale :</t>
-  </si>
-  <si>
-    <t>Q63 : On a pour $n \in \mathbb{N}^*$, $\lim_{x \to 0} \frac{\cos(nx) - e^x}{x}$ est égale à :</t>
-  </si>
-  <si>
-    <t>Q64 : Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour $\ln(3x)&gt;\ln(2-5x)$ est:</t>
-  </si>
-  <si>
-    <t>Q65 : L’ensemble des solutions de l’inéquation $(x - 0,5)^{\ln(x)} \leq 0,98$ est:</t>
-  </si>
-  <si>
-    <t>Q66 : La primitive $F$ de la fonction $f$ définie sur l’intervalle $I=]0,+\infty[$ par $f(x) = x^2 \ln(x) + x - 1$, telle que : $F(1)=1$ vérifier :</t>
-  </si>
-  <si>
-    <t>Q67 : Soit $(v_n)_{n \in \mathbb{N}^*}$ la suite définie par $v_n = \ln(\frac{n+2}{n})$, alors la somme : $v_1 + v_2 + \dots + v_{n-1}$ est égale à :</t>
-  </si>
-  <si>
-    <t>Q68 : On a pour $n \in \mathbb{N}^*$, $x \in \mathbb{R}$, $\lim_{x \to +\infty} (\frac{x+\ln(x)}{x-\ln(x)})^x$ est égale à :</t>
-  </si>
-  <si>
-    <t>Q69 : Soit $z$ un nombre complexe non nul et diffèrent de 1, on définit pour tout entier naturel n , la suite $(Z_n)$ de nombre complexe par : $Z_{n+1} - Z_n = z^n$ et $Z_0 = 1$ , alors l’égalité correct est :</t>
-  </si>
-  <si>
-    <t>Q70 : Si $(\forall x \in \mathbb{R})$, $f(x)=(\sqrt{x^2 - x}).(\sqrt{x^2 + x}).(x + 1).(x - 1)$, alors $f'(1)$ est égale à :</t>
-  </si>
-  <si>
-    <t>Q71 : Soit $f$ définit par : $f(x)= \frac{1}{x \ln(x) \ln(\ln(x))}$, la primitive de $f$ sur $]e,+\infty[$ est :</t>
-  </si>
-  <si>
-    <t>Q72 : Le domaine de définition de la fontion f définie par : $f(x)= \frac{\ln(\ln(\ln(x)))}{x - e^\pi}$ est :</t>
-  </si>
-  <si>
-    <t>Q73 : L’intégrale $\int_{e^\pi}^{1} \sin(\ln(x)) dx$ égale :</t>
-  </si>
-  <si>
-    <t>Q74 : L’intégrale $\int_{0}^{1/2} \frac{1}{e^{2x}+1} dx$ égale :</t>
-  </si>
-  <si>
-    <t>Q75 : Le plan complexe est rapporté à un repère orthonormal $(o, \vec{u}, \vec{v})$. L’ensemble des points M d’affixe $Z$ tel que : $Z = \frac{\bar{z}+1}{z-1}$ est réel est :</t>
-  </si>
-  <si>
-    <t>Q76 : si $Z=\frac{1-e^{2i\theta}}{1-e^{i\theta}}$ où $\theta \in ]0, \pi[$ alors $|Z|$ égale à :</t>
-  </si>
-  <si>
-    <t>Q77 : Le nombre complexe $(\frac{1}{2} + \frac{i\sqrt{3}}{2})^{13}$ égale :</t>
-  </si>
-  <si>
-    <t>Q78 : Soit $f$ la fonction définit sur $\mathbb{R}$, la droite $x=a$ est la droite de symétrie tel que :</t>
-  </si>
-  <si>
-    <t>Q79 : Soit $f^{-1}$ la fonction reciproque de $f$ définit sur $]\ln(4),+\infty[$, par : $x \mapsto \ln(e^{2x} - 4e^x)$ , alors $f^{-1}(\ln(5))$ égale :</t>
-  </si>
-  <si>
-    <t>Q80 : Soit $(v_n)$ la suite définit par : $v_{n+1} = \ln(\frac{u_{n+1}}{9}) = \frac{1}{2}v_n$ et $u_0 = 9e$, pour tout entier naturel n. Alors la limite de $u_n$ vaut :</t>
-  </si>
-  <si>
-    <t>A : $i \cot(\frac{a-b}{2}) e^{i \frac{a+b}{2}}$.</t>
-  </si>
-  <si>
-    <t>B : $2i \cos(\frac{a+b}{2}) e^{i \frac{a+b}{2}}$.</t>
-  </si>
-  <si>
-    <t>C : $2i \sin(\frac{a-b}{2}) e^{i \frac{a+b}{2}}$.</t>
-  </si>
-  <si>
-    <t>D : $2 \cos(\frac{a+b}{2}) e^{i \frac{a+b}{2}}$.</t>
-  </si>
-  <si>
     <t>E : $2 \sin(\frac{a-b}{2}) e^{i \frac{a+b}{2}}$.</t>
   </si>
   <si>
-    <t>A : $n$.</t>
-  </si>
-  <si>
-    <t>B : $\frac{n+1}{2}$.</t>
-  </si>
-  <si>
     <t>C : $0$.</t>
   </si>
   <si>
-    <t>E : aucune valeur de $n$.</t>
-  </si>
-  <si>
-    <t>A : $-1$.</t>
-  </si>
-  <si>
     <t>B : $1$.</t>
   </si>
   <si>
-    <t>C : $n.e$.</t>
-  </si>
-  <si>
-    <t>E : $0$.</t>
-  </si>
-  <si>
     <t>A : $]-\infty, \frac{1}{4}[$.</t>
   </si>
   <si>
@@ -1431,33 +1341,12 @@
     <t>D : $[\frac{\ln(0,98)}{\ln(0,5)}, +\infty[$.</t>
   </si>
   <si>
-    <t>A : $\frac{x^3 \ln(x)}{3} + \dots$.</t>
-  </si>
-  <si>
-    <t>B : $\dots$.</t>
-  </si>
-  <si>
-    <t>C : $\dots$.</t>
-  </si>
-  <si>
-    <t>D : $\dots$.</t>
-  </si>
-  <si>
-    <t>E : $\dots$.</t>
-  </si>
-  <si>
     <t>A : $\ln(n)$.</t>
   </si>
   <si>
-    <t>B : $\ln(\frac{n(n+1)}{2})$.</t>
-  </si>
-  <si>
     <t>C : $\ln(n-2)$.</t>
   </si>
   <si>
-    <t>D : $\ln(\frac{n+1}{2})$.</t>
-  </si>
-  <si>
     <t>E : $\ln(n+2)$.</t>
   </si>
   <si>
@@ -1473,60 +1362,15 @@
     <t>E : $+\infty$.</t>
   </si>
   <si>
-    <t>A : $Z_1 = z$.</t>
-  </si>
-  <si>
-    <t>B : $Z_3 - Z_2 = \bar{z}^2$.</t>
-  </si>
-  <si>
-    <t>C : $Z_2 = (\bar{z} + 1)z$.</t>
-  </si>
-  <si>
-    <t>D : $Z_2 + 1 = (\bar{z} + 2)z$.</t>
-  </si>
-  <si>
-    <t>E : $Z_3 = (z^2 + z + 1)z$.</t>
-  </si>
-  <si>
-    <t>A : $1$.</t>
-  </si>
-  <si>
-    <t>B : $e-1$.</t>
-  </si>
-  <si>
-    <t>C : $\frac{\sqrt{4 - 1}}{2}$.</t>
-  </si>
-  <si>
     <t>D : $0$.</t>
   </si>
   <si>
-    <t>E : $\frac{\sqrt{2 - 1}}{2}$.</t>
-  </si>
-  <si>
-    <t>A : $\ln(\ln(\ln(x)))+3$.</t>
-  </si>
-  <si>
-    <t>B : $\ln(\ln(\ln(x)))+3$.</t>
-  </si>
-  <si>
-    <t>C : $\ln(\ln(\ln(\ln(x))))+3$.</t>
-  </si>
-  <si>
-    <t>D : $\ln(\ln(x))+3$.</t>
-  </si>
-  <si>
-    <t>E : $\ln(\ln(x)+3)$.</t>
-  </si>
-  <si>
     <t>A : $]e, e^\pi[$.</t>
   </si>
   <si>
     <t>B : $]-\infty, e[ \cup ]e, e^\pi[ \cup ]e^\pi, +\infty[$.</t>
   </si>
   <si>
-    <t>C : $]1, e[ \cup ]e, +\infty[$.</t>
-  </si>
-  <si>
     <t>D : $]-\infty, e[ \cup ]e, e^\pi[$.</t>
   </si>
   <si>
@@ -1642,6 +1486,168 @@
   </si>
   <si>
     <t>C : $\frac{1}{e}$.</t>
+  </si>
+  <si>
+    <t>Soient $a,b \in ]0,\pi[$, alors la forme exponentiel de $z = e^{ia} + e^{ib}$ est:</t>
+  </si>
+  <si>
+    <t>B : $2 \cos(\frac{a+b}{2}) e^{i \frac{a+b}{2}}$.</t>
+  </si>
+  <si>
+    <t>D : $2 \sin(\frac{a+b}{2}) e^{i \frac{a+b}{2}}$.</t>
+  </si>
+  <si>
+    <t>C : $2i \cos(\frac{a-b}{2}) e^{i \frac{a+b}{2}}$.</t>
+  </si>
+  <si>
+    <t>A : $ \cot(\frac{a-b}{2}) e^{i(a+b)}$.</t>
+  </si>
+  <si>
+    <t>Les nombres complexes $sin(\teta) + i cos(2.\teta)$ et $cos(\teta) - i sin(2.\teta) sont conjugués l’un à l’autre pour $\teta$ égale à :</t>
+  </si>
+  <si>
+    <t>A : $n\pi$.</t>
+  </si>
+  <si>
+    <t>B : $(n + \frac{1}{2})\pi$.</t>
+  </si>
+  <si>
+    <t>E : aucune valeur de $\teta$.</t>
+  </si>
+  <si>
+    <t>On a pour $n \in \mathbb{N}^*$, $\lim_{x \to e} \frac{\ln(x^n) - n}{x - e}$ est égale à :</t>
+  </si>
+  <si>
+    <t>A : $\frac{n}{e}$</t>
+  </si>
+  <si>
+    <t>B : $\frac{e}{n}$</t>
+  </si>
+  <si>
+    <t>C : $n.e$</t>
+  </si>
+  <si>
+    <t>D : $1$</t>
+  </si>
+  <si>
+    <t>E : $0$</t>
+  </si>
+  <si>
+    <t>Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour $$\ln(3x)&gt;\ln(2-5x)$$ est:</t>
+  </si>
+  <si>
+    <t>L’ensemble des solutions de l’inéquation $(1 - 0.02)^{x} \leq 0,5$ est:</t>
+  </si>
+  <si>
+    <t>La primitive $F$ de la fonction $f$ définie sur l’intervalle $I=]0,+\infty[$ par $f(x) = \frac{2x^3 + 3 - x}{x}, telle que : $F(1)=1$ vérifiée est :</t>
+  </si>
+  <si>
+    <t>A : $\frac{x^2 - 1 +3 \ln(x)}{3} $</t>
+  </si>
+  <si>
+    <t>C : $\frac{x^3 - x + 3 \ln(x)}{3} $</t>
+  </si>
+  <si>
+    <t>B : $\frac{2x^3 - 3x + 9 \ln(x) + 4}{3} $</t>
+  </si>
+  <si>
+    <t>D : $\frac{3x^2 - x + \ln(x) + 4}{3} $</t>
+  </si>
+  <si>
+    <t>B : $\frac{2x^3 - x + \ln(x) + 1}{3} $</t>
+  </si>
+  <si>
+    <t>Soit $(v_n)_{n \in \mathbb{N}^*}$ la suite définie par $v_n = \ln(\frac{n}{n+1})$, alors la somme : $v_2 + v_3 + \dots + v_{n-1}$ est égale à :</t>
+  </si>
+  <si>
+    <t>B : $\ln(\frac{n}{2})$.</t>
+  </si>
+  <si>
+    <t>D : $\ln(\frac{2}{n})$.</t>
+  </si>
+  <si>
+    <t>On a pour $n \in \mathbb{N}^*$, $x \in \mathbb{R}$, $\lim_{x \to +\infty} (\frac{\ln(nx)}{e^{nx})^2$ est égale à :</t>
+  </si>
+  <si>
+    <t>Soit $\lambda$ un nombre complexe non nul et diffèrent de 1, on définit pour tout entier naturel n , la suite $(Z_n)$ de nombre complexe par : $Z_{n+1} - \lambda Z_n = i$ et $Z_0 = 0$ , alors l’égalité correcte est :</t>
+  </si>
+  <si>
+    <t>A : $Z_1 = i$.</t>
+  </si>
+  <si>
+    <t>B : $\bar(Z_3 - Z_2) = \bar{\lambda}^2 i$.</t>
+  </si>
+  <si>
+    <t>C : $Z_2 = (\bar{\lambda} + 1)i$.</t>
+  </si>
+  <si>
+    <t>D : $\bar(Z_2 + Z_1) = (\bar{\lambda} + 2)i$.</t>
+  </si>
+  <si>
+    <t>E : $Z_3 = (\lambda^2 + \lambda + 1)i$.</t>
+  </si>
+  <si>
+    <t>Si $(\forall x \in \mathbb{R})$, $f(x)=(e^\sqrt{x} - 1).(\sqrt{x} + e^x).(e^{2x} + 1).(x - 1)$, alors $f'(1)$ est égale à :</t>
+  </si>
+  <si>
+    <t>C : $e^4 - 1$</t>
+  </si>
+  <si>
+    <t>B : $e-1$</t>
+  </si>
+  <si>
+    <t>A : $1$</t>
+  </si>
+  <si>
+    <t>E : $e^2 - 1$</t>
+  </si>
+  <si>
+    <t>A : $\ln(\ln(\ln(x) + 3))$</t>
+  </si>
+  <si>
+    <t>B : $\ln(\ln(\ln(x))+3)$</t>
+  </si>
+  <si>
+    <t>C : $\ln(\ln(\ln(\ln(x))))+3$</t>
+  </si>
+  <si>
+    <t>E : $\ln(\ln(x)+3)$</t>
+  </si>
+  <si>
+    <t>D : $\ln(\ln(x))+3$</t>
+  </si>
+  <si>
+    <t>Soit $f$ définit par : $f(x)= \frac{1}{x \ln(x) \ln(\ln(x))}$, la primitive de $f$ sur $]e,+\infty[$ est :</t>
+  </si>
+  <si>
+    <t>Le domaine de définition de la fontion f définie par : $f(x)= \frac{\ln(\ln(\ln(x)))}{x - e^\pi}$ est :</t>
+  </si>
+  <si>
+    <t>C : $]1, e^pi[ \cup ]e^pi, +\infty[$.</t>
+  </si>
+  <si>
+    <t>L’intégrale $\int_{e^\pi}^{1} \sin(\ln(x)) dx$ égale :</t>
+  </si>
+  <si>
+    <t>L’intégrale $\int_{0}^{1/2} \frac{1}{e^{2x}+1} dx$ égale :</t>
+  </si>
+  <si>
+    <t>Le plan complexe est rapporté à un repère orthonormal $(o, \vec{u}, \vec{v})$. L’ensemble des points M d’affixe $Z$ tel que : $Z = \frac{\bar{z}+1}{z-1}$ est réel est :</t>
+  </si>
+  <si>
+    <t>si $Z=\frac{1-e^{2i\theta}}{1-e^{i\theta}}$ où $\theta \in ]0, \pi[$ alors $|Z|$ égale à :</t>
+  </si>
+  <si>
+    <t>Le nombre complexe $(\frac{1}{2} + \frac{i\sqrt{3}}{2})^{13}$ égale :</t>
+  </si>
+  <si>
+    <t>Soit $f$ la fonction définit sur $\mathbb{R}$, la droite $x=a$ est la droite de symétrie tel que :</t>
+  </si>
+  <si>
+    <t>Soit $f^{-1}$ la fonction reciproque de $f$ définit sur $]\ln(4),+\infty[$, par : $x \mapsto \ln(e^{2x} - 4e^x)$ , alors $f^{-1}(\ln(5))$ égale :</t>
+  </si>
+  <si>
+    <t>Soit $(v_n)$ la suite définit par : $v_{n+1} = \ln(\frac{u_{n+1}}{9}) = \frac{1}{2}v_n$ et $u_0 = 9e$, pour tout entier naturel n. Alors la limite de $u_n$ vaut :</t>
   </si>
 </sst>
 </file>
@@ -4460,23 +4466,23 @@
         <v>14</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>388</v>
+        <v>449</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s">
-        <v>408</v>
+        <v>453</v>
       </c>
       <c r="F76" t="s">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="G76" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="H76" t="s">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="I76" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="4" t="s">
@@ -4489,7 +4495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>1</v>
       </c>
@@ -4497,23 +4503,23 @@
         <v>14</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>389</v>
+        <v>454</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s">
-        <v>413</v>
+        <v>455</v>
       </c>
       <c r="F77" t="s">
-        <v>414</v>
+        <v>456</v>
       </c>
       <c r="G77" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="H77" t="s">
         <v>374</v>
       </c>
       <c r="I77" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="4" t="s">
@@ -4532,23 +4538,23 @@
         <v>14</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>390</v>
+        <v>458</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s">
-        <v>417</v>
+        <v>459</v>
       </c>
       <c r="F78" t="s">
-        <v>418</v>
+        <v>460</v>
       </c>
       <c r="G78" t="s">
-        <v>419</v>
+        <v>461</v>
       </c>
       <c r="H78" t="s">
-        <v>374</v>
+        <v>462</v>
       </c>
       <c r="I78" t="s">
-        <v>420</v>
+        <v>463</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="4" t="s">
@@ -4569,23 +4575,23 @@
         <v>14</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>391</v>
+        <v>464</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="F79" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="G79" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="H79" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="I79" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="4" t="s">
@@ -4606,23 +4612,23 @@
         <v>14</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>392</v>
+        <v>465</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F80" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="G80" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="H80" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="I80" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="4" t="s">
@@ -4643,23 +4649,23 @@
         <v>14</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>393</v>
+        <v>466</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s">
-        <v>430</v>
+        <v>467</v>
       </c>
       <c r="F81" t="s">
-        <v>431</v>
+        <v>469</v>
       </c>
       <c r="G81" t="s">
-        <v>432</v>
+        <v>468</v>
       </c>
       <c r="H81" t="s">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="I81" t="s">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="4" t="s">
@@ -4678,23 +4684,23 @@
         <v>14</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>394</v>
+        <v>472</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="F82" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="G82" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="H82" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="I82" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" s="4" t="s">
@@ -4715,23 +4721,23 @@
         <v>14</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>395</v>
+        <v>475</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="F83" t="s">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="G83" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="H83" t="s">
-        <v>442</v>
+        <v>405</v>
       </c>
       <c r="I83" t="s">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" s="4" t="s">
@@ -4752,23 +4758,23 @@
         <v>14</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>396</v>
+        <v>476</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="F84" t="s">
-        <v>445</v>
+        <v>478</v>
       </c>
       <c r="G84" t="s">
-        <v>446</v>
+        <v>479</v>
       </c>
       <c r="H84" t="s">
-        <v>447</v>
+        <v>480</v>
       </c>
       <c r="I84" t="s">
-        <v>448</v>
+        <v>481</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="4" t="s">
@@ -4787,23 +4793,23 @@
         <v>14</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>397</v>
+        <v>482</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s">
-        <v>449</v>
+        <v>485</v>
       </c>
       <c r="F85" t="s">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="G85" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="H85" t="s">
-        <v>452</v>
+        <v>407</v>
       </c>
       <c r="I85" t="s">
-        <v>453</v>
+        <v>486</v>
       </c>
       <c r="J85" s="9"/>
       <c r="K85" s="4" t="s">
@@ -4824,23 +4830,23 @@
         <v>14</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>398</v>
+        <v>492</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="F86" t="s">
-        <v>455</v>
+        <v>488</v>
       </c>
       <c r="G86" t="s">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="H86" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="I86" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="J86" s="9"/>
       <c r="K86" s="4" t="s">
@@ -4861,23 +4867,23 @@
         <v>14</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>399</v>
+        <v>493</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s">
-        <v>459</v>
+        <v>408</v>
       </c>
       <c r="F87" t="s">
-        <v>460</v>
+        <v>409</v>
       </c>
       <c r="G87" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="H87" t="s">
-        <v>462</v>
+        <v>410</v>
       </c>
       <c r="I87" t="s">
-        <v>463</v>
+        <v>411</v>
       </c>
       <c r="J87" s="9"/>
       <c r="K87" s="4" t="s">
@@ -4898,23 +4904,23 @@
         <v>14</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>400</v>
+        <v>495</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s">
-        <v>464</v>
+        <v>412</v>
       </c>
       <c r="F88" t="s">
-        <v>465</v>
+        <v>413</v>
       </c>
       <c r="G88" t="s">
-        <v>466</v>
+        <v>414</v>
       </c>
       <c r="H88" t="s">
-        <v>467</v>
+        <v>415</v>
       </c>
       <c r="I88" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="4" t="s">
@@ -4933,23 +4939,23 @@
         <v>14</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>401</v>
+        <v>496</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s">
-        <v>469</v>
+        <v>417</v>
       </c>
       <c r="F89" t="s">
-        <v>470</v>
+        <v>418</v>
       </c>
       <c r="G89" t="s">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="H89" t="s">
-        <v>472</v>
+        <v>420</v>
       </c>
       <c r="I89" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J89" s="9"/>
       <c r="K89" s="4" t="s">
@@ -4970,23 +4976,23 @@
         <v>14</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>402</v>
+        <v>497</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
       <c r="F90" t="s">
-        <v>475</v>
+        <v>423</v>
       </c>
       <c r="G90" t="s">
-        <v>476</v>
+        <v>424</v>
       </c>
       <c r="H90" t="s">
-        <v>477</v>
+        <v>425</v>
       </c>
       <c r="I90" t="s">
-        <v>478</v>
+        <v>426</v>
       </c>
       <c r="J90" s="9"/>
       <c r="K90" s="4" t="s">
@@ -5007,23 +5013,23 @@
         <v>14</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>403</v>
+        <v>498</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s">
-        <v>479</v>
+        <v>427</v>
       </c>
       <c r="F91" t="s">
-        <v>480</v>
+        <v>428</v>
       </c>
       <c r="G91" t="s">
-        <v>481</v>
+        <v>429</v>
       </c>
       <c r="H91" t="s">
-        <v>482</v>
+        <v>430</v>
       </c>
       <c r="I91" t="s">
-        <v>483</v>
+        <v>431</v>
       </c>
       <c r="J91" s="9"/>
       <c r="K91" s="4" t="s">
@@ -5044,23 +5050,23 @@
         <v>14</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>404</v>
+        <v>499</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s">
-        <v>484</v>
+        <v>432</v>
       </c>
       <c r="F92" t="s">
-        <v>485</v>
+        <v>433</v>
       </c>
       <c r="G92" t="s">
-        <v>486</v>
+        <v>434</v>
       </c>
       <c r="H92" t="s">
-        <v>487</v>
+        <v>435</v>
       </c>
       <c r="I92" t="s">
-        <v>488</v>
+        <v>436</v>
       </c>
       <c r="J92" s="9"/>
       <c r="K92" s="4" t="s">
@@ -5081,23 +5087,23 @@
         <v>14</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>405</v>
+        <v>500</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s">
-        <v>489</v>
+        <v>437</v>
       </c>
       <c r="F93" t="s">
-        <v>490</v>
+        <v>438</v>
       </c>
       <c r="G93" t="s">
-        <v>491</v>
+        <v>439</v>
       </c>
       <c r="H93" t="s">
-        <v>492</v>
+        <v>440</v>
       </c>
       <c r="I93" t="s">
-        <v>493</v>
+        <v>441</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="4" t="s">
@@ -5116,23 +5122,23 @@
         <v>14</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>406</v>
+        <v>501</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="F94" t="s">
-        <v>494</v>
+        <v>442</v>
       </c>
       <c r="G94" t="s">
-        <v>495</v>
+        <v>443</v>
       </c>
       <c r="H94" t="s">
-        <v>496</v>
+        <v>444</v>
       </c>
       <c r="I94" t="s">
-        <v>497</v>
+        <v>445</v>
       </c>
       <c r="J94" s="9"/>
       <c r="K94" s="4" t="s">
@@ -5153,23 +5159,23 @@
         <v>14</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>407</v>
+        <v>502</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s">
-        <v>498</v>
+        <v>446</v>
       </c>
       <c r="F95" t="s">
-        <v>499</v>
+        <v>447</v>
       </c>
       <c r="G95" t="s">
-        <v>500</v>
+        <v>448</v>
       </c>
       <c r="H95" t="s">
-        <v>442</v>
+        <v>405</v>
       </c>
       <c r="I95" t="s">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="J95" s="9"/>
       <c r="K95" s="4" t="s">

--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE120AA0-D392-419E-B670-20DC4F5B7E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB45AA3-4396-4B99-A411-14379C0C6DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="504">
   <si>
     <t>Option 1</t>
   </si>
@@ -908,746 +908,756 @@
     <t>La date lorsque $N(C_a)(t) = \frac {7}{8} \cdot N_0$ est:</t>
   </si>
   <si>
+    <t>6,33ms</t>
+  </si>
+  <si>
+    <t>30.30 ms</t>
+  </si>
+  <si>
+    <t>16,5 ms</t>
+  </si>
+  <si>
+    <t>33,33 ms</t>
+  </si>
+  <si>
+    <t>3,67 ms</t>
+  </si>
+  <si>
+    <t>A : $(Al^{3+}/Al)$ et $(H_3O^+/H_2)$.</t>
+  </si>
+  <si>
+    <t>C : $(Al^{3+}/Al)$ et $(H_2/H_3O^+)$.</t>
+  </si>
+  <si>
+    <t>D : $(Al^{3+}/Al)$ et $(HO^-/H_2)$.</t>
+  </si>
+  <si>
+    <t>A : $9mg$ .</t>
+  </si>
+  <si>
+    <t>B : $16mg$.</t>
+  </si>
+  <si>
+    <t>C : $11mg$.</t>
+  </si>
+  <si>
+    <t>D : $12mg$.</t>
+  </si>
+  <si>
+    <t>E : $13mg$.</t>
+  </si>
+  <si>
+    <t>E : $-18,5.10^{-3} mol.L^{-1}.s^{-1}$.</t>
+  </si>
+  <si>
+    <t>A : $V_{be}$.</t>
+  </si>
+  <si>
+    <t>B : $V_{be}/2$.</t>
+  </si>
+  <si>
+    <t>C : $2.V_{be}$.</t>
+  </si>
+  <si>
+    <t>D : $V_{be}/3$.</t>
+  </si>
+  <si>
+    <t>E : $3.V_{be}$.</t>
+  </si>
+  <si>
+    <t>A : $1,22 mg$.</t>
+  </si>
+  <si>
+    <t>B : $122 mg$.</t>
+  </si>
+  <si>
+    <t>C : $12,2 mg$.</t>
+  </si>
+  <si>
+    <t>D : $12,2 g$.</t>
+  </si>
+  <si>
+    <t>E : $1,22 g$.</t>
+  </si>
+  <si>
+    <t>A : $4,1$.</t>
+  </si>
+  <si>
+    <t>B : $4,3$.</t>
+  </si>
+  <si>
+    <t>C : $4,4$.</t>
+  </si>
+  <si>
+    <t>D : $4,2$.</t>
+  </si>
+  <si>
+    <t>E : $4$.</t>
+  </si>
+  <si>
+    <t>A : $\frac{1}{10^{-pK_{a1}}-10^{-pK_{a2}}}$.</t>
+  </si>
+  <si>
+    <t>B : $\frac{1}{1+10^{\frac{pK_{a2}-pK_{a1}}{2}}}$.</t>
+  </si>
+  <si>
+    <t>C : $\frac{1}{10^{-pK_{a1}}+10^{-pK_{a2}}}$.</t>
+  </si>
+  <si>
+    <t>D : $\frac{1}{1+10^{\frac{pK_{a1}-pK_{a2}}{2}}}$.</t>
+  </si>
+  <si>
+    <t>A : $0\%$.</t>
+  </si>
+  <si>
+    <t>B : $20\%$.</t>
+  </si>
+  <si>
+    <t>C : $30\%$.</t>
+  </si>
+  <si>
+    <t>D : $50\%$.</t>
+  </si>
+  <si>
+    <t>E : $100\%$.</t>
+  </si>
+  <si>
+    <t>A : $7$.</t>
+  </si>
+  <si>
+    <t>B : $2,2$.</t>
+  </si>
+  <si>
+    <t>D : $1$.</t>
+  </si>
+  <si>
+    <t>E : $14$.</t>
+  </si>
+  <si>
+    <t>A : $20\%$.</t>
+  </si>
+  <si>
+    <t>B : $10\%$.</t>
+  </si>
+  <si>
+    <t>D : $40\%$.</t>
+  </si>
+  <si>
+    <t>E : $50\%$.</t>
+  </si>
+  <si>
+    <t>E : $2 \sin(\frac{a-b}{2}) e^{i \frac{a+b}{2}}$.</t>
+  </si>
+  <si>
+    <t>C : $0$.</t>
+  </si>
+  <si>
+    <t>B : $1$.</t>
+  </si>
+  <si>
+    <t>A : $]-\infty, \frac{1}{4}[$.</t>
+  </si>
+  <si>
+    <t>B : $]\frac{1}{4}, \frac{2}{5}[$.</t>
+  </si>
+  <si>
+    <t>C : $]\frac{1}{4}, +\infty[$.</t>
+  </si>
+  <si>
+    <t>D : $]0, \frac{1}{4}[$.</t>
+  </si>
+  <si>
+    <t>E : $\emptyset$.</t>
+  </si>
+  <si>
+    <t>A : $]-\infty, \frac{\ln(0,5)}{\ln(0,98)}]$.</t>
+  </si>
+  <si>
+    <t>B : $]-\infty, \frac{\ln(0,98)}{\ln(0,5)}]$.</t>
+  </si>
+  <si>
+    <t>C : $[\frac{\ln(0,5)}{\ln(0,98)}, +\infty[$.</t>
+  </si>
+  <si>
+    <t>D : $[\frac{\ln(0,98)}{\ln(0,5)}, +\infty[$.</t>
+  </si>
+  <si>
+    <t>A : $\ln(n)$.</t>
+  </si>
+  <si>
+    <t>C : $\ln(n-2)$.</t>
+  </si>
+  <si>
+    <t>E : $\ln(n+2)$.</t>
+  </si>
+  <si>
+    <t>A : $0$.</t>
+  </si>
+  <si>
+    <t>C : $n$.</t>
+  </si>
+  <si>
+    <t>D : $e$.</t>
+  </si>
+  <si>
+    <t>E : $+\infty$.</t>
+  </si>
+  <si>
+    <t>D : $0$.</t>
+  </si>
+  <si>
+    <t>A : $]e, e^\pi[$.</t>
+  </si>
+  <si>
+    <t>B : $]-\infty, e[ \cup ]e, e^\pi[ \cup ]e^\pi, +\infty[$.</t>
+  </si>
+  <si>
+    <t>D : $]-\infty, e[ \cup ]e, e^\pi[$.</t>
+  </si>
+  <si>
+    <t>E : $]e, e^\pi[ \cup ]e^\pi, +\infty[$.</t>
+  </si>
+  <si>
+    <t>A : $\frac{e^\pi+1}{2}$.</t>
+  </si>
+  <si>
+    <t>B : $\frac{e^\pi-1}{2}$.</t>
+  </si>
+  <si>
+    <t>C : $\frac{1}{2}$.</t>
+  </si>
+  <si>
+    <t>D : $\frac{e}{2}$.</t>
+  </si>
+  <si>
+    <t>E : $\frac{1-e^\pi}{2}$.</t>
+  </si>
+  <si>
+    <t>A : $\ln[\frac{2\sqrt{e}}{e+1}]$.</t>
+  </si>
+  <si>
+    <t>B : $\ln(e) + \ln(e+1)$.</t>
+  </si>
+  <si>
+    <t>C : $\frac{1}{2} + \ln(e+1)$.</t>
+  </si>
+  <si>
+    <t>D : $\ln[\frac{e+1}{2\sqrt{e}}]$.</t>
+  </si>
+  <si>
+    <t>E : $\ln[2\sqrt{e}(e+1)]$.</t>
+  </si>
+  <si>
+    <t>A : Le cercle de centre O et de rayon 1 privé du point d’affixe 1.</t>
+  </si>
+  <si>
+    <t>B : L’axe des imaginaires purs privé du point d’affixe 1.</t>
+  </si>
+  <si>
+    <t>C : L’axe des réels privé du point d’affixe 1.</t>
+  </si>
+  <si>
+    <t>D : Le cercle de centre M et de rayon 1 privé du point d’affixe 1.</t>
+  </si>
+  <si>
+    <t>E : On ne peut rien en dire.</t>
+  </si>
+  <si>
+    <t>A : $2\cos(\frac{\theta}{2})$.</t>
+  </si>
+  <si>
+    <t>B : $2\sin(\frac{\theta}{2})$.</t>
+  </si>
+  <si>
+    <t>C : $\tan(\frac{\theta}{2})$.</t>
+  </si>
+  <si>
+    <t>D : $\cos(\theta)$.</t>
+  </si>
+  <si>
+    <t>E : $1$.</t>
+  </si>
+  <si>
+    <t>A : $(\frac{1}{2} + \frac{i\sqrt{3}}{2})$.</t>
+  </si>
+  <si>
+    <t>B : $(\frac{1}{2} - \frac{i\sqrt{3}}{2})$.</t>
+  </si>
+  <si>
+    <t>C : $i$.</t>
+  </si>
+  <si>
+    <t>D : $-1$.</t>
+  </si>
+  <si>
+    <t>E : $-i$.</t>
+  </si>
+  <si>
+    <t>A : $f(x)=f(2a-x)$.</t>
+  </si>
+  <si>
+    <t>B : $f(x)=f(2a+x)$.</t>
+  </si>
+  <si>
+    <t>C : $f(x)=f(x-a)$.</t>
+  </si>
+  <si>
+    <t>D : $f(x)=-f(x-2a)$.</t>
+  </si>
+  <si>
+    <t>E : $f(x)=f(x+a)$.</t>
+  </si>
+  <si>
+    <t>B : $\frac{1}{6}$.</t>
+  </si>
+  <si>
+    <t>C : $-\frac{1}{6}$.</t>
+  </si>
+  <si>
+    <t>D : $\ln(5)$.</t>
+  </si>
+  <si>
+    <t>E : $-\ln(5)$.</t>
+  </si>
+  <si>
+    <t>A : $9$.</t>
+  </si>
+  <si>
+    <t>B : $\frac{1}{9}$.</t>
+  </si>
+  <si>
+    <t>C : $\frac{1}{e}$.</t>
+  </si>
+  <si>
+    <t>Soient $a,b \in ]0,\pi[$, alors la forme exponentiel de $z = e^{ia} + e^{ib}$ est:</t>
+  </si>
+  <si>
+    <t>B : $2 \cos(\frac{a+b}{2}) e^{i \frac{a+b}{2}}$.</t>
+  </si>
+  <si>
+    <t>D : $2 \sin(\frac{a+b}{2}) e^{i \frac{a+b}{2}}$.</t>
+  </si>
+  <si>
+    <t>C : $2i \cos(\frac{a-b}{2}) e^{i \frac{a+b}{2}}$.</t>
+  </si>
+  <si>
+    <t>A : $ \cot(\frac{a-b}{2}) e^{i(a+b)}$.</t>
+  </si>
+  <si>
+    <t>Les nombres complexes $sin(\teta) + i cos(2.\teta)$ et $cos(\teta) - i sin(2.\teta) sont conjugués l’un à l’autre pour $\teta$ égale à :</t>
+  </si>
+  <si>
+    <t>A : $n\pi$.</t>
+  </si>
+  <si>
+    <t>B : $(n + \frac{1}{2})\pi$.</t>
+  </si>
+  <si>
+    <t>E : aucune valeur de $\teta$.</t>
+  </si>
+  <si>
+    <t>On a pour $n \in \mathbb{N}^*$, $\lim_{x \to e} \frac{\ln(x^n) - n}{x - e}$ est égale à :</t>
+  </si>
+  <si>
+    <t>A : $\frac{n}{e}$</t>
+  </si>
+  <si>
+    <t>B : $\frac{e}{n}$</t>
+  </si>
+  <si>
+    <t>C : $n.e$</t>
+  </si>
+  <si>
+    <t>D : $1$</t>
+  </si>
+  <si>
+    <t>E : $0$</t>
+  </si>
+  <si>
+    <t>Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour $$\ln(3x)&gt;\ln(2-5x)$$ est:</t>
+  </si>
+  <si>
+    <t>L’ensemble des solutions de l’inéquation $(1 - 0.02)^{x} \leq 0,5$ est:</t>
+  </si>
+  <si>
+    <t>La primitive $F$ de la fonction $f$ définie sur l’intervalle $I=]0,+\infty[$ par $f(x) = \frac{2x^3 + 3 - x}{x}, telle que : $F(1)=1$ vérifiée est :</t>
+  </si>
+  <si>
+    <t>A : $\frac{x^2 - 1 +3 \ln(x)}{3} $</t>
+  </si>
+  <si>
+    <t>C : $\frac{x^3 - x + 3 \ln(x)}{3} $</t>
+  </si>
+  <si>
+    <t>B : $\frac{2x^3 - 3x + 9 \ln(x) + 4}{3} $</t>
+  </si>
+  <si>
+    <t>D : $\frac{3x^2 - x + \ln(x) + 4}{3} $</t>
+  </si>
+  <si>
+    <t>B : $\frac{2x^3 - x + \ln(x) + 1}{3} $</t>
+  </si>
+  <si>
+    <t>Soit $(v_n)_{n \in \mathbb{N}^*}$ la suite définie par $v_n = \ln(\frac{n}{n+1})$, alors la somme : $v_2 + v_3 + \dots + v_{n-1}$ est égale à :</t>
+  </si>
+  <si>
+    <t>B : $\ln(\frac{n}{2})$.</t>
+  </si>
+  <si>
+    <t>D : $\ln(\frac{2}{n})$.</t>
+  </si>
+  <si>
+    <t>On a pour $n \in \mathbb{N}^*$, $x \in \mathbb{R}$, $\lim_{x \to +\infty} (\frac{\ln(nx)}{e^{nx})^2$ est égale à :</t>
+  </si>
+  <si>
+    <t>Soit $\lambda$ un nombre complexe non nul et diffèrent de 1, on définit pour tout entier naturel n , la suite $(Z_n)$ de nombre complexe par : $Z_{n+1} - \lambda Z_n = i$ et $Z_0 = 0$ , alors l’égalité correcte est :</t>
+  </si>
+  <si>
+    <t>A : $Z_1 = i$.</t>
+  </si>
+  <si>
+    <t>B : $\bar(Z_3 - Z_2) = \bar{\lambda}^2 i$.</t>
+  </si>
+  <si>
+    <t>C : $Z_2 = (\bar{\lambda} + 1)i$.</t>
+  </si>
+  <si>
+    <t>D : $\bar(Z_2 + Z_1) = (\bar{\lambda} + 2)i$.</t>
+  </si>
+  <si>
+    <t>E : $Z_3 = (\lambda^2 + \lambda + 1)i$.</t>
+  </si>
+  <si>
+    <t>Si $(\forall x \in \mathbb{R})$, $f(x)=(e^\sqrt{x} - 1).(\sqrt{x} + e^x).(e^{2x} + 1).(x - 1)$, alors $f'(1)$ est égale à :</t>
+  </si>
+  <si>
+    <t>C : $e^4 - 1$</t>
+  </si>
+  <si>
+    <t>B : $e-1$</t>
+  </si>
+  <si>
+    <t>A : $1$</t>
+  </si>
+  <si>
+    <t>E : $e^2 - 1$</t>
+  </si>
+  <si>
+    <t>A : $\ln(\ln(\ln(x) + 3))$</t>
+  </si>
+  <si>
+    <t>B : $\ln(\ln(\ln(x))+3)$</t>
+  </si>
+  <si>
+    <t>C : $\ln(\ln(\ln(\ln(x))))+3$</t>
+  </si>
+  <si>
+    <t>E : $\ln(\ln(x)+3)$</t>
+  </si>
+  <si>
+    <t>D : $\ln(\ln(x))+3$</t>
+  </si>
+  <si>
+    <t>Soit $f$ définit par : $f(x)= \frac{1}{x \ln(x) \ln(\ln(x))}$, la primitive de $f$ sur $]e,+\infty[$ est :</t>
+  </si>
+  <si>
+    <t>Le domaine de définition de la fontion f définie par : $f(x)= \frac{\ln(\ln(\ln(x)))}{x - e^\pi}$ est :</t>
+  </si>
+  <si>
+    <t>C : $]1, e^pi[ \cup ]e^pi, +\infty[$.</t>
+  </si>
+  <si>
+    <t>L’intégrale $\int_{e^\pi}^{1} \sin(\ln(x)) dx$ égale :</t>
+  </si>
+  <si>
+    <t>L’intégrale $\int_{0}^{1/2} \frac{1}{e^{2x}+1} dx$ égale :</t>
+  </si>
+  <si>
+    <t>Le plan complexe est rapporté à un repère orthonormal $(o, \vec{u}, \vec{v})$. L’ensemble des points M d’affixe $Z$ tel que : $Z = \frac{\bar{z}+1}{z-1}$ est réel est :</t>
+  </si>
+  <si>
+    <t>si $Z=\frac{1-e^{2i\theta}}{1-e^{i\theta}}$ où $\theta \in ]0, \pi[$ alors $|Z|$ égale à :</t>
+  </si>
+  <si>
+    <t>Le nombre complexe $(\frac{1}{2} + \frac{i\sqrt{3}}{2})^{13}$ égale :</t>
+  </si>
+  <si>
+    <t>Soit $f$ la fonction définit sur $\mathbb{R}$, la droite $x=a$ est la droite de symétrie tel que :</t>
+  </si>
+  <si>
+    <t>Soit $f^{-1}$ la fonction reciproque de $f$ définit sur $]\ln(4),+\infty[$, par : $x \mapsto \ln(e^{2x} - 4e^x)$ , alors $f^{-1}(\ln(5))$ égale :</t>
+  </si>
+  <si>
+    <t>Soit $(v_n)$ la suite définit par : $v_{n+1} = \ln(\frac{u_{n+1}}{9}) = \frac{1}{2}v_n$ et $u_0 = 9e$, pour tout entier naturel n. Alors la limite de $u_n$ vaut :</t>
+  </si>
+  <si>
     <t>&lt;b&gt;Exercice 6 &lt;/b&gt; : $\quad$ L’activité du radon 222 &lt;br&gt;
-Un noyau radioactif de radon $$^{222}_{86}\text{Rn}$$ se désintègre en émettant une particule $\alpha$ et noyau fils  $$^{218}_{84}\text{Po}$$. 
+Un noyau radioactif de radon $^{222}_{86}\text{Rn}$ se désintègre en émettant une particule $\alpha$ et noyau fils  $$^{218}_{84}\text{Po}$$. 
 La figure ci-dessous représente les variations de la fonction Y(t) tel que : $Y(t) = N_{Pₒ}(t) − N_{Rn}(t)$.
 &lt;br&gt;&lt;img src="/images/CB1_Q14.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;On donne :   $5,8.10^{-4} = \frac{50}{3600  .  24}$ $\quad$ In(2) = 0,7 $\quad$ et $\quad$ 0,18 . 5,8 = 1,044</t>
   </si>
   <si>
-    <t>6,33ms</t>
-  </si>
-  <si>
-    <t>30.30 ms</t>
-  </si>
-  <si>
-    <t>16,5 ms</t>
-  </si>
-  <si>
-    <t>33,33 ms</t>
-  </si>
-  <si>
-    <t>3,67 ms</t>
-  </si>
-  <si>
-    <t>Exercice 1 : Suivi temporel d’une transformation chimique
+    <t>B : $(Al^{3+}/Al)$ et $(H_3O^+/H_2)$.</t>
+  </si>
+  <si>
+    <t>E : $(Al/Al^{3+})$ et $(H_2/H_{2O})$.</t>
+  </si>
+  <si>
+    <t>A : $-18,5.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
+  </si>
+  <si>
+    <t>B : $18,5.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
+  </si>
+  <si>
+    <t>C : $-9,25.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
+  </si>
+  <si>
+    <t>D : $9,25.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
+  </si>
+  <si>
+    <t>Les couples (Ox/Red) participant à cette réaction sont :</t>
+  </si>
+  <si>
+    <t>La valeur de $m(Al)$ est :</t>
+  </si>
+  <si>
+    <t>La valeur de la vitesse volumique a l’instant $t=0s$ est :</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 2 : $\quad$ conductimétrie&lt;/b&gt;&lt;br&gt;
+On verse dans un bécher un volume $V = 2.10^{-4} m^3$ d’une solution $(S_B)$ d’hydroxyde de sodium de concentration molaire $C_B$ , et on y ajoute à l’instant $t=0$, considéré comme origine des temps, une quantité de matière $n_E$ du méthanoate de méthyle égale à la quantité de matière $n_B$ d’hydroxyde de sodium ($n_E=n_B$). (On considère que le volume reste constant $V$).
+&lt;br&gt;On donne : $HCOOCH_{3(aq)} + HO^-_{(aq)} \longrightarrow HCOO^-_{(aq)} + CH_3OH_{(aq)}$
+&lt;br&gt; G(t) =0,72. X(t) + 2,5.10^{-3} en (S), $\lambda_{HO^-} + \lambda_{Na^+} = 25 mS. m^2. mol^{-1}$ , $\lambda_{HO^-} - \lambda_{HCO_2^-} = 14,4 mS. m^2. mol^{-1}$</t>
+  </si>
+  <si>
+    <t>A : $H_3O^+, cl^{-1}, Na^+$</t>
+  </si>
+  <si>
+    <t>B : $HCO_2^-, H_3O^+, Na^+$</t>
+  </si>
+  <si>
+    <t>C : $HCO_2^-, cl^{-1}, Na^+$</t>
+  </si>
+  <si>
+    <t>D : $HO^-, H_3O^+, Na^+$.</t>
+  </si>
+  <si>
+    <t>E : $HCO_2^-, HO^-, Na^+$</t>
+  </si>
+  <si>
+    <t>Les ions présent dans le mélange à un instant t sont :</t>
+  </si>
+  <si>
+    <t>Sachant que $G_{max} = 1,06 mS$, la valeur de $X_{max}$ est :</t>
+  </si>
+  <si>
+    <t>A : $10^{-3} mol$</t>
+  </si>
+  <si>
+    <t>B : $3.10^{-2} mol$</t>
+  </si>
+  <si>
+    <t>C : $4.10^{-3} mol$</t>
+  </si>
+  <si>
+    <t>D : $2.10^{-3} mol$</t>
+  </si>
+  <si>
+    <t>E : $10^{-2} mol$</t>
+  </si>
+  <si>
+    <t>La valeur de $G_{t1/2}$ égale :</t>
+  </si>
+  <si>
+    <t>B : $3.10^{-2} S$</t>
+  </si>
+  <si>
+    <t>A : $10^{-3} mS$</t>
+  </si>
+  <si>
+    <t>C : $1,78 mS$</t>
+  </si>
+  <si>
+    <t>D : $1,87 mS$</t>
+  </si>
+  <si>
+    <t>E : $10^{-4} S$</t>
+  </si>
+  <si>
+    <t>La valeur de $[HCO_2CH_3]$ à $t_{1/2}$ égale :</t>
+  </si>
+  <si>
+    <t>A : $5 mol.cm^{-3}$.</t>
+  </si>
+  <si>
+    <t>B : $5 mol.mm^{-3}$.</t>
+  </si>
+  <si>
+    <t>C : $5 mmol.m^{-3}$.</t>
+  </si>
+  <si>
+    <t>D : $5 mol.L^{-1}$.</t>
+  </si>
+  <si>
+    <t>E : $5 mol.m^{-3}$.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 3 : $\quad$ Dissolution de l’ammoniac dans l’eau&lt;/b&gt;&lt;br&gt;
+&lt;br&gt;On considère une solution aqueuse $(S_b)$ d’ammoniac $NH_3$ avec taux d’avancement $\tau = 2,5\%$.
+&lt;br&gt;On donne : $\log 25 = 1,4$ , $\quad$ $\frac{975}{25} = 39$; $\quad$ $\log 39 = 1,6$</t>
+  </si>
+  <si>
+    <t>Le taux d’avancement a pour expression :</t>
+  </si>
+  <si>
+    <t>A : $\frac{10^{-pH}}{C_b. K_e}$</t>
+  </si>
+  <si>
+    <t>B : $\frac{10^{pH}}{C_b. K_e}$</t>
+  </si>
+  <si>
+    <t>C : $\frac{10^{-pH}.K_e}{C_b}$</t>
+  </si>
+  <si>
+    <t>D : $\frac{10^{pH}.K_e}{C_b}$</t>
+  </si>
+  <si>
+    <t>E : $\frac{10^{-pH}.C_b}{K_e}$</t>
+  </si>
+  <si>
+    <t>Sachant que $C_b = 2,5.10^{-2} mol.L^{-1}$, la valeur de $pH$ est :</t>
+  </si>
+  <si>
+    <t>E : $10,8$</t>
+  </si>
+  <si>
+    <t>D : $11,8$</t>
+  </si>
+  <si>
+    <t>C : $12,4$</t>
+  </si>
+  <si>
+    <t>B : $10$</t>
+  </si>
+  <si>
+    <t>A : $10,4$</t>
+  </si>
+  <si>
+    <t>La constante d’acidité $K_a$ du couple $(NH_4^+/NH_3)$ a pour expression :</t>
+  </si>
+  <si>
+    <t>A : $\frac{1-\tau}{10^{pH}.\tau}$</t>
+  </si>
+  <si>
+    <t>B : $\frac{1-\tau}{10^{-pH}.\tau}$</t>
+  </si>
+  <si>
+    <t>C : $\frac{10^{pH}.\tau}{1-\tau}$</t>
+  </si>
+  <si>
+    <t>D : $\frac{10^{-pH}.\tau}{1-\tau}$</t>
+  </si>
+  <si>
+    <t>E : $\frac{10^{-pH}.\tau}{\tau - 1}$</t>
+  </si>
+  <si>
+    <t>La valeur de $pK_a$ est :</t>
+  </si>
+  <si>
+    <t>B : $9,2$</t>
+  </si>
+  <si>
+    <t>C : $9,4$</t>
+  </si>
+  <si>
+    <t>D : $9,8$</t>
+  </si>
+  <si>
+    <t>E : $9,6$</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 4 : $\quad$ Dilution de la solution commerciale &lt;/b&gt;&lt;br&gt;
+Sur l’étiquette d’une bouteille d’acide chlorhydrique commercial, on lit les indications suivantes : « Acide chlorhydrique, masse volumique : $\rho = 1190 Kg.m^{-3}$ ; pourcentage en masse d’acide pur : $p = 37\%$ ; masse molaire de chlorure d’hydrogène HCl : $M = 36,5 g.mol^{-1}$ ». On extrait de cette bouteille $V_0 = 4,1 mL$ d’acide, que l’on complète à $V_1 = 500 mL$ avec de l’eau distillée.
+&lt;br&gt; On donne : 37 x 1,19 x 4,1 = 36,5 x 4,9
+&lt;br&gt;Le nombre de moles du soluté dans $4,1 mL$ de la solution commerciale vaut :</t>
+  </si>
+  <si>
+    <t>A : $4,9    mol$.</t>
+  </si>
+  <si>
+    <t>B : $490    mmol$.</t>
+  </si>
+  <si>
+    <t>C : $49    mmol$.</t>
+  </si>
+  <si>
+    <t>D : $0,49    mmol$.</t>
+  </si>
+  <si>
+    <t>E : $4,9    mmol$.</t>
+  </si>
+  <si>
+    <t>Les deux courbes se croisent lorsque $V_b$ égale :</t>
+  </si>
+  <si>
+    <t>La valeur de la masse $m'$ de l’acide benzoique égale :</t>
+  </si>
+  <si>
+    <t>Sachant que la constante d’équilibre de la réaction de dosage est $K = 10^{9.8}$, la valeur de $pK_a$ est :</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 6 : $\quad$ Réaction de l’acide éthanoïque avec l’ammoniac&lt;/b&gt;&lt;br&gt;
+&lt;br&gt;On prépare un mélange (S) de volume $V$, en introduisant $n_1 = 10^{-3} mol$ d’acide éthanoïque $CH_3COOH$ et $n_2 = 10^{-3} mol$ d’ammoniac $NH_3$, dans un récipient contenant de l’eau distillée. 
+&lt;br&gt;On donne : pK_a du couple (CH_3COOH/CH_3COO^-) = $pK_{a1} = 4,8$ $\quad$ et $\quad$ pK_a du couple (NH_4^+/NH_3) = $pK_{a2} = 9,2$ $\quad$ et $\quad$ $1 - 10^{2,2} = 1$</t>
+  </si>
+  <si>
+    <t>E : $\frac{1}{10^{-\frac{pK_{a1}}{2}}-10^{-\frac{pK_{a2}}{2}}}$</t>
+  </si>
+  <si>
+    <t>La valeur de taux d’avancement égale :</t>
+  </si>
+  <si>
+    <t>La valeur de $pH$ du mélange à l’équilibre est :</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 7 : $\quad$ Dilution d’acide méthanoïque&lt;/b&gt;&lt;br&gt;
+&lt;br&gt;On dissout une quantité $n$ de l’acide méthanoïque HCOOH dans l’eau distillée pour obtenir une solution aqueuse (S) de volume $V$. on mesure la valeur de $pH$ et on trouve que $pH = 2,91$. Après on dilue 10 fois la solution (S) on obtient une solution (S’) avec $pH' = 3,4$. 
+&lt;br&gt;On donne : $pK_a = 3,75$; $\quad$ $10^0,51 = 3$;  $\quad$ $10^0,84 = 6,5$</t>
+  </si>
+  <si>
+    <t>Le taux d’avancement $\tau'$ a pour expression :</t>
+  </si>
+  <si>
+    <t>E : $\frac{10^{pH'+pH-1}}{1+10^{pK_a-pH'}}$</t>
+  </si>
+  <si>
+    <t>D : $\frac{10^{1-pH'-pH}}{1+10^{pH-pK_a}}$</t>
+  </si>
+  <si>
+    <t>C : $\frac{10^{1-pH'+pH}}{1+10^{pH-pK_a}}$</t>
+  </si>
+  <si>
+    <t>B : $\frac{10^{1+pH'-pH}}{1+10^{pK_a-pH}}$</t>
+  </si>
+  <si>
+    <t>A : $\frac{10^{1-pH'+pH}}{1+10^{pK_a-pH}}$</t>
+  </si>
+  <si>
+    <t>La valeur de $\tau'$ est :</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 5 : $\quad$ Dosage de l’acide benzoïque&lt;/b&gt;&lt;br&gt;
+&lt;br&gt;On dissout une masse $m'$ d’une poudre d’acide benzoique dans un volume $V_e = 1 L$ d’eau pour obtenir une solution aqueuse (S). On titre un volume $V_a = 10 mL$ de la solution (S) par une solution aqueuse d’hydroxyde de sodium de concentration $C_b = 10 mmol.L^{-1}$. La figure ci-dessous représente Le diagramme de distribution en fonction de $V_b$ le volume versé lors de titrage. On donne : $M(C_6H_5COOH) = 122 g.mol^{-1}$.
+&lt;br&gt;&lt;img src="/images/CB1_Q18.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 1 : Suivi temporel d’une transformation chimique&lt;/b&gt;&lt;br&gt;
 À l’instant t=0 , on introduit une masse $m_0 = 27mg$ d’Aluminium ($Al_{(s)}$)
 dans un ballon contenant $V = 20mL$ d’une solution d’acide chlorhydrique ($H_3O^+_{(aq)} + Cl^-_{(aq)}$) de concentration $C_0$.
-On donne : $M(Al) = 27 g.mol^{-1}$ , $6H_3O^+_{(aq)} + 2Al_{(s)} \longrightarrow 3H_{2(g)} + 2Al^{3+}_{(aq)} + 6H_2O_{(l)}$</t>
-  </si>
-  <si>
-    <t>Q41 : Les couples (Ox/Red) participant à cette réaction sont :</t>
-  </si>
-  <si>
-    <t>Q42 : La valeur de $m(Al)$ est :</t>
-  </si>
-  <si>
-    <t>Q43 : La valeur de la vitesse volumique a l’instant $t=0s$ est :</t>
-  </si>
-  <si>
-    <t>A : $(Al^{3+}/Al)$ et $(H_3O^+/H_2)$.</t>
-  </si>
-  <si>
-    <t>B : $(Al^{3+}/Al)$ et $(H_2O/H_2)$.</t>
-  </si>
-  <si>
-    <t>C : $(Al^{3+}/Al)$ et $(H_2/H_3O^+)$.</t>
-  </si>
-  <si>
-    <t>D : $(Al^{3+}/Al)$ et $(HO^-/H_2)$.</t>
-  </si>
-  <si>
-    <t>E : $(Al/Al^{3+})$ et $(H_2O/H_2)$.</t>
-  </si>
-  <si>
-    <t>A : $9mg$ .</t>
-  </si>
-  <si>
-    <t>B : $16mg$.</t>
-  </si>
-  <si>
-    <t>C : $11mg$.</t>
-  </si>
-  <si>
-    <t>D : $12mg$.</t>
-  </si>
-  <si>
-    <t>E : $13mg$.</t>
-  </si>
-  <si>
-    <t>A : $-18,5.10^{-3} mol.L^{-1}.s^{-1}$.</t>
-  </si>
-  <si>
-    <t>B : $18,5.10^{-3} mol.L^{-1}.s^{-1}$.</t>
-  </si>
-  <si>
-    <t>C : $-9,25.10^{-3} mol.L^{-1}.s^{-1}$.</t>
-  </si>
-  <si>
-    <t>D : $9,25.10^{-3} mol.L^{-1}.s^{-1}$.</t>
-  </si>
-  <si>
-    <t>E : $-18,5.10^{-3} mol.L^{-1}.s^{-1}$.</t>
-  </si>
-  <si>
-    <t>Exercice 2 : conductimétrie
-On verse dans un bécher un volume $V = 10^{-2} L$ d’une solution $(S_B)$ d’hydroxyde de sodium de concentration molaire $C_B$ , et on y ajoute à l’instant $t=0$ considérée comme origine des temps, une quantité de matière $n_E$ du méthanoate de méthyle égale à la quantité de matière $n_B$ d’hydroxyde de sodium ($n_E=n_B$). (On considère que le volume reste constant $V$).
-On donne : $HCOOCH_{3(aq)} + HO^-_{(aq)} \longrightarrow HCOO^-_{(aq)} + CH_3OH_{(aq)}$</t>
-  </si>
-  <si>
-    <t>Q44 : Les ions présent dans le mélange à un instant t sont :</t>
-  </si>
-  <si>
-    <t>Q45 : Sachant que $X_{max} = 10^{-3} mol$, la valeur de $X_{max}$ est :</t>
-  </si>
-  <si>
-    <t>Q46 : La valeur de $\tau$ égale :</t>
-  </si>
-  <si>
-    <t>Q47 : La valeur de $[HO^-]$ à $t_{1/2}$ égale :</t>
-  </si>
-  <si>
-    <t>A : $Na^+, HO^-, H_3O^+$.</t>
-  </si>
-  <si>
-    <t>B : $HCOO^-, Na^+, H_3O^+$.</t>
-  </si>
-  <si>
-    <t>C : $HCOO^-, HO^-, Na^+$.</t>
-  </si>
-  <si>
-    <t>D : $HCOO^-, H_3O^+, Na^+$.</t>
-  </si>
-  <si>
-    <t>E : $HCOO^-, HO^-, H_3O^+$.</t>
-  </si>
-  <si>
-    <t>A : $10^{-3}$.</t>
-  </si>
-  <si>
-    <t>B : $3.10^{-2}$.</t>
-  </si>
-  <si>
-    <t>C : $4.10^{-3}$.</t>
-  </si>
-  <si>
-    <t>D : $2.10^{-3}$.</t>
-  </si>
-  <si>
-    <t>E : $10^{-2}$.</t>
-  </si>
-  <si>
-    <t>C : $1,78$.</t>
-  </si>
-  <si>
-    <t>D : $1,87$.</t>
-  </si>
-  <si>
-    <t>E : $10^{-4}$.</t>
-  </si>
-  <si>
-    <t>A : $5.10^{-3} mol.L^{-1}$.</t>
-  </si>
-  <si>
-    <t>B : $5.10^{-3} mol.L^{-1}$.</t>
-  </si>
-  <si>
-    <t>C : $5.10^{-3} mol.L^{-1}$.</t>
-  </si>
-  <si>
-    <t>D : $5.10^{-1} mol.L^{-1}$.</t>
-  </si>
-  <si>
-    <t>E : $5.10^{-3} mol.L^{-1}$.</t>
-  </si>
-  <si>
-    <t>Exercice 3 : Dissolution de l’ammoniac dans l’eau
-On considère une solution aqueuse $(S)$ d’ammoniac $NH_3$ avec taux d’avancement $\tau = 4,2\%$.
-On donne : $pH = 10,6$ , $K_e = 10^{-14}$</t>
-  </si>
-  <si>
-    <t>Q48 : Le taux d’avancement a pour expression :</t>
-  </si>
-  <si>
-    <t>Q49 : Sachant que $C = 1,0.10^{-2} mol.L^{-1}$, la valeur de $pH$ est :</t>
-  </si>
-  <si>
-    <t>Q50 : La constante d’acidité $K_a$ du couple $(NH_4^+/NH_3)$ a pour expression :</t>
-  </si>
-  <si>
-    <t>Q51 : La valeur de $pK_a$ est :</t>
-  </si>
-  <si>
-    <t>A : $\frac{10^{-pH}}{C}$.</t>
-  </si>
-  <si>
-    <t>B : $\frac{10^{pH}}{C}$.</t>
-  </si>
-  <si>
-    <t>C : $\frac{10^{-pH}}{C_0}$.</t>
-  </si>
-  <si>
-    <t>D : $\frac{10^{pH}}{C_0}$.</t>
-  </si>
-  <si>
-    <t>E : $\frac{10^{-pH}}{C_0}$.</t>
-  </si>
-  <si>
-    <t>A : $10,4$.</t>
-  </si>
-  <si>
-    <t>B : $10$.</t>
-  </si>
-  <si>
-    <t>C : $12,4$.</t>
-  </si>
-  <si>
-    <t>D : $11,8$.</t>
-  </si>
-  <si>
-    <t>E : $10,8$.</t>
-  </si>
-  <si>
-    <t>A : $\frac{1-\tau}{10^{pH}.C}$.</t>
-  </si>
-  <si>
-    <t>B : $\frac{1-\tau}{10^{-pH}.C}$.</t>
-  </si>
-  <si>
-    <t>C : $\frac{10^{pH}.C}{1-\tau}$.</t>
-  </si>
-  <si>
-    <t>D : $\frac{10^{-pH}.C}{1-\tau}$.</t>
-  </si>
-  <si>
-    <t>E : $\frac{10^{-pH}.C}{\tau - 1}$.</t>
-  </si>
-  <si>
-    <t>B : $9,2$.</t>
-  </si>
-  <si>
-    <t>C : $9,4$.</t>
-  </si>
-  <si>
-    <t>D : $9,8$.</t>
-  </si>
-  <si>
-    <t>E : $9,6$.</t>
-  </si>
-  <si>
-    <t>Exercice 4 : Dilution de la solution commerciale.
-Sur l’étiquette d’une bouteille d’acide chlorhydrique commercial, on lit les indications suivantes : « Acide chlorhydrique, masse volumique : $\rho = 1,19 g.mL^{-1}$ ; pourcentage en masse d’acide pur : $p = 37\%$ ; masse molaire de chlorure d’hydrogène HCl : $M = 36,5 g.mol^{-1}$ ». On extrait de cette bouteille $V_0 = 4,1 mL$ d’acide, que l’on complète à $V_1 = 1 L$ avec de l’eau distillée.
-&lt;br&gt;Q52 : le nombre de moles du soluté dans $4,1 mL$ de la solution commerciale vaut :</t>
-  </si>
-  <si>
-    <t>A : $4,9 mol$.</t>
-  </si>
-  <si>
-    <t>B : $490 mmol$.</t>
-  </si>
-  <si>
-    <t>C : $49 mmol$.</t>
-  </si>
-  <si>
-    <t>D : $0,49 mmol$.</t>
-  </si>
-  <si>
-    <t>E : $4,9 mmol$.</t>
-  </si>
-  <si>
-    <t>Exercice 5 : Dosage de l’acide benzoïque
-On dissout une masse $m'$ d’une poudre d’acide benzoique dans un volume $V_e = 1 L$ d’eau pour obtenir une solution aqueuse (S). On titre un volume $V_a = 10 mL$ de la solution (S) par une solution aqueuse d’hydroxyde de sodium de concentration $C_b = 10 mmol.L^{-1}$. La figure ci-dessous représente Le diagramme de distribution en fonction de $V_b$ le volume versé lors de titrage. On donne : $M(C_6H_5COOH) = 122 g.mol^{-1}$.</t>
-  </si>
-  <si>
-    <t>Q53 : Les deux courbes se croisent lorsque $V_b$ égale :</t>
-  </si>
-  <si>
-    <t>Q54 : La valeur de la masse $m'$ de l’acide benzoique égale :</t>
-  </si>
-  <si>
-    <t>Q55 : Sachant que la constante d’équilibre de la réaction de dosage est $K = 10^{9.8}$, la valeur de $pK_a$ est :</t>
-  </si>
-  <si>
-    <t>A : $V_{be}$.</t>
-  </si>
-  <si>
-    <t>B : $V_{be}/2$.</t>
-  </si>
-  <si>
-    <t>C : $2.V_{be}$.</t>
-  </si>
-  <si>
-    <t>D : $V_{be}/3$.</t>
-  </si>
-  <si>
-    <t>E : $3.V_{be}$.</t>
-  </si>
-  <si>
-    <t>A : $1,22 mg$.</t>
-  </si>
-  <si>
-    <t>B : $122 mg$.</t>
-  </si>
-  <si>
-    <t>C : $12,2 mg$.</t>
-  </si>
-  <si>
-    <t>D : $12,2 g$.</t>
-  </si>
-  <si>
-    <t>E : $1,22 g$.</t>
-  </si>
-  <si>
-    <t>A : $4,1$.</t>
-  </si>
-  <si>
-    <t>B : $4,3$.</t>
-  </si>
-  <si>
-    <t>C : $4,4$.</t>
-  </si>
-  <si>
-    <t>D : $4,2$.</t>
-  </si>
-  <si>
-    <t>E : $4$.</t>
-  </si>
-  <si>
-    <t>Exercice 6 : Réaction de l’acide éthanoïque avec l’ammoniac
-On prépare un mélange (S) de volume $V$, en introduisant $n_1 = 10^{-3} mol$ d’acide éthanoïque $CH_3COOH$ et $n_2 = 10^{-3} mol$ d’ammoniac $NH_3$, dans un récipient contenant de l’eau distillée. On donne : $pK_{a1} = 4,8$ et $pK_{a2} = 9,2$.</t>
-  </si>
-  <si>
-    <t>Q56 : Le taux d’avancement a pour expression :</t>
-  </si>
-  <si>
-    <t>Q57 : La valeur de taux d’avancement égale :</t>
-  </si>
-  <si>
-    <t>Q58 : La valeur de $pH$ du mélange a l’équilibre est :</t>
-  </si>
-  <si>
-    <t>A : $\frac{1}{10^{-pK_{a1}}-10^{-pK_{a2}}}$.</t>
-  </si>
-  <si>
-    <t>B : $\frac{1}{1+10^{\frac{pK_{a2}-pK_{a1}}{2}}}$.</t>
-  </si>
-  <si>
-    <t>C : $\frac{1}{10^{-pK_{a1}}+10^{-pK_{a2}}}$.</t>
-  </si>
-  <si>
-    <t>D : $\frac{1}{1+10^{\frac{pK_{a1}-pK_{a2}}{2}}}$.</t>
-  </si>
-  <si>
-    <t>E : $\frac{1}{10^{-\frac{pK_{a2}}{2}}-10^{-\frac{pK_{a2}}{2}}}$.</t>
-  </si>
-  <si>
-    <t>A : $0\%$.</t>
-  </si>
-  <si>
-    <t>B : $20\%$.</t>
-  </si>
-  <si>
-    <t>C : $30\%$.</t>
-  </si>
-  <si>
-    <t>D : $50\%$.</t>
-  </si>
-  <si>
-    <t>E : $100\%$.</t>
-  </si>
-  <si>
-    <t>A : $7$.</t>
-  </si>
-  <si>
-    <t>B : $2,2$.</t>
-  </si>
-  <si>
-    <t>D : $1$.</t>
-  </si>
-  <si>
-    <t>E : $14$.</t>
-  </si>
-  <si>
-    <t>Exercice 7 : Dilution d’acide méthanoïque
-On dissout une quantité $n$ de l’acide méthanoïque HCOOH dans l’eau distillée pour obtenir une solution aqueuse (S) de volume $V$. on mesure la valeur de $pH$ et on trouve que $pH = 2,91$. Après on dilue 10 fois la solution (S) on obtient une solution (S’) avec $pH' = 3,4$. On donne : $pK_a = 3,75$.</t>
-  </si>
-  <si>
-    <t>Q59 : Le taux d’avancement $\tau'$ a pour expression :</t>
-  </si>
-  <si>
-    <t>Q60 : la valeur de $\tau'$ est :</t>
-  </si>
-  <si>
-    <t>A : $\frac{10^{1-pH'+pH}}{1+10^{pK_a-pH}}$.</t>
-  </si>
-  <si>
-    <t>B : $\frac{10^{1+pH'-pH}}{1+10^{pK_a-pH}}$.</t>
-  </si>
-  <si>
-    <t>C : $\frac{10^{1-pH'+pH}}{1+10^{pH-pK_a}}$.</t>
-  </si>
-  <si>
-    <t>D : $\frac{10^{1-pH'-pH}}{1+10^{pH-pK_a}}$.</t>
-  </si>
-  <si>
-    <t>E : $\frac{10^{pH'+pH-1}}{1+10^{pK_a-pH}}$.</t>
-  </si>
-  <si>
-    <t>A : $20\%$.</t>
-  </si>
-  <si>
-    <t>B : $10\%$.</t>
-  </si>
-  <si>
-    <t>D : $40\%$.</t>
-  </si>
-  <si>
-    <t>E : $50\%$.</t>
-  </si>
-  <si>
-    <t>E : $2 \sin(\frac{a-b}{2}) e^{i \frac{a+b}{2}}$.</t>
-  </si>
-  <si>
-    <t>C : $0$.</t>
-  </si>
-  <si>
-    <t>B : $1$.</t>
-  </si>
-  <si>
-    <t>A : $]-\infty, \frac{1}{4}[$.</t>
-  </si>
-  <si>
-    <t>B : $]\frac{1}{4}, \frac{2}{5}[$.</t>
-  </si>
-  <si>
-    <t>C : $]\frac{1}{4}, +\infty[$.</t>
-  </si>
-  <si>
-    <t>D : $]0, \frac{1}{4}[$.</t>
-  </si>
-  <si>
-    <t>E : $\emptyset$.</t>
-  </si>
-  <si>
-    <t>A : $]-\infty, \frac{\ln(0,5)}{\ln(0,98)}]$.</t>
-  </si>
-  <si>
-    <t>B : $]-\infty, \frac{\ln(0,98)}{\ln(0,5)}]$.</t>
-  </si>
-  <si>
-    <t>C : $[\frac{\ln(0,5)}{\ln(0,98)}, +\infty[$.</t>
-  </si>
-  <si>
-    <t>D : $[\frac{\ln(0,98)}{\ln(0,5)}, +\infty[$.</t>
-  </si>
-  <si>
-    <t>A : $\ln(n)$.</t>
-  </si>
-  <si>
-    <t>C : $\ln(n-2)$.</t>
-  </si>
-  <si>
-    <t>E : $\ln(n+2)$.</t>
-  </si>
-  <si>
-    <t>A : $0$.</t>
-  </si>
-  <si>
-    <t>C : $n$.</t>
-  </si>
-  <si>
-    <t>D : $e$.</t>
-  </si>
-  <si>
-    <t>E : $+\infty$.</t>
-  </si>
-  <si>
-    <t>D : $0$.</t>
-  </si>
-  <si>
-    <t>A : $]e, e^\pi[$.</t>
-  </si>
-  <si>
-    <t>B : $]-\infty, e[ \cup ]e, e^\pi[ \cup ]e^\pi, +\infty[$.</t>
-  </si>
-  <si>
-    <t>D : $]-\infty, e[ \cup ]e, e^\pi[$.</t>
-  </si>
-  <si>
-    <t>E : $]e, e^\pi[ \cup ]e^\pi, +\infty[$.</t>
-  </si>
-  <si>
-    <t>A : $\frac{e^\pi+1}{2}$.</t>
-  </si>
-  <si>
-    <t>B : $\frac{e^\pi-1}{2}$.</t>
-  </si>
-  <si>
-    <t>C : $\frac{1}{2}$.</t>
-  </si>
-  <si>
-    <t>D : $\frac{e}{2}$.</t>
-  </si>
-  <si>
-    <t>E : $\frac{1-e^\pi}{2}$.</t>
-  </si>
-  <si>
-    <t>A : $\ln[\frac{2\sqrt{e}}{e+1}]$.</t>
-  </si>
-  <si>
-    <t>B : $\ln(e) + \ln(e+1)$.</t>
-  </si>
-  <si>
-    <t>C : $\frac{1}{2} + \ln(e+1)$.</t>
-  </si>
-  <si>
-    <t>D : $\ln[\frac{e+1}{2\sqrt{e}}]$.</t>
-  </si>
-  <si>
-    <t>E : $\ln[2\sqrt{e}(e+1)]$.</t>
-  </si>
-  <si>
-    <t>A : Le cercle de centre O et de rayon 1 privé du point d’affixe 1.</t>
-  </si>
-  <si>
-    <t>B : L’axe des imaginaires purs privé du point d’affixe 1.</t>
-  </si>
-  <si>
-    <t>C : L’axe des réels privé du point d’affixe 1.</t>
-  </si>
-  <si>
-    <t>D : Le cercle de centre M et de rayon 1 privé du point d’affixe 1.</t>
-  </si>
-  <si>
-    <t>E : On ne peut rien en dire.</t>
-  </si>
-  <si>
-    <t>A : $2\cos(\frac{\theta}{2})$.</t>
-  </si>
-  <si>
-    <t>B : $2\sin(\frac{\theta}{2})$.</t>
-  </si>
-  <si>
-    <t>C : $\tan(\frac{\theta}{2})$.</t>
-  </si>
-  <si>
-    <t>D : $\cos(\theta)$.</t>
-  </si>
-  <si>
-    <t>E : $1$.</t>
-  </si>
-  <si>
-    <t>A : $(\frac{1}{2} + \frac{i\sqrt{3}}{2})$.</t>
-  </si>
-  <si>
-    <t>B : $(\frac{1}{2} - \frac{i\sqrt{3}}{2})$.</t>
-  </si>
-  <si>
-    <t>C : $i$.</t>
-  </si>
-  <si>
-    <t>D : $-1$.</t>
-  </si>
-  <si>
-    <t>E : $-i$.</t>
-  </si>
-  <si>
-    <t>A : $f(x)=f(2a-x)$.</t>
-  </si>
-  <si>
-    <t>B : $f(x)=f(2a+x)$.</t>
-  </si>
-  <si>
-    <t>C : $f(x)=f(x-a)$.</t>
-  </si>
-  <si>
-    <t>D : $f(x)=-f(x-2a)$.</t>
-  </si>
-  <si>
-    <t>E : $f(x)=f(x+a)$.</t>
-  </si>
-  <si>
-    <t>B : $\frac{1}{6}$.</t>
-  </si>
-  <si>
-    <t>C : $-\frac{1}{6}$.</t>
-  </si>
-  <si>
-    <t>D : $\ln(5)$.</t>
-  </si>
-  <si>
-    <t>E : $-\ln(5)$.</t>
-  </si>
-  <si>
-    <t>A : $9$.</t>
-  </si>
-  <si>
-    <t>B : $\frac{1}{9}$.</t>
-  </si>
-  <si>
-    <t>C : $\frac{1}{e}$.</t>
-  </si>
-  <si>
-    <t>Soient $a,b \in ]0,\pi[$, alors la forme exponentiel de $z = e^{ia} + e^{ib}$ est:</t>
-  </si>
-  <si>
-    <t>B : $2 \cos(\frac{a+b}{2}) e^{i \frac{a+b}{2}}$.</t>
-  </si>
-  <si>
-    <t>D : $2 \sin(\frac{a+b}{2}) e^{i \frac{a+b}{2}}$.</t>
-  </si>
-  <si>
-    <t>C : $2i \cos(\frac{a-b}{2}) e^{i \frac{a+b}{2}}$.</t>
-  </si>
-  <si>
-    <t>A : $ \cot(\frac{a-b}{2}) e^{i(a+b)}$.</t>
-  </si>
-  <si>
-    <t>Les nombres complexes $sin(\teta) + i cos(2.\teta)$ et $cos(\teta) - i sin(2.\teta) sont conjugués l’un à l’autre pour $\teta$ égale à :</t>
-  </si>
-  <si>
-    <t>A : $n\pi$.</t>
-  </si>
-  <si>
-    <t>B : $(n + \frac{1}{2})\pi$.</t>
-  </si>
-  <si>
-    <t>E : aucune valeur de $\teta$.</t>
-  </si>
-  <si>
-    <t>On a pour $n \in \mathbb{N}^*$, $\lim_{x \to e} \frac{\ln(x^n) - n}{x - e}$ est égale à :</t>
-  </si>
-  <si>
-    <t>A : $\frac{n}{e}$</t>
-  </si>
-  <si>
-    <t>B : $\frac{e}{n}$</t>
-  </si>
-  <si>
-    <t>C : $n.e$</t>
-  </si>
-  <si>
-    <t>D : $1$</t>
-  </si>
-  <si>
-    <t>E : $0$</t>
-  </si>
-  <si>
-    <t>Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour $$\ln(3x)&gt;\ln(2-5x)$$ est:</t>
-  </si>
-  <si>
-    <t>L’ensemble des solutions de l’inéquation $(1 - 0.02)^{x} \leq 0,5$ est:</t>
-  </si>
-  <si>
-    <t>La primitive $F$ de la fonction $f$ définie sur l’intervalle $I=]0,+\infty[$ par $f(x) = \frac{2x^3 + 3 - x}{x}, telle que : $F(1)=1$ vérifiée est :</t>
-  </si>
-  <si>
-    <t>A : $\frac{x^2 - 1 +3 \ln(x)}{3} $</t>
-  </si>
-  <si>
-    <t>C : $\frac{x^3 - x + 3 \ln(x)}{3} $</t>
-  </si>
-  <si>
-    <t>B : $\frac{2x^3 - 3x + 9 \ln(x) + 4}{3} $</t>
-  </si>
-  <si>
-    <t>D : $\frac{3x^2 - x + \ln(x) + 4}{3} $</t>
-  </si>
-  <si>
-    <t>B : $\frac{2x^3 - x + \ln(x) + 1}{3} $</t>
-  </si>
-  <si>
-    <t>Soit $(v_n)_{n \in \mathbb{N}^*}$ la suite définie par $v_n = \ln(\frac{n}{n+1})$, alors la somme : $v_2 + v_3 + \dots + v_{n-1}$ est égale à :</t>
-  </si>
-  <si>
-    <t>B : $\ln(\frac{n}{2})$.</t>
-  </si>
-  <si>
-    <t>D : $\ln(\frac{2}{n})$.</t>
-  </si>
-  <si>
-    <t>On a pour $n \in \mathbb{N}^*$, $x \in \mathbb{R}$, $\lim_{x \to +\infty} (\frac{\ln(nx)}{e^{nx})^2$ est égale à :</t>
-  </si>
-  <si>
-    <t>Soit $\lambda$ un nombre complexe non nul et diffèrent de 1, on définit pour tout entier naturel n , la suite $(Z_n)$ de nombre complexe par : $Z_{n+1} - \lambda Z_n = i$ et $Z_0 = 0$ , alors l’égalité correcte est :</t>
-  </si>
-  <si>
-    <t>A : $Z_1 = i$.</t>
-  </si>
-  <si>
-    <t>B : $\bar(Z_3 - Z_2) = \bar{\lambda}^2 i$.</t>
-  </si>
-  <si>
-    <t>C : $Z_2 = (\bar{\lambda} + 1)i$.</t>
-  </si>
-  <si>
-    <t>D : $\bar(Z_2 + Z_1) = (\bar{\lambda} + 2)i$.</t>
-  </si>
-  <si>
-    <t>E : $Z_3 = (\lambda^2 + \lambda + 1)i$.</t>
-  </si>
-  <si>
-    <t>Si $(\forall x \in \mathbb{R})$, $f(x)=(e^\sqrt{x} - 1).(\sqrt{x} + e^x).(e^{2x} + 1).(x - 1)$, alors $f'(1)$ est égale à :</t>
-  </si>
-  <si>
-    <t>C : $e^4 - 1$</t>
-  </si>
-  <si>
-    <t>B : $e-1$</t>
-  </si>
-  <si>
-    <t>A : $1$</t>
-  </si>
-  <si>
-    <t>E : $e^2 - 1$</t>
-  </si>
-  <si>
-    <t>A : $\ln(\ln(\ln(x) + 3))$</t>
-  </si>
-  <si>
-    <t>B : $\ln(\ln(\ln(x))+3)$</t>
-  </si>
-  <si>
-    <t>C : $\ln(\ln(\ln(\ln(x))))+3$</t>
-  </si>
-  <si>
-    <t>E : $\ln(\ln(x)+3)$</t>
-  </si>
-  <si>
-    <t>D : $\ln(\ln(x))+3$</t>
-  </si>
-  <si>
-    <t>Soit $f$ définit par : $f(x)= \frac{1}{x \ln(x) \ln(\ln(x))}$, la primitive de $f$ sur $]e,+\infty[$ est :</t>
-  </si>
-  <si>
-    <t>Le domaine de définition de la fontion f définie par : $f(x)= \frac{\ln(\ln(\ln(x)))}{x - e^\pi}$ est :</t>
-  </si>
-  <si>
-    <t>C : $]1, e^pi[ \cup ]e^pi, +\infty[$.</t>
-  </si>
-  <si>
-    <t>L’intégrale $\int_{e^\pi}^{1} \sin(\ln(x)) dx$ égale :</t>
-  </si>
-  <si>
-    <t>L’intégrale $\int_{0}^{1/2} \frac{1}{e^{2x}+1} dx$ égale :</t>
-  </si>
-  <si>
-    <t>Le plan complexe est rapporté à un repère orthonormal $(o, \vec{u}, \vec{v})$. L’ensemble des points M d’affixe $Z$ tel que : $Z = \frac{\bar{z}+1}{z-1}$ est réel est :</t>
-  </si>
-  <si>
-    <t>si $Z=\frac{1-e^{2i\theta}}{1-e^{i\theta}}$ où $\theta \in ]0, \pi[$ alors $|Z|$ égale à :</t>
-  </si>
-  <si>
-    <t>Le nombre complexe $(\frac{1}{2} + \frac{i\sqrt{3}}{2})^{13}$ égale :</t>
-  </si>
-  <si>
-    <t>Soit $f$ la fonction définit sur $\mathbb{R}$, la droite $x=a$ est la droite de symétrie tel que :</t>
-  </si>
-  <si>
-    <t>Soit $f^{-1}$ la fonction reciproque de $f$ définit sur $]\ln(4),+\infty[$, par : $x \mapsto \ln(e^{2x} - 4e^x)$ , alors $f^{-1}(\ln(5))$ égale :</t>
-  </si>
-  <si>
-    <t>Soit $(v_n)$ la suite définit par : $v_{n+1} = \ln(\frac{u_{n+1}}{9}) = \frac{1}{2}v_n$ et $u_0 = 9e$, pour tout entier naturel n. Alors la limite de $u_n$ vaut :</t>
+&lt;br&gt; On a : $6H_3O^+_{(aq)} + 2Al_{(s)} \longrightarrow 3H_{2(g)} + 2Al^{3+}_{(aq)} + 6H_2O_{(l)}$
+&lt;br&gt; On donne : $M(Al) = 27 g.mol^{-1}$ , $\frac{2}{54} = 0, 0185$ , 20x27 = 540, 27x440 = 540x22 , $\frac{1}{44} = 0, 0227
+&lt;br&gt;&lt;img src="/images/CB1_Q17.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
 </sst>
 </file>
@@ -3383,7 +3393,7 @@
         <v>135</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>261</v>
+        <v>422</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="3"/>
@@ -3586,19 +3596,19 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="J47" s="2"/>
       <c r="M47" s="4">
@@ -3671,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>1</v>
       </c>
@@ -3679,7 +3689,7 @@
         <v>135</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>267</v>
+        <v>503</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="3"/>
@@ -3704,23 +3714,23 @@
         <v>136</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>268</v>
+        <v>429</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F51" t="s">
-        <v>272</v>
+        <v>423</v>
       </c>
       <c r="G51" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H51" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="I51" t="s">
-        <v>275</v>
+        <v>424</v>
       </c>
       <c r="J51" s="2"/>
       <c r="M51" s="4">
@@ -3735,23 +3745,23 @@
         <v>136</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>269</v>
+        <v>430</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F52" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G52" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="H52" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="I52" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="4"/>
@@ -3768,23 +3778,23 @@
         <v>136</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>270</v>
+        <v>431</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s">
-        <v>281</v>
+        <v>425</v>
       </c>
       <c r="F53" t="s">
-        <v>282</v>
+        <v>426</v>
       </c>
       <c r="G53" t="s">
-        <v>283</v>
+        <v>427</v>
       </c>
       <c r="H53" t="s">
-        <v>284</v>
+        <v>428</v>
       </c>
       <c r="I53" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="4"/>
@@ -3793,7 +3803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>1</v>
       </c>
@@ -3801,7 +3811,7 @@
         <v>135</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>286</v>
+        <v>432</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="3"/>
@@ -3826,30 +3836,30 @@
         <v>136</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>287</v>
+        <v>438</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s">
-        <v>291</v>
+        <v>433</v>
       </c>
       <c r="F55" t="s">
-        <v>292</v>
+        <v>434</v>
       </c>
       <c r="G55" t="s">
-        <v>293</v>
+        <v>435</v>
       </c>
       <c r="H55" t="s">
-        <v>294</v>
+        <v>436</v>
       </c>
       <c r="I55" t="s">
-        <v>295</v>
+        <v>437</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="12"/>
       <c r="L55" s="12"/>
       <c r="M55" s="5"/>
     </row>
-    <row r="56" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>1</v>
       </c>
@@ -3857,23 +3867,23 @@
         <v>136</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>288</v>
+        <v>439</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s">
-        <v>296</v>
+        <v>440</v>
       </c>
       <c r="F56" t="s">
-        <v>297</v>
+        <v>441</v>
       </c>
       <c r="G56" t="s">
-        <v>298</v>
+        <v>442</v>
       </c>
       <c r="H56" t="s">
-        <v>299</v>
+        <v>443</v>
       </c>
       <c r="I56" t="s">
-        <v>300</v>
+        <v>444</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="12"/>
@@ -3888,23 +3898,23 @@
         <v>136</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>289</v>
+        <v>445</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s">
-        <v>296</v>
+        <v>447</v>
       </c>
       <c r="F57" t="s">
-        <v>297</v>
+        <v>446</v>
       </c>
       <c r="G57" t="s">
-        <v>301</v>
+        <v>448</v>
       </c>
       <c r="H57" t="s">
-        <v>302</v>
+        <v>449</v>
       </c>
       <c r="I57" t="s">
-        <v>303</v>
+        <v>450</v>
       </c>
       <c r="J57" s="3"/>
       <c r="M57" s="5">
@@ -3919,23 +3929,23 @@
         <v>136</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>290</v>
+        <v>451</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s">
-        <v>304</v>
+        <v>452</v>
       </c>
       <c r="F58" t="s">
-        <v>305</v>
+        <v>453</v>
       </c>
       <c r="G58" t="s">
-        <v>306</v>
+        <v>454</v>
       </c>
       <c r="H58" t="s">
-        <v>307</v>
+        <v>455</v>
       </c>
       <c r="I58" t="s">
-        <v>308</v>
+        <v>456</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="4"/>
@@ -3944,7 +3954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>1</v>
       </c>
@@ -3952,7 +3962,7 @@
         <v>135</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>309</v>
+        <v>457</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="3"/>
@@ -3977,23 +3987,23 @@
         <v>136</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>310</v>
+        <v>458</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s">
-        <v>314</v>
+        <v>459</v>
       </c>
       <c r="F60" t="s">
-        <v>315</v>
+        <v>460</v>
       </c>
       <c r="G60" t="s">
-        <v>316</v>
+        <v>461</v>
       </c>
       <c r="H60" t="s">
-        <v>317</v>
+        <v>462</v>
       </c>
       <c r="I60" t="s">
-        <v>318</v>
+        <v>463</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="4"/>
@@ -4010,23 +4020,23 @@
         <v>136</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>311</v>
+        <v>464</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s">
-        <v>319</v>
+        <v>469</v>
       </c>
       <c r="F61" t="s">
-        <v>320</v>
+        <v>468</v>
       </c>
       <c r="G61" t="s">
-        <v>321</v>
+        <v>467</v>
       </c>
       <c r="H61" t="s">
-        <v>322</v>
+        <v>466</v>
       </c>
       <c r="I61" t="s">
-        <v>323</v>
+        <v>465</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="4"/>
@@ -4041,23 +4051,23 @@
         <v>136</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>312</v>
+        <v>470</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s">
-        <v>324</v>
+        <v>471</v>
       </c>
       <c r="F62" t="s">
-        <v>325</v>
+        <v>472</v>
       </c>
       <c r="G62" t="s">
-        <v>326</v>
+        <v>473</v>
       </c>
       <c r="H62" t="s">
-        <v>327</v>
+        <v>474</v>
       </c>
       <c r="I62" t="s">
-        <v>328</v>
+        <v>475</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="4"/>
@@ -4074,23 +4084,23 @@
         <v>136</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>313</v>
+        <v>476</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s">
-        <v>319</v>
+        <v>469</v>
       </c>
       <c r="F63" t="s">
-        <v>329</v>
+        <v>477</v>
       </c>
       <c r="G63" t="s">
-        <v>330</v>
+        <v>478</v>
       </c>
       <c r="H63" t="s">
-        <v>331</v>
+        <v>479</v>
       </c>
       <c r="I63" t="s">
-        <v>332</v>
+        <v>480</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="4"/>
@@ -4099,7 +4109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>1</v>
       </c>
@@ -4107,30 +4117,30 @@
         <v>14</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>333</v>
+        <v>481</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s">
-        <v>334</v>
+        <v>482</v>
       </c>
       <c r="F64" t="s">
-        <v>335</v>
+        <v>483</v>
       </c>
       <c r="G64" t="s">
-        <v>336</v>
+        <v>484</v>
       </c>
       <c r="H64" t="s">
-        <v>337</v>
+        <v>485</v>
       </c>
       <c r="I64" t="s">
-        <v>338</v>
+        <v>486</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
     </row>
-    <row r="65" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>1</v>
       </c>
@@ -4138,7 +4148,7 @@
         <v>135</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>339</v>
+        <v>502</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3"/>
@@ -4163,23 +4173,23 @@
         <v>136</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>340</v>
+        <v>487</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s">
-        <v>343</v>
+        <v>275</v>
       </c>
       <c r="F66" t="s">
-        <v>344</v>
+        <v>276</v>
       </c>
       <c r="G66" t="s">
-        <v>345</v>
+        <v>277</v>
       </c>
       <c r="H66" t="s">
-        <v>346</v>
+        <v>278</v>
       </c>
       <c r="I66" t="s">
-        <v>347</v>
+        <v>279</v>
       </c>
       <c r="J66" s="2"/>
       <c r="M66" s="5">
@@ -4194,23 +4204,23 @@
         <v>136</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>341</v>
+        <v>488</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s">
-        <v>348</v>
+        <v>280</v>
       </c>
       <c r="F67" t="s">
-        <v>349</v>
+        <v>281</v>
       </c>
       <c r="G67" t="s">
-        <v>350</v>
+        <v>282</v>
       </c>
       <c r="H67" t="s">
-        <v>351</v>
+        <v>283</v>
       </c>
       <c r="I67" t="s">
-        <v>352</v>
+        <v>284</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="4"/>
@@ -4227,23 +4237,23 @@
         <v>136</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>342</v>
+        <v>489</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s">
-        <v>353</v>
+        <v>285</v>
       </c>
       <c r="F68" t="s">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="G68" t="s">
-        <v>355</v>
+        <v>287</v>
       </c>
       <c r="H68" t="s">
-        <v>356</v>
+        <v>288</v>
       </c>
       <c r="I68" t="s">
-        <v>357</v>
+        <v>289</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="4"/>
@@ -4252,7 +4262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>1</v>
       </c>
@@ -4260,7 +4270,7 @@
         <v>135</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>358</v>
+        <v>490</v>
       </c>
       <c r="D69" s="2"/>
       <c r="J69" s="2"/>
@@ -4280,23 +4290,23 @@
         <v>136</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>359</v>
+        <v>458</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s">
-        <v>362</v>
+        <v>290</v>
       </c>
       <c r="F70" t="s">
-        <v>363</v>
+        <v>291</v>
       </c>
       <c r="G70" t="s">
-        <v>364</v>
+        <v>292</v>
       </c>
       <c r="H70" t="s">
-        <v>365</v>
+        <v>293</v>
       </c>
       <c r="I70" t="s">
-        <v>366</v>
+        <v>491</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="4"/>
@@ -4313,23 +4323,23 @@
         <v>136</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>360</v>
+        <v>492</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s">
-        <v>367</v>
+        <v>294</v>
       </c>
       <c r="F71" t="s">
-        <v>368</v>
+        <v>295</v>
       </c>
       <c r="G71" t="s">
-        <v>369</v>
+        <v>296</v>
       </c>
       <c r="H71" t="s">
-        <v>370</v>
+        <v>297</v>
       </c>
       <c r="I71" t="s">
-        <v>371</v>
+        <v>298</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="4"/>
@@ -4344,23 +4354,23 @@
         <v>136</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>361</v>
+        <v>493</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s">
-        <v>372</v>
+        <v>299</v>
       </c>
       <c r="F72" t="s">
-        <v>373</v>
+        <v>300</v>
       </c>
       <c r="G72" t="s">
-        <v>355</v>
+        <v>287</v>
       </c>
       <c r="H72" t="s">
-        <v>374</v>
+        <v>301</v>
       </c>
       <c r="I72" t="s">
-        <v>375</v>
+        <v>302</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="4"/>
@@ -4369,7 +4379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>1</v>
       </c>
@@ -4377,7 +4387,7 @@
         <v>135</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>376</v>
+        <v>494</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="3"/>
@@ -4402,23 +4412,23 @@
         <v>136</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>377</v>
+        <v>495</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s">
-        <v>379</v>
+        <v>500</v>
       </c>
       <c r="F74" t="s">
-        <v>380</v>
+        <v>499</v>
       </c>
       <c r="G74" t="s">
-        <v>381</v>
+        <v>498</v>
       </c>
       <c r="H74" t="s">
-        <v>382</v>
+        <v>497</v>
       </c>
       <c r="I74" t="s">
-        <v>383</v>
+        <v>496</v>
       </c>
       <c r="J74" s="2"/>
       <c r="M74" s="5">
@@ -4433,23 +4443,23 @@
         <v>136</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>378</v>
+        <v>501</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s">
-        <v>384</v>
+        <v>303</v>
       </c>
       <c r="F75" t="s">
-        <v>385</v>
+        <v>304</v>
       </c>
       <c r="G75" t="s">
-        <v>369</v>
+        <v>296</v>
       </c>
       <c r="H75" t="s">
-        <v>386</v>
+        <v>305</v>
       </c>
       <c r="I75" t="s">
-        <v>387</v>
+        <v>306</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="4"/>
@@ -4466,23 +4476,23 @@
         <v>14</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>449</v>
+        <v>368</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s">
-        <v>453</v>
+        <v>372</v>
       </c>
       <c r="F76" t="s">
-        <v>450</v>
+        <v>369</v>
       </c>
       <c r="G76" t="s">
-        <v>452</v>
+        <v>371</v>
       </c>
       <c r="H76" t="s">
-        <v>451</v>
+        <v>370</v>
       </c>
       <c r="I76" t="s">
-        <v>388</v>
+        <v>307</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="4" t="s">
@@ -4503,23 +4513,23 @@
         <v>14</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>454</v>
+        <v>373</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s">
-        <v>455</v>
+        <v>374</v>
       </c>
       <c r="F77" t="s">
-        <v>456</v>
+        <v>375</v>
       </c>
       <c r="G77" t="s">
-        <v>389</v>
+        <v>308</v>
       </c>
       <c r="H77" t="s">
-        <v>374</v>
+        <v>301</v>
       </c>
       <c r="I77" t="s">
-        <v>457</v>
+        <v>376</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="4" t="s">
@@ -4538,23 +4548,23 @@
         <v>14</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>458</v>
+        <v>377</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s">
-        <v>459</v>
+        <v>378</v>
       </c>
       <c r="F78" t="s">
-        <v>460</v>
+        <v>379</v>
       </c>
       <c r="G78" t="s">
-        <v>461</v>
+        <v>380</v>
       </c>
       <c r="H78" t="s">
-        <v>462</v>
+        <v>381</v>
       </c>
       <c r="I78" t="s">
-        <v>463</v>
+        <v>382</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="4" t="s">
@@ -4575,23 +4585,23 @@
         <v>14</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>464</v>
+        <v>383</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s">
-        <v>391</v>
+        <v>310</v>
       </c>
       <c r="F79" t="s">
-        <v>392</v>
+        <v>311</v>
       </c>
       <c r="G79" t="s">
-        <v>393</v>
+        <v>312</v>
       </c>
       <c r="H79" t="s">
-        <v>394</v>
+        <v>313</v>
       </c>
       <c r="I79" t="s">
-        <v>395</v>
+        <v>314</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="4" t="s">
@@ -4612,23 +4622,23 @@
         <v>14</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>465</v>
+        <v>384</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s">
-        <v>396</v>
+        <v>315</v>
       </c>
       <c r="F80" t="s">
-        <v>397</v>
+        <v>316</v>
       </c>
       <c r="G80" t="s">
-        <v>398</v>
+        <v>317</v>
       </c>
       <c r="H80" t="s">
-        <v>399</v>
+        <v>318</v>
       </c>
       <c r="I80" t="s">
-        <v>395</v>
+        <v>314</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="4" t="s">
@@ -4649,23 +4659,23 @@
         <v>14</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>466</v>
+        <v>385</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s">
-        <v>467</v>
+        <v>386</v>
       </c>
       <c r="F81" t="s">
-        <v>469</v>
+        <v>388</v>
       </c>
       <c r="G81" t="s">
-        <v>468</v>
+        <v>387</v>
       </c>
       <c r="H81" t="s">
-        <v>470</v>
+        <v>389</v>
       </c>
       <c r="I81" t="s">
-        <v>471</v>
+        <v>390</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="4" t="s">
@@ -4684,23 +4694,23 @@
         <v>14</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>472</v>
+        <v>391</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s">
-        <v>400</v>
+        <v>319</v>
       </c>
       <c r="F82" t="s">
-        <v>473</v>
+        <v>392</v>
       </c>
       <c r="G82" t="s">
-        <v>401</v>
+        <v>320</v>
       </c>
       <c r="H82" t="s">
-        <v>474</v>
+        <v>393</v>
       </c>
       <c r="I82" t="s">
-        <v>402</v>
+        <v>321</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" s="4" t="s">
@@ -4721,23 +4731,23 @@
         <v>14</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>475</v>
+        <v>394</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s">
-        <v>403</v>
+        <v>322</v>
       </c>
       <c r="F83" t="s">
-        <v>390</v>
+        <v>309</v>
       </c>
       <c r="G83" t="s">
-        <v>404</v>
+        <v>323</v>
       </c>
       <c r="H83" t="s">
-        <v>405</v>
+        <v>324</v>
       </c>
       <c r="I83" t="s">
-        <v>406</v>
+        <v>325</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" s="4" t="s">
@@ -4758,23 +4768,23 @@
         <v>14</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>476</v>
+        <v>395</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s">
-        <v>477</v>
+        <v>396</v>
       </c>
       <c r="F84" t="s">
-        <v>478</v>
+        <v>397</v>
       </c>
       <c r="G84" t="s">
-        <v>479</v>
+        <v>398</v>
       </c>
       <c r="H84" t="s">
-        <v>480</v>
+        <v>399</v>
       </c>
       <c r="I84" t="s">
-        <v>481</v>
+        <v>400</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="4" t="s">
@@ -4793,23 +4803,23 @@
         <v>14</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>482</v>
+        <v>401</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s">
-        <v>485</v>
+        <v>404</v>
       </c>
       <c r="F85" t="s">
-        <v>484</v>
+        <v>403</v>
       </c>
       <c r="G85" t="s">
-        <v>483</v>
+        <v>402</v>
       </c>
       <c r="H85" t="s">
-        <v>407</v>
+        <v>326</v>
       </c>
       <c r="I85" t="s">
-        <v>486</v>
+        <v>405</v>
       </c>
       <c r="J85" s="9"/>
       <c r="K85" s="4" t="s">
@@ -4830,23 +4840,23 @@
         <v>14</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>492</v>
+        <v>411</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s">
-        <v>487</v>
+        <v>406</v>
       </c>
       <c r="F86" t="s">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="G86" t="s">
-        <v>489</v>
+        <v>408</v>
       </c>
       <c r="H86" t="s">
-        <v>491</v>
+        <v>410</v>
       </c>
       <c r="I86" t="s">
-        <v>490</v>
+        <v>409</v>
       </c>
       <c r="J86" s="9"/>
       <c r="K86" s="4" t="s">
@@ -4867,23 +4877,23 @@
         <v>14</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>493</v>
+        <v>412</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s">
-        <v>408</v>
+        <v>327</v>
       </c>
       <c r="F87" t="s">
-        <v>409</v>
+        <v>328</v>
       </c>
       <c r="G87" t="s">
-        <v>494</v>
+        <v>413</v>
       </c>
       <c r="H87" t="s">
-        <v>410</v>
+        <v>329</v>
       </c>
       <c r="I87" t="s">
-        <v>411</v>
+        <v>330</v>
       </c>
       <c r="J87" s="9"/>
       <c r="K87" s="4" t="s">
@@ -4904,23 +4914,23 @@
         <v>14</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>495</v>
+        <v>414</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s">
-        <v>412</v>
+        <v>331</v>
       </c>
       <c r="F88" t="s">
-        <v>413</v>
+        <v>332</v>
       </c>
       <c r="G88" t="s">
-        <v>414</v>
+        <v>333</v>
       </c>
       <c r="H88" t="s">
-        <v>415</v>
+        <v>334</v>
       </c>
       <c r="I88" t="s">
-        <v>416</v>
+        <v>335</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="4" t="s">
@@ -4939,23 +4949,23 @@
         <v>14</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>496</v>
+        <v>415</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s">
-        <v>417</v>
+        <v>336</v>
       </c>
       <c r="F89" t="s">
-        <v>418</v>
+        <v>337</v>
       </c>
       <c r="G89" t="s">
-        <v>419</v>
+        <v>338</v>
       </c>
       <c r="H89" t="s">
-        <v>420</v>
+        <v>339</v>
       </c>
       <c r="I89" t="s">
-        <v>421</v>
+        <v>340</v>
       </c>
       <c r="J89" s="9"/>
       <c r="K89" s="4" t="s">
@@ -4976,23 +4986,23 @@
         <v>14</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>497</v>
+        <v>416</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s">
-        <v>422</v>
+        <v>341</v>
       </c>
       <c r="F90" t="s">
-        <v>423</v>
+        <v>342</v>
       </c>
       <c r="G90" t="s">
-        <v>424</v>
+        <v>343</v>
       </c>
       <c r="H90" t="s">
-        <v>425</v>
+        <v>344</v>
       </c>
       <c r="I90" t="s">
-        <v>426</v>
+        <v>345</v>
       </c>
       <c r="J90" s="9"/>
       <c r="K90" s="4" t="s">
@@ -5013,23 +5023,23 @@
         <v>14</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>498</v>
+        <v>417</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s">
-        <v>427</v>
+        <v>346</v>
       </c>
       <c r="F91" t="s">
-        <v>428</v>
+        <v>347</v>
       </c>
       <c r="G91" t="s">
-        <v>429</v>
+        <v>348</v>
       </c>
       <c r="H91" t="s">
-        <v>430</v>
+        <v>349</v>
       </c>
       <c r="I91" t="s">
-        <v>431</v>
+        <v>350</v>
       </c>
       <c r="J91" s="9"/>
       <c r="K91" s="4" t="s">
@@ -5050,23 +5060,23 @@
         <v>14</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>499</v>
+        <v>418</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s">
-        <v>432</v>
+        <v>351</v>
       </c>
       <c r="F92" t="s">
-        <v>433</v>
+        <v>352</v>
       </c>
       <c r="G92" t="s">
-        <v>434</v>
+        <v>353</v>
       </c>
       <c r="H92" t="s">
-        <v>435</v>
+        <v>354</v>
       </c>
       <c r="I92" t="s">
-        <v>436</v>
+        <v>355</v>
       </c>
       <c r="J92" s="9"/>
       <c r="K92" s="4" t="s">
@@ -5087,23 +5097,23 @@
         <v>14</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>500</v>
+        <v>419</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s">
-        <v>437</v>
+        <v>356</v>
       </c>
       <c r="F93" t="s">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="G93" t="s">
-        <v>439</v>
+        <v>358</v>
       </c>
       <c r="H93" t="s">
-        <v>440</v>
+        <v>359</v>
       </c>
       <c r="I93" t="s">
-        <v>441</v>
+        <v>360</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="4" t="s">
@@ -5122,23 +5132,23 @@
         <v>14</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>501</v>
+        <v>420</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s">
-        <v>403</v>
+        <v>322</v>
       </c>
       <c r="F94" t="s">
-        <v>442</v>
+        <v>361</v>
       </c>
       <c r="G94" t="s">
-        <v>443</v>
+        <v>362</v>
       </c>
       <c r="H94" t="s">
-        <v>444</v>
+        <v>363</v>
       </c>
       <c r="I94" t="s">
-        <v>445</v>
+        <v>364</v>
       </c>
       <c r="J94" s="9"/>
       <c r="K94" s="4" t="s">
@@ -5159,23 +5169,23 @@
         <v>14</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>502</v>
+        <v>421</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s">
-        <v>446</v>
+        <v>365</v>
       </c>
       <c r="F95" t="s">
-        <v>447</v>
+        <v>366</v>
       </c>
       <c r="G95" t="s">
-        <v>448</v>
+        <v>367</v>
       </c>
       <c r="H95" t="s">
-        <v>405</v>
+        <v>324</v>
       </c>
       <c r="I95" t="s">
-        <v>406</v>
+        <v>325</v>
       </c>
       <c r="J95" s="9"/>
       <c r="K95" s="4" t="s">

--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB45AA3-4396-4B99-A411-14379C0C6DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6314C4-0FBE-40A0-8FEB-D081C59B33AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="505">
   <si>
     <t>Option 1</t>
   </si>
@@ -712,15 +712,6 @@
     <t>$3. t_{1/2}$</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;b&gt;Exercice 5&lt;/b&gt; :   $\quad$ Désintégration du potassium 40&lt;br&gt;
-88% des noyaux de potassium ${}_{19}^{40}K$ se transforment en calcium ${}_{20}^{40}Ca. C’est une désintégration 
-radioactive de type $\beta^-$. 
-&lt;br&gt;La figure ci-dessous représente les variation de potassium et calcium en fonction du temps. 
-&lt;br&gt;&lt;img src="/images/CB1_Q13.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-&lt;br&gt;On donne : ln(2)=0,7.
-</t>
-  </si>
-  <si>
     <t>$N_{0}.(2-e^{-\lambda.t})$</t>
   </si>
   <si>
@@ -902,9 +893,6 @@
  Séparés par électrophorèse, le profile attendu correspondra à :</t>
   </si>
   <si>
-    <t>La date lorsque $$\frac{m(^{206}_{82}\text{Pb}(t))}{m(^{238}_{92}\text{U}(t))} = 2{,}6$$ en fonction de $t_{1/2}$ est :</t>
-  </si>
-  <si>
     <t>La date lorsque $N(C_a)(t) = \frac {7}{8} \cdot N_0$ est:</t>
   </si>
   <si>
@@ -1241,21 +1229,12 @@
     <t>C : $2i \cos(\frac{a-b}{2}) e^{i \frac{a+b}{2}}$.</t>
   </si>
   <si>
-    <t>A : $ \cot(\frac{a-b}{2}) e^{i(a+b)}$.</t>
-  </si>
-  <si>
-    <t>Les nombres complexes $sin(\teta) + i cos(2.\teta)$ et $cos(\teta) - i sin(2.\teta) sont conjugués l’un à l’autre pour $\teta$ égale à :</t>
-  </si>
-  <si>
     <t>A : $n\pi$.</t>
   </si>
   <si>
     <t>B : $(n + \frac{1}{2})\pi$.</t>
   </si>
   <si>
-    <t>E : aucune valeur de $\teta$.</t>
-  </si>
-  <si>
     <t>On a pour $n \in \mathbb{N}^*$, $\lim_{x \to e} \frac{\ln(x^n) - n}{x - e}$ est égale à :</t>
   </si>
   <si>
@@ -1274,15 +1253,9 @@
     <t>E : $0$</t>
   </si>
   <si>
-    <t>Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour $$\ln(3x)&gt;\ln(2-5x)$$ est:</t>
-  </si>
-  <si>
     <t>L’ensemble des solutions de l’inéquation $(1 - 0.02)^{x} \leq 0,5$ est:</t>
   </si>
   <si>
-    <t>La primitive $F$ de la fonction $f$ définie sur l’intervalle $I=]0,+\infty[$ par $f(x) = \frac{2x^3 + 3 - x}{x}, telle que : $F(1)=1$ vérifiée est :</t>
-  </si>
-  <si>
     <t>A : $\frac{x^2 - 1 +3 \ln(x)}{3} $</t>
   </si>
   <si>
@@ -1307,9 +1280,6 @@
     <t>D : $\ln(\frac{2}{n})$.</t>
   </si>
   <si>
-    <t>On a pour $n \in \mathbb{N}^*$, $x \in \mathbb{R}$, $\lim_{x \to +\infty} (\frac{\ln(nx)}{e^{nx})^2$ est égale à :</t>
-  </si>
-  <si>
     <t>Soit $\lambda$ un nombre complexe non nul et diffèrent de 1, on définit pour tout entier naturel n , la suite $(Z_n)$ de nombre complexe par : $Z_{n+1} - \lambda Z_n = i$ et $Z_0 = 0$ , alors l’égalité correcte est :</t>
   </si>
   <si>
@@ -1328,9 +1298,6 @@
     <t>E : $Z_3 = (\lambda^2 + \lambda + 1)i$.</t>
   </si>
   <si>
-    <t>Si $(\forall x \in \mathbb{R})$, $f(x)=(e^\sqrt{x} - 1).(\sqrt{x} + e^x).(e^{2x} + 1).(x - 1)$, alors $f'(1)$ est égale à :</t>
-  </si>
-  <si>
     <t>C : $e^4 - 1$</t>
   </si>
   <si>
@@ -1391,273 +1358,312 @@
     <t>Soit $(v_n)$ la suite définit par : $v_{n+1} = \ln(\frac{u_{n+1}}{9}) = \frac{1}{2}v_n$ et $u_0 = 9e$, pour tout entier naturel n. Alors la limite de $u_n$ vaut :</t>
   </si>
   <si>
+    <t>B : $(Al^{3+}/Al)$ et $(H_3O^+/H_2)$.</t>
+  </si>
+  <si>
+    <t>E : $(Al/Al^{3+})$ et $(H_2/H_{2O})$.</t>
+  </si>
+  <si>
+    <t>A : $-18,5.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
+  </si>
+  <si>
+    <t>B : $18,5.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
+  </si>
+  <si>
+    <t>C : $-9,25.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
+  </si>
+  <si>
+    <t>D : $9,25.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
+  </si>
+  <si>
+    <t>Les couples (Ox/Red) participant à cette réaction sont :</t>
+  </si>
+  <si>
+    <t>La valeur de $m(Al)$ est :</t>
+  </si>
+  <si>
+    <t>La valeur de la vitesse volumique a l’instant $t=0s$ est :</t>
+  </si>
+  <si>
+    <t>A : $H_3O^+, cl^{-1}, Na^+$</t>
+  </si>
+  <si>
+    <t>B : $HCO_2^-, H_3O^+, Na^+$</t>
+  </si>
+  <si>
+    <t>C : $HCO_2^-, cl^{-1}, Na^+$</t>
+  </si>
+  <si>
+    <t>D : $HO^-, H_3O^+, Na^+$.</t>
+  </si>
+  <si>
+    <t>E : $HCO_2^-, HO^-, Na^+$</t>
+  </si>
+  <si>
+    <t>Les ions présent dans le mélange à un instant t sont :</t>
+  </si>
+  <si>
+    <t>Sachant que $G_{max} = 1,06 mS$, la valeur de $X_{max}$ est :</t>
+  </si>
+  <si>
+    <t>A : $10^{-3} mol$</t>
+  </si>
+  <si>
+    <t>B : $3.10^{-2} mol$</t>
+  </si>
+  <si>
+    <t>C : $4.10^{-3} mol$</t>
+  </si>
+  <si>
+    <t>D : $2.10^{-3} mol$</t>
+  </si>
+  <si>
+    <t>E : $10^{-2} mol$</t>
+  </si>
+  <si>
+    <t>La valeur de $G_{t1/2}$ égale :</t>
+  </si>
+  <si>
+    <t>B : $3.10^{-2} S$</t>
+  </si>
+  <si>
+    <t>A : $10^{-3} mS$</t>
+  </si>
+  <si>
+    <t>C : $1,78 mS$</t>
+  </si>
+  <si>
+    <t>D : $1,87 mS$</t>
+  </si>
+  <si>
+    <t>E : $10^{-4} S$</t>
+  </si>
+  <si>
+    <t>La valeur de $[HCO_2CH_3]$ à $t_{1/2}$ égale :</t>
+  </si>
+  <si>
+    <t>A : $5 mol.cm^{-3}$.</t>
+  </si>
+  <si>
+    <t>B : $5 mol.mm^{-3}$.</t>
+  </si>
+  <si>
+    <t>C : $5 mmol.m^{-3}$.</t>
+  </si>
+  <si>
+    <t>D : $5 mol.L^{-1}$.</t>
+  </si>
+  <si>
+    <t>E : $5 mol.m^{-3}$.</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 3 : $\quad$ Dissolution de l’ammoniac dans l’eau&lt;/b&gt;&lt;br&gt;
+&lt;br&gt;On considère une solution aqueuse $(S_b)$ d’ammoniac $NH_3$ avec taux d’avancement $\tau = 2,5\%$.
+&lt;br&gt;On donne : $\log 25 = 1,4$ , $\quad$ $\frac{975}{25} = 39$; $\quad$ $\log 39 = 1,6$</t>
+  </si>
+  <si>
+    <t>Le taux d’avancement a pour expression :</t>
+  </si>
+  <si>
+    <t>A : $\frac{10^{-pH}}{C_b. K_e}$</t>
+  </si>
+  <si>
+    <t>B : $\frac{10^{pH}}{C_b. K_e}$</t>
+  </si>
+  <si>
+    <t>C : $\frac{10^{-pH}.K_e}{C_b}$</t>
+  </si>
+  <si>
+    <t>D : $\frac{10^{pH}.K_e}{C_b}$</t>
+  </si>
+  <si>
+    <t>E : $\frac{10^{-pH}.C_b}{K_e}$</t>
+  </si>
+  <si>
+    <t>Sachant que $C_b = 2,5.10^{-2} mol.L^{-1}$, la valeur de $pH$ est :</t>
+  </si>
+  <si>
+    <t>E : $10,8$</t>
+  </si>
+  <si>
+    <t>D : $11,8$</t>
+  </si>
+  <si>
+    <t>C : $12,4$</t>
+  </si>
+  <si>
+    <t>B : $10$</t>
+  </si>
+  <si>
+    <t>A : $10,4$</t>
+  </si>
+  <si>
+    <t>La constante d’acidité $K_a$ du couple $(NH_4^+/NH_3)$ a pour expression :</t>
+  </si>
+  <si>
+    <t>A : $\frac{1-\tau}{10^{pH}.\tau}$</t>
+  </si>
+  <si>
+    <t>B : $\frac{1-\tau}{10^{-pH}.\tau}$</t>
+  </si>
+  <si>
+    <t>C : $\frac{10^{pH}.\tau}{1-\tau}$</t>
+  </si>
+  <si>
+    <t>D : $\frac{10^{-pH}.\tau}{1-\tau}$</t>
+  </si>
+  <si>
+    <t>E : $\frac{10^{-pH}.\tau}{\tau - 1}$</t>
+  </si>
+  <si>
+    <t>La valeur de $pK_a$ est :</t>
+  </si>
+  <si>
+    <t>B : $9,2$</t>
+  </si>
+  <si>
+    <t>C : $9,4$</t>
+  </si>
+  <si>
+    <t>D : $9,8$</t>
+  </si>
+  <si>
+    <t>E : $9,6$</t>
+  </si>
+  <si>
+    <t>A : $4,9    mol$.</t>
+  </si>
+  <si>
+    <t>B : $490    mmol$.</t>
+  </si>
+  <si>
+    <t>C : $49    mmol$.</t>
+  </si>
+  <si>
+    <t>D : $0,49    mmol$.</t>
+  </si>
+  <si>
+    <t>E : $4,9    mmol$.</t>
+  </si>
+  <si>
+    <t>Les deux courbes se croisent lorsque $V_b$ égale :</t>
+  </si>
+  <si>
+    <t>La valeur de la masse $m'$ de l’acide benzoique égale :</t>
+  </si>
+  <si>
+    <t>Sachant que la constante d’équilibre de la réaction de dosage est $K = 10^{9.8}$, la valeur de $pK_a$ est :</t>
+  </si>
+  <si>
+    <t>E : $\frac{1}{10^{-\frac{pK_{a1}}{2}}-10^{-\frac{pK_{a2}}{2}}}$</t>
+  </si>
+  <si>
+    <t>La valeur de taux d’avancement égale :</t>
+  </si>
+  <si>
+    <t>La valeur de $pH$ du mélange à l’équilibre est :</t>
+  </si>
+  <si>
+    <t>Le taux d’avancement $\tau'$ a pour expression :</t>
+  </si>
+  <si>
+    <t>E : $\frac{10^{pH'+pH-1}}{1+10^{pK_a-pH'}}$</t>
+  </si>
+  <si>
+    <t>D : $\frac{10^{1-pH'-pH}}{1+10^{pH-pK_a}}$</t>
+  </si>
+  <si>
+    <t>C : $\frac{10^{1-pH'+pH}}{1+10^{pH-pK_a}}$</t>
+  </si>
+  <si>
+    <t>B : $\frac{10^{1+pH'-pH}}{1+10^{pK_a-pH}}$</t>
+  </si>
+  <si>
+    <t>A : $\frac{10^{1-pH'+pH}}{1+10^{pK_a-pH}}$</t>
+  </si>
+  <si>
+    <t>La valeur de $\tau'$ est :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Exercice 5&lt;/b&gt; :   $\quad$ Désintégration du potassium 40&lt;br&gt;
+88% des noyaux de potassium ${}_{19}^{40}K$ se transforment en calcium ${}_{20}^{40}Ca$. C’est une désintégration 
+radioactive de type $\beta^-$. 
+&lt;br&gt;La figure ci-dessous représente les variation de potassium et calcium en fonction du temps. 
+&lt;br&gt;&lt;img src="/images/CB1_Q13.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;On donne : ln(2)=0,7.
+</t>
+  </si>
+  <si>
+    <t>La date lorsque $\frac{m(^{206}_{82}\text{Pb}(t))}{m(^{238}_{92}\text{U}(t))} = 2{,}6$ en fonction de $t_{1/2}$ est :</t>
+  </si>
+  <si>
     <t>&lt;b&gt;Exercice 6 &lt;/b&gt; : $\quad$ L’activité du radon 222 &lt;br&gt;
-Un noyau radioactif de radon $^{222}_{86}\text{Rn}$ se désintègre en émettant une particule $\alpha$ et noyau fils  $$^{218}_{84}\text{Po}$$. 
+Un noyau radioactif de radon $^{222}_{86}\text{Rn}$ se désintègre en émettant une particule $\alpha$ et noyau fils  $^{218}_{84}\text{Po}$. 
 La figure ci-dessous représente les variations de la fonction Y(t) tel que : $Y(t) = N_{Pₒ}(t) − N_{Rn}(t)$.
 &lt;br&gt;&lt;img src="/images/CB1_Q14.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;On donne :   $5,8.10^{-4} = \frac{50}{3600  .  24}$ $\quad$ In(2) = 0,7 $\quad$ et $\quad$ 0,18 . 5,8 = 1,044</t>
   </si>
   <si>
-    <t>B : $(Al^{3+}/Al)$ et $(H_3O^+/H_2)$.</t>
-  </si>
-  <si>
-    <t>E : $(Al/Al^{3+})$ et $(H_2/H_{2O})$.</t>
-  </si>
-  <si>
-    <t>A : $-18,5.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
-  </si>
-  <si>
-    <t>B : $18,5.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
-  </si>
-  <si>
-    <t>C : $-9,25.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
-  </si>
-  <si>
-    <t>D : $9,25.10^{-3} mol.L^{-1}.mn^{-1}$.</t>
-  </si>
-  <si>
-    <t>Les couples (Ox/Red) participant à cette réaction sont :</t>
-  </si>
-  <si>
-    <t>La valeur de $m(Al)$ est :</t>
-  </si>
-  <si>
-    <t>La valeur de la vitesse volumique a l’instant $t=0s$ est :</t>
+    <t>&lt;b&gt;Exercice 1 : Suivi temporel d’une transformation chimique&lt;/b&gt;&lt;br&gt;
+&lt;br&gt;À l’instant t=0 , on introduit une masse $m_0 = 27mg$ d’Aluminium ($Al_{(s)}$)
+dans un ballon contenant $V = 20mL$ d’une solution d’acide chlorhydrique ($H_3O^+_{(aq)} + Cl^-_{(aq)}$) de concentration $C_0$.
+&lt;br&gt; On a : $6H_3O^+_{(aq)} + 2Al_{(s)} \longrightarrow 3H_{2(g)} + 2Al^{3+}_{(aq)} + 6H_2O_{(l)}$
+&lt;br&gt; On donne : $M(Al) = 27 g.mol^{-1}$ , $\quad$ $\frac{2}{54} = 0, 0185$, $\quad$ 20x27 = 540, $\quad$ 27x440 = 540x22, $\quad$ $\frac{1}{44} = 0, 0227$
+&lt;br&gt;&lt;img src="/images/CB1_Q17.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
   <si>
     <t>&lt;b&gt;Exercice 2 : $\quad$ conductimétrie&lt;/b&gt;&lt;br&gt;
 On verse dans un bécher un volume $V = 2.10^{-4} m^3$ d’une solution $(S_B)$ d’hydroxyde de sodium de concentration molaire $C_B$ , et on y ajoute à l’instant $t=0$, considéré comme origine des temps, une quantité de matière $n_E$ du méthanoate de méthyle égale à la quantité de matière $n_B$ d’hydroxyde de sodium ($n_E=n_B$). (On considère que le volume reste constant $V$).
 &lt;br&gt;On donne : $HCOOCH_{3(aq)} + HO^-_{(aq)} \longrightarrow HCOO^-_{(aq)} + CH_3OH_{(aq)}$
-&lt;br&gt; G(t) =0,72. X(t) + 2,5.10^{-3} en (S), $\lambda_{HO^-} + \lambda_{Na^+} = 25 mS. m^2. mol^{-1}$ , $\lambda_{HO^-} - \lambda_{HCO_2^-} = 14,4 mS. m^2. mol^{-1}$</t>
-  </si>
-  <si>
-    <t>A : $H_3O^+, cl^{-1}, Na^+$</t>
-  </si>
-  <si>
-    <t>B : $HCO_2^-, H_3O^+, Na^+$</t>
-  </si>
-  <si>
-    <t>C : $HCO_2^-, cl^{-1}, Na^+$</t>
-  </si>
-  <si>
-    <t>D : $HO^-, H_3O^+, Na^+$.</t>
-  </si>
-  <si>
-    <t>E : $HCO_2^-, HO^-, Na^+$</t>
-  </si>
-  <si>
-    <t>Les ions présent dans le mélange à un instant t sont :</t>
-  </si>
-  <si>
-    <t>Sachant que $G_{max} = 1,06 mS$, la valeur de $X_{max}$ est :</t>
-  </si>
-  <si>
-    <t>A : $10^{-3} mol$</t>
-  </si>
-  <si>
-    <t>B : $3.10^{-2} mol$</t>
-  </si>
-  <si>
-    <t>C : $4.10^{-3} mol$</t>
-  </si>
-  <si>
-    <t>D : $2.10^{-3} mol$</t>
-  </si>
-  <si>
-    <t>E : $10^{-2} mol$</t>
-  </si>
-  <si>
-    <t>La valeur de $G_{t1/2}$ égale :</t>
-  </si>
-  <si>
-    <t>B : $3.10^{-2} S$</t>
-  </si>
-  <si>
-    <t>A : $10^{-3} mS$</t>
-  </si>
-  <si>
-    <t>C : $1,78 mS$</t>
-  </si>
-  <si>
-    <t>D : $1,87 mS$</t>
-  </si>
-  <si>
-    <t>E : $10^{-4} S$</t>
-  </si>
-  <si>
-    <t>La valeur de $[HCO_2CH_3]$ à $t_{1/2}$ égale :</t>
-  </si>
-  <si>
-    <t>A : $5 mol.cm^{-3}$.</t>
-  </si>
-  <si>
-    <t>B : $5 mol.mm^{-3}$.</t>
-  </si>
-  <si>
-    <t>C : $5 mmol.m^{-3}$.</t>
-  </si>
-  <si>
-    <t>D : $5 mol.L^{-1}$.</t>
-  </si>
-  <si>
-    <t>E : $5 mol.m^{-3}$.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Exercice 3 : $\quad$ Dissolution de l’ammoniac dans l’eau&lt;/b&gt;&lt;br&gt;
-&lt;br&gt;On considère une solution aqueuse $(S_b)$ d’ammoniac $NH_3$ avec taux d’avancement $\tau = 2,5\%$.
-&lt;br&gt;On donne : $\log 25 = 1,4$ , $\quad$ $\frac{975}{25} = 39$; $\quad$ $\log 39 = 1,6$</t>
-  </si>
-  <si>
-    <t>Le taux d’avancement a pour expression :</t>
-  </si>
-  <si>
-    <t>A : $\frac{10^{-pH}}{C_b. K_e}$</t>
-  </si>
-  <si>
-    <t>B : $\frac{10^{pH}}{C_b. K_e}$</t>
-  </si>
-  <si>
-    <t>C : $\frac{10^{-pH}.K_e}{C_b}$</t>
-  </si>
-  <si>
-    <t>D : $\frac{10^{pH}.K_e}{C_b}$</t>
-  </si>
-  <si>
-    <t>E : $\frac{10^{-pH}.C_b}{K_e}$</t>
-  </si>
-  <si>
-    <t>Sachant que $C_b = 2,5.10^{-2} mol.L^{-1}$, la valeur de $pH$ est :</t>
-  </si>
-  <si>
-    <t>E : $10,8$</t>
-  </si>
-  <si>
-    <t>D : $11,8$</t>
-  </si>
-  <si>
-    <t>C : $12,4$</t>
-  </si>
-  <si>
-    <t>B : $10$</t>
-  </si>
-  <si>
-    <t>A : $10,4$</t>
-  </si>
-  <si>
-    <t>La constante d’acidité $K_a$ du couple $(NH_4^+/NH_3)$ a pour expression :</t>
-  </si>
-  <si>
-    <t>A : $\frac{1-\tau}{10^{pH}.\tau}$</t>
-  </si>
-  <si>
-    <t>B : $\frac{1-\tau}{10^{-pH}.\tau}$</t>
-  </si>
-  <si>
-    <t>C : $\frac{10^{pH}.\tau}{1-\tau}$</t>
-  </si>
-  <si>
-    <t>D : $\frac{10^{-pH}.\tau}{1-\tau}$</t>
-  </si>
-  <si>
-    <t>E : $\frac{10^{-pH}.\tau}{\tau - 1}$</t>
-  </si>
-  <si>
-    <t>La valeur de $pK_a$ est :</t>
-  </si>
-  <si>
-    <t>B : $9,2$</t>
-  </si>
-  <si>
-    <t>C : $9,4$</t>
-  </si>
-  <si>
-    <t>D : $9,8$</t>
-  </si>
-  <si>
-    <t>E : $9,6$</t>
+&lt;br&gt; G(t) =$0,72. X(t) + 2,5.10^{-3}$ en (S), $\lambda_{HO^-} + \lambda_{Na^+} = 25 mS. m^2. mol^{-1}$ , $\lambda_{HO^-} - \lambda_{HCO_2^-} = 14,4 mS. m^2. mol^{-1}$</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 6 : $\quad$ Réaction de l’acide éthanoïque avec l’ammoniac&lt;/b&gt;&lt;br&gt;
+&lt;br&gt;On prépare un mélange (S) de volume $V$, en introduisant $n_1 = 10^{-3} mol$ d’acide éthanoïque $CH_3COOH$ et $n_2 = 10^{-3} mol$ d’ammoniac $NH_3$, dans un récipient contenant de l’eau distillée. 
+&lt;br&gt;On donne : $pK_a du couple (CH_3COOH/CH_3COO^-) = pK_{a1} = 4,8$ $\quad$ et $\quad$ $pK_a du couple (NH_4^+/NH_3) = pK_{a2} = 9,2$ $\quad$ et $\quad$ $1 - 10^{-2,2} = 1$</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Exercice 7 : $\quad$ Dilution d’acide méthanoïque&lt;/b&gt;&lt;br&gt;
+&lt;br&gt;On dissout une quantité $n$ de l’acide méthanoïque HCOOH dans l’eau distillée pour obtenir une solution aqueuse (S) de volume $V$. on mesure la valeur de $pH$ et on trouve que $pH = 2,91$. Après on dilue 10 fois la solution (S) on obtient une solution (S’) avec $pH' = 3,4$. 
+&lt;br&gt;On donne : $pK_a = 3,75$; $\quad$ $10^{0,51} = 3$;  $\quad$ $10^{0,84} = 6,5$</t>
+  </si>
+  <si>
+    <t>Mathématique</t>
   </si>
   <si>
     <t>&lt;b&gt;Exercice 4 : $\quad$ Dilution de la solution commerciale &lt;/b&gt;&lt;br&gt;
-Sur l’étiquette d’une bouteille d’acide chlorhydrique commercial, on lit les indications suivantes : « Acide chlorhydrique, masse volumique : $\rho = 1190 Kg.m^{-3}$ ; pourcentage en masse d’acide pur : $p = 37\%$ ; masse molaire de chlorure d’hydrogène HCl : $M = 36,5 g.mol^{-1}$ ». On extrait de cette bouteille $V_0 = 4,1 mL$ d’acide, que l’on complète à $V_1 = 500 mL$ avec de l’eau distillée.
+Sur l’étiquette d’une bouteille d’acide chlorhydrique commercial, on lit les indications suivantes : 
+&lt;br&gt;« Acide chlorhydrique, masse volumique : $\rho = 1190 Kg.m^{-3}$ ; pourcentage en masse d’acide pur : $p = 37\%$ ; masse molaire de chlorure d’hydrogène HCl : $M = 36,5 g.mol^{-1}$ ». 
+&lt;br&gt;On extrait de cette bouteille $V_0 = 4,1 mL$ d’acide, que l’on complète à $V_1 = 500 mL$ avec de l’eau distillée.
 &lt;br&gt; On donne : 37 x 1,19 x 4,1 = 36,5 x 4,9
 &lt;br&gt;Le nombre de moles du soluté dans $4,1 mL$ de la solution commerciale vaut :</t>
   </si>
   <si>
-    <t>A : $4,9    mol$.</t>
-  </si>
-  <si>
-    <t>B : $490    mmol$.</t>
-  </si>
-  <si>
-    <t>C : $49    mmol$.</t>
-  </si>
-  <si>
-    <t>D : $0,49    mmol$.</t>
-  </si>
-  <si>
-    <t>E : $4,9    mmol$.</t>
-  </si>
-  <si>
-    <t>Les deux courbes se croisent lorsque $V_b$ égale :</t>
-  </si>
-  <si>
-    <t>La valeur de la masse $m'$ de l’acide benzoique égale :</t>
-  </si>
-  <si>
-    <t>Sachant que la constante d’équilibre de la réaction de dosage est $K = 10^{9.8}$, la valeur de $pK_a$ est :</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Exercice 6 : $\quad$ Réaction de l’acide éthanoïque avec l’ammoniac&lt;/b&gt;&lt;br&gt;
-&lt;br&gt;On prépare un mélange (S) de volume $V$, en introduisant $n_1 = 10^{-3} mol$ d’acide éthanoïque $CH_3COOH$ et $n_2 = 10^{-3} mol$ d’ammoniac $NH_3$, dans un récipient contenant de l’eau distillée. 
-&lt;br&gt;On donne : pK_a du couple (CH_3COOH/CH_3COO^-) = $pK_{a1} = 4,8$ $\quad$ et $\quad$ pK_a du couple (NH_4^+/NH_3) = $pK_{a2} = 9,2$ $\quad$ et $\quad$ $1 - 10^{2,2} = 1$</t>
-  </si>
-  <si>
-    <t>E : $\frac{1}{10^{-\frac{pK_{a1}}{2}}-10^{-\frac{pK_{a2}}{2}}}$</t>
-  </si>
-  <si>
-    <t>La valeur de taux d’avancement égale :</t>
-  </si>
-  <si>
-    <t>La valeur de $pH$ du mélange à l’équilibre est :</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Exercice 7 : $\quad$ Dilution d’acide méthanoïque&lt;/b&gt;&lt;br&gt;
-&lt;br&gt;On dissout une quantité $n$ de l’acide méthanoïque HCOOH dans l’eau distillée pour obtenir une solution aqueuse (S) de volume $V$. on mesure la valeur de $pH$ et on trouve que $pH = 2,91$. Après on dilue 10 fois la solution (S) on obtient une solution (S’) avec $pH' = 3,4$. 
-&lt;br&gt;On donne : $pK_a = 3,75$; $\quad$ $10^0,51 = 3$;  $\quad$ $10^0,84 = 6,5$</t>
-  </si>
-  <si>
-    <t>Le taux d’avancement $\tau'$ a pour expression :</t>
-  </si>
-  <si>
-    <t>E : $\frac{10^{pH'+pH-1}}{1+10^{pK_a-pH'}}$</t>
-  </si>
-  <si>
-    <t>D : $\frac{10^{1-pH'-pH}}{1+10^{pH-pK_a}}$</t>
-  </si>
-  <si>
-    <t>C : $\frac{10^{1-pH'+pH}}{1+10^{pH-pK_a}}$</t>
-  </si>
-  <si>
-    <t>B : $\frac{10^{1+pH'-pH}}{1+10^{pK_a-pH}}$</t>
-  </si>
-  <si>
-    <t>A : $\frac{10^{1-pH'+pH}}{1+10^{pK_a-pH}}$</t>
-  </si>
-  <si>
-    <t>La valeur de $\tau'$ est :</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Exercice 5 : $\quad$ Dosage de l’acide benzoïque&lt;/b&gt;&lt;br&gt;
-&lt;br&gt;On dissout une masse $m'$ d’une poudre d’acide benzoique dans un volume $V_e = 1 L$ d’eau pour obtenir une solution aqueuse (S). On titre un volume $V_a = 10 mL$ de la solution (S) par une solution aqueuse d’hydroxyde de sodium de concentration $C_b = 10 mmol.L^{-1}$. La figure ci-dessous représente Le diagramme de distribution en fonction de $V_b$ le volume versé lors de titrage. On donne : $M(C_6H_5COOH) = 122 g.mol^{-1}$.
+&lt;br&gt;On dissout une masse $m'$ d’une poudre d’acide benzoique dans un volume $V_e = 1 L$ d’eau pour obtenir une solution aqueuse (S). On titre un volume $V_a = 10 mL$ de la solution (S) par une solution aqueuse d’hydroxyde de sodium de concentration $C_b = 10 mmol.L^{-1}$. La figure ci-dessous représente Le diagramme de distribution en fonction de $V_b$ le volume versé lors de titrage. 
+&lt;br&gt;On donne : $M(C_6H_5COOH) = 122 g.mol^{-1}$.
 &lt;br&gt;&lt;img src="/images/CB1_Q18.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
   <si>
-    <t>&lt;b&gt;Exercice 1 : Suivi temporel d’une transformation chimique&lt;/b&gt;&lt;br&gt;
-À l’instant t=0 , on introduit une masse $m_0 = 27mg$ d’Aluminium ($Al_{(s)}$)
-dans un ballon contenant $V = 20mL$ d’une solution d’acide chlorhydrique ($H_3O^+_{(aq)} + Cl^-_{(aq)}$) de concentration $C_0$.
-&lt;br&gt; On a : $6H_3O^+_{(aq)} + 2Al_{(s)} \longrightarrow 3H_{2(g)} + 2Al^{3+}_{(aq)} + 6H_2O_{(l)}$
-&lt;br&gt; On donne : $M(Al) = 27 g.mol^{-1}$ , $\frac{2}{54} = 0, 0185$ , 20x27 = 540, 27x440 = 540x22 , $\frac{1}{44} = 0, 0227
-&lt;br&gt;&lt;img src="/images/CB1_Q17.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+    <t>A : $ \cos(\frac{a-b}{2}) e^{i(a+b)}$.</t>
+  </si>
+  <si>
+    <t>Les nombres complexes $sin(\theta) + i cos(2.\theta)$ et $cos(\theta) - i sin(2.\theta) sont conjugués l’un à l’autre pour $\theta$ égale à :</t>
+  </si>
+  <si>
+    <t>E : aucune valeur de $\theta$.</t>
+  </si>
+  <si>
+    <t>Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour $\ln(3x)&gt;\ln(2-5x)$ est:</t>
+  </si>
+  <si>
+    <t>La primitive $F$ de la fonction $f$ définie sur l’intervalle $I=]0,+\infty[$ par $f(x) = \frac{2x^3 + 3 - x}{x}$, telle que : $F(1)=1$ vérifiée est :</t>
+  </si>
+  <si>
+    <t>On a pour $n \in \mathbb{N}^*$, $x \in \mathbb{R}$, $\lim_{x \to +\infty}$ $(\frac{\ln(nx)}{e^{nx})^2$ est égale à :</t>
+  </si>
+  <si>
+    <t>Si $(\forall x \in \mathbb{R}^+)$, $f(x) = (e^{\sqrt{x}} - 1)(\sqrt{x} + e^x)(e^{2x} + 1)(x - 1)$, alors $f'(1)$ est égal à :</t>
   </si>
 </sst>
 </file>
@@ -2385,19 +2391,19 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="4" t="s">
@@ -2566,7 +2572,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="3" t="s">
@@ -2825,7 +2831,7 @@
         <v>14</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3" t="s">
@@ -2892,10 +2898,10 @@
         <v>125</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>126</v>
@@ -2920,19 +2926,19 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="4"/>
@@ -3258,10 +3264,10 @@
         <v>198</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="4"/>
@@ -3278,7 +3284,7 @@
         <v>136</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>259</v>
+        <v>489</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="3" t="s">
@@ -3311,7 +3317,7 @@
         <v>135</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>203</v>
+        <v>488</v>
       </c>
       <c r="D37" s="2"/>
       <c r="J37" s="2"/>
@@ -3333,19 +3339,19 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>129</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="4"/>
@@ -3362,23 +3368,23 @@
         <v>136</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="4"/>
@@ -3393,7 +3399,7 @@
         <v>135</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>422</v>
+        <v>490</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="3"/>
@@ -3425,16 +3431,16 @@
         <v>130</v>
       </c>
       <c r="F41" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="I41" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J41" s="2"/>
       <c r="M41" s="5">
@@ -3449,23 +3455,23 @@
         <v>136</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="H42" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="4"/>
@@ -3480,7 +3486,7 @@
         <v>135</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="3"/>
@@ -3509,19 +3515,19 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>131</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="J44" s="2"/>
       <c r="M44" s="5">
@@ -3540,16 +3546,16 @@
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>132</v>
@@ -3567,7 +3573,7 @@
         <v>135</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="3"/>
@@ -3596,19 +3602,19 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>265</v>
       </c>
       <c r="J47" s="2"/>
       <c r="M47" s="4">
@@ -3623,23 +3629,23 @@
         <v>136</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="G48" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="H48" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="I48" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="4"/>
@@ -3663,16 +3669,16 @@
         <v>133</v>
       </c>
       <c r="F49" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="H49" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="4"/>
@@ -3681,7 +3687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>1</v>
       </c>
@@ -3689,7 +3695,7 @@
         <v>135</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="3"/>
@@ -3699,7 +3705,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="9"/>
       <c r="K50" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>17</v>
@@ -3714,23 +3720,23 @@
         <v>136</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" t="s">
+        <v>264</v>
+      </c>
+      <c r="F51" t="s">
+        <v>413</v>
+      </c>
+      <c r="G51" t="s">
+        <v>265</v>
+      </c>
+      <c r="H51" t="s">
         <v>266</v>
       </c>
-      <c r="F51" t="s">
-        <v>423</v>
-      </c>
-      <c r="G51" t="s">
-        <v>267</v>
-      </c>
-      <c r="H51" t="s">
-        <v>268</v>
-      </c>
       <c r="I51" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="J51" s="2"/>
       <c r="M51" s="4">
@@ -3745,23 +3751,23 @@
         <v>136</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s">
+        <v>267</v>
+      </c>
+      <c r="F52" t="s">
+        <v>268</v>
+      </c>
+      <c r="G52" t="s">
         <v>269</v>
       </c>
-      <c r="F52" t="s">
+      <c r="H52" t="s">
         <v>270</v>
       </c>
-      <c r="G52" t="s">
+      <c r="I52" t="s">
         <v>271</v>
-      </c>
-      <c r="H52" t="s">
-        <v>272</v>
-      </c>
-      <c r="I52" t="s">
-        <v>273</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="4"/>
@@ -3778,23 +3784,23 @@
         <v>136</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="F53" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="G53" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="H53" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="I53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="4"/>
@@ -3811,7 +3817,7 @@
         <v>135</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>432</v>
+        <v>492</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="3"/>
@@ -3821,7 +3827,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>17</v>
@@ -3836,28 +3842,30 @@
         <v>136</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="F55" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="G55" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="H55" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="I55" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="12"/>
       <c r="L55" s="12"/>
-      <c r="M55" s="5"/>
+      <c r="M55" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
@@ -3867,28 +3875,30 @@
         <v>136</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="F56" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="G56" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="H56" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="I56" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="12"/>
       <c r="L56" s="12"/>
-      <c r="M56" s="5"/>
+      <c r="M56" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
@@ -3898,23 +3908,23 @@
         <v>136</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="F57" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="G57" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="H57" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="I57" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="J57" s="3"/>
       <c r="M57" s="5">
@@ -3929,23 +3939,23 @@
         <v>136</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F58" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G58" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="H58" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="I58" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="4"/>
@@ -3962,7 +3972,7 @@
         <v>135</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="3"/>
@@ -3972,7 +3982,7 @@
       <c r="I59" s="3"/>
       <c r="J59" s="2"/>
       <c r="K59" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>17</v>
@@ -3987,23 +3997,23 @@
         <v>136</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="F60" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="G60" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="H60" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="I60" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="4"/>
@@ -4020,28 +4030,30 @@
         <v>136</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="F61" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="G61" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="H61" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="I61" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
-      <c r="M61" s="5"/>
+      <c r="M61" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
@@ -4051,23 +4063,23 @@
         <v>136</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="F62" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="G62" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="H62" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="I62" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="4"/>
@@ -4084,23 +4096,23 @@
         <v>136</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s">
+        <v>458</v>
+      </c>
+      <c r="F63" t="s">
+        <v>466</v>
+      </c>
+      <c r="G63" t="s">
+        <v>467</v>
+      </c>
+      <c r="H63" t="s">
+        <v>468</v>
+      </c>
+      <c r="I63" t="s">
         <v>469</v>
-      </c>
-      <c r="F63" t="s">
-        <v>477</v>
-      </c>
-      <c r="G63" t="s">
-        <v>478</v>
-      </c>
-      <c r="H63" t="s">
-        <v>479</v>
-      </c>
-      <c r="I63" t="s">
-        <v>480</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="4"/>
@@ -4109,7 +4121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>1</v>
       </c>
@@ -4117,28 +4129,34 @@
         <v>14</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="F64" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="G64" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="H64" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="I64" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="J64" s="2"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
+      <c r="K64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M64" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
@@ -4148,7 +4166,7 @@
         <v>135</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3"/>
@@ -4158,7 +4176,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="2"/>
       <c r="K65" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>17</v>
@@ -4173,23 +4191,23 @@
         <v>136</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s">
+        <v>273</v>
+      </c>
+      <c r="F66" t="s">
+        <v>274</v>
+      </c>
+      <c r="G66" t="s">
         <v>275</v>
       </c>
-      <c r="F66" t="s">
+      <c r="H66" t="s">
         <v>276</v>
       </c>
-      <c r="G66" t="s">
+      <c r="I66" t="s">
         <v>277</v>
-      </c>
-      <c r="H66" t="s">
-        <v>278</v>
-      </c>
-      <c r="I66" t="s">
-        <v>279</v>
       </c>
       <c r="J66" s="2"/>
       <c r="M66" s="5">
@@ -4204,23 +4222,23 @@
         <v>136</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s">
+        <v>278</v>
+      </c>
+      <c r="F67" t="s">
+        <v>279</v>
+      </c>
+      <c r="G67" t="s">
         <v>280</v>
       </c>
-      <c r="F67" t="s">
+      <c r="H67" t="s">
         <v>281</v>
       </c>
-      <c r="G67" t="s">
+      <c r="I67" t="s">
         <v>282</v>
-      </c>
-      <c r="H67" t="s">
-        <v>283</v>
-      </c>
-      <c r="I67" t="s">
-        <v>284</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="4"/>
@@ -4237,23 +4255,23 @@
         <v>136</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s">
+        <v>283</v>
+      </c>
+      <c r="F68" t="s">
+        <v>284</v>
+      </c>
+      <c r="G68" t="s">
         <v>285</v>
       </c>
-      <c r="F68" t="s">
+      <c r="H68" t="s">
         <v>286</v>
       </c>
-      <c r="G68" t="s">
+      <c r="I68" t="s">
         <v>287</v>
-      </c>
-      <c r="H68" t="s">
-        <v>288</v>
-      </c>
-      <c r="I68" t="s">
-        <v>289</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="4"/>
@@ -4270,12 +4288,12 @@
         <v>135</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L69" s="4" t="s">
         <v>17</v>
@@ -4290,23 +4308,23 @@
         <v>136</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s">
+        <v>288</v>
+      </c>
+      <c r="F70" t="s">
+        <v>289</v>
+      </c>
+      <c r="G70" t="s">
         <v>290</v>
       </c>
-      <c r="F70" t="s">
+      <c r="H70" t="s">
         <v>291</v>
       </c>
-      <c r="G70" t="s">
-        <v>292</v>
-      </c>
-      <c r="H70" t="s">
-        <v>293</v>
-      </c>
       <c r="I70" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="4"/>
@@ -4323,28 +4341,30 @@
         <v>136</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s">
+        <v>292</v>
+      </c>
+      <c r="F71" t="s">
+        <v>293</v>
+      </c>
+      <c r="G71" t="s">
         <v>294</v>
       </c>
-      <c r="F71" t="s">
+      <c r="H71" t="s">
         <v>295</v>
       </c>
-      <c r="G71" t="s">
+      <c r="I71" t="s">
         <v>296</v>
-      </c>
-      <c r="H71" t="s">
-        <v>297</v>
-      </c>
-      <c r="I71" t="s">
-        <v>298</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
+      <c r="M71" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
@@ -4354,23 +4374,23 @@
         <v>136</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s">
+        <v>297</v>
+      </c>
+      <c r="F72" t="s">
+        <v>298</v>
+      </c>
+      <c r="G72" t="s">
+        <v>285</v>
+      </c>
+      <c r="H72" t="s">
         <v>299</v>
       </c>
-      <c r="F72" t="s">
+      <c r="I72" t="s">
         <v>300</v>
-      </c>
-      <c r="G72" t="s">
-        <v>287</v>
-      </c>
-      <c r="H72" t="s">
-        <v>301</v>
-      </c>
-      <c r="I72" t="s">
-        <v>302</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="4"/>
@@ -4397,7 +4417,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="2"/>
       <c r="K73" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L73" s="4" t="s">
         <v>17</v>
@@ -4412,23 +4432,23 @@
         <v>136</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="F74" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="G74" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="H74" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="I74" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="J74" s="2"/>
       <c r="M74" s="5">
@@ -4443,23 +4463,23 @@
         <v>136</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s">
+        <v>301</v>
+      </c>
+      <c r="F75" t="s">
+        <v>302</v>
+      </c>
+      <c r="G75" t="s">
+        <v>294</v>
+      </c>
+      <c r="H75" t="s">
         <v>303</v>
       </c>
-      <c r="F75" t="s">
+      <c r="I75" t="s">
         <v>304</v>
-      </c>
-      <c r="G75" t="s">
-        <v>296</v>
-      </c>
-      <c r="H75" t="s">
-        <v>305</v>
-      </c>
-      <c r="I75" t="s">
-        <v>306</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="4"/>
@@ -4476,27 +4496,27 @@
         <v>14</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s">
-        <v>372</v>
+        <v>498</v>
       </c>
       <c r="F76" t="s">
+        <v>367</v>
+      </c>
+      <c r="G76" t="s">
         <v>369</v>
       </c>
-      <c r="G76" t="s">
-        <v>371</v>
-      </c>
       <c r="H76" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I76" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L76" s="4" t="s">
         <v>17</v>
@@ -4513,32 +4533,34 @@
         <v>14</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>373</v>
+        <v>499</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F77" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="G77" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H77" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I77" t="s">
-        <v>376</v>
+        <v>500</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M77" s="4"/>
+      <c r="M77" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
@@ -4548,27 +4570,27 @@
         <v>14</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F78" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="G78" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="H78" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="I78" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L78" s="4" t="s">
         <v>17</v>
@@ -4585,27 +4607,27 @@
         <v>14</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>383</v>
+        <v>501</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s">
+        <v>308</v>
+      </c>
+      <c r="F79" t="s">
+        <v>309</v>
+      </c>
+      <c r="G79" t="s">
         <v>310</v>
       </c>
-      <c r="F79" t="s">
+      <c r="H79" t="s">
         <v>311</v>
       </c>
-      <c r="G79" t="s">
+      <c r="I79" t="s">
         <v>312</v>
-      </c>
-      <c r="H79" t="s">
-        <v>313</v>
-      </c>
-      <c r="I79" t="s">
-        <v>314</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L79" s="4" t="s">
         <v>17</v>
@@ -4622,27 +4644,27 @@
         <v>14</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s">
+        <v>313</v>
+      </c>
+      <c r="F80" t="s">
+        <v>314</v>
+      </c>
+      <c r="G80" t="s">
         <v>315</v>
       </c>
-      <c r="F80" t="s">
+      <c r="H80" t="s">
         <v>316</v>
       </c>
-      <c r="G80" t="s">
-        <v>317</v>
-      </c>
-      <c r="H80" t="s">
-        <v>318</v>
-      </c>
       <c r="I80" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L80" s="4" t="s">
         <v>17</v>
@@ -4659,32 +4681,34 @@
         <v>14</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>385</v>
+        <v>502</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="F81" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G81" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="H81" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="I81" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L81" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M81" s="4"/>
+      <c r="M81" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
@@ -4694,27 +4718,27 @@
         <v>14</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s">
+        <v>317</v>
+      </c>
+      <c r="F82" t="s">
+        <v>385</v>
+      </c>
+      <c r="G82" t="s">
+        <v>318</v>
+      </c>
+      <c r="H82" t="s">
+        <v>386</v>
+      </c>
+      <c r="I82" t="s">
         <v>319</v>
-      </c>
-      <c r="F82" t="s">
-        <v>392</v>
-      </c>
-      <c r="G82" t="s">
-        <v>320</v>
-      </c>
-      <c r="H82" t="s">
-        <v>393</v>
-      </c>
-      <c r="I82" t="s">
-        <v>321</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L82" s="4" t="s">
         <v>17</v>
@@ -4731,27 +4755,27 @@
         <v>14</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>394</v>
+        <v>503</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s">
+        <v>320</v>
+      </c>
+      <c r="F83" t="s">
+        <v>307</v>
+      </c>
+      <c r="G83" t="s">
+        <v>321</v>
+      </c>
+      <c r="H83" t="s">
         <v>322</v>
       </c>
-      <c r="F83" t="s">
-        <v>309</v>
-      </c>
-      <c r="G83" t="s">
+      <c r="I83" t="s">
         <v>323</v>
-      </c>
-      <c r="H83" t="s">
-        <v>324</v>
-      </c>
-      <c r="I83" t="s">
-        <v>325</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L83" s="4" t="s">
         <v>17</v>
@@ -4768,32 +4792,34 @@
         <v>14</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="F84" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="G84" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="H84" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="I84" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L84" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M84" s="4"/>
+      <c r="M84" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
@@ -4803,27 +4829,27 @@
         <v>14</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>401</v>
+        <v>504</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F85" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="G85" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="H85" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I85" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="J85" s="9"/>
       <c r="K85" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L85" s="4" t="s">
         <v>17</v>
@@ -4840,27 +4866,27 @@
         <v>14</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F86" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="G86" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="H86" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="I86" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="J86" s="9"/>
       <c r="K86" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L86" s="4" t="s">
         <v>17</v>
@@ -4877,27 +4903,27 @@
         <v>14</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s">
+        <v>325</v>
+      </c>
+      <c r="F87" t="s">
+        <v>326</v>
+      </c>
+      <c r="G87" t="s">
+        <v>404</v>
+      </c>
+      <c r="H87" t="s">
         <v>327</v>
       </c>
-      <c r="F87" t="s">
+      <c r="I87" t="s">
         <v>328</v>
-      </c>
-      <c r="G87" t="s">
-        <v>413</v>
-      </c>
-      <c r="H87" t="s">
-        <v>329</v>
-      </c>
-      <c r="I87" t="s">
-        <v>330</v>
       </c>
       <c r="J87" s="9"/>
       <c r="K87" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L87" s="4" t="s">
         <v>17</v>
@@ -4914,32 +4940,34 @@
         <v>14</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s">
+        <v>329</v>
+      </c>
+      <c r="F88" t="s">
+        <v>330</v>
+      </c>
+      <c r="G88" t="s">
         <v>331</v>
       </c>
-      <c r="F88" t="s">
+      <c r="H88" t="s">
         <v>332</v>
       </c>
-      <c r="G88" t="s">
+      <c r="I88" t="s">
         <v>333</v>
-      </c>
-      <c r="H88" t="s">
-        <v>334</v>
-      </c>
-      <c r="I88" t="s">
-        <v>335</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L88" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M88" s="4"/>
+      <c r="M88" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
@@ -4949,27 +4977,27 @@
         <v>14</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s">
+        <v>334</v>
+      </c>
+      <c r="F89" t="s">
+        <v>335</v>
+      </c>
+      <c r="G89" t="s">
         <v>336</v>
       </c>
-      <c r="F89" t="s">
+      <c r="H89" t="s">
         <v>337</v>
       </c>
-      <c r="G89" t="s">
+      <c r="I89" t="s">
         <v>338</v>
-      </c>
-      <c r="H89" t="s">
-        <v>339</v>
-      </c>
-      <c r="I89" t="s">
-        <v>340</v>
       </c>
       <c r="J89" s="9"/>
       <c r="K89" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L89" s="4" t="s">
         <v>17</v>
@@ -4986,27 +5014,27 @@
         <v>14</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s">
+        <v>339</v>
+      </c>
+      <c r="F90" t="s">
+        <v>340</v>
+      </c>
+      <c r="G90" t="s">
         <v>341</v>
       </c>
-      <c r="F90" t="s">
+      <c r="H90" t="s">
         <v>342</v>
       </c>
-      <c r="G90" t="s">
+      <c r="I90" t="s">
         <v>343</v>
-      </c>
-      <c r="H90" t="s">
-        <v>344</v>
-      </c>
-      <c r="I90" t="s">
-        <v>345</v>
       </c>
       <c r="J90" s="9"/>
       <c r="K90" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L90" s="4" t="s">
         <v>17</v>
@@ -5023,27 +5051,27 @@
         <v>14</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s">
+        <v>344</v>
+      </c>
+      <c r="F91" t="s">
+        <v>345</v>
+      </c>
+      <c r="G91" t="s">
         <v>346</v>
       </c>
-      <c r="F91" t="s">
+      <c r="H91" t="s">
         <v>347</v>
       </c>
-      <c r="G91" t="s">
+      <c r="I91" t="s">
         <v>348</v>
-      </c>
-      <c r="H91" t="s">
-        <v>349</v>
-      </c>
-      <c r="I91" t="s">
-        <v>350</v>
       </c>
       <c r="J91" s="9"/>
       <c r="K91" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L91" s="4" t="s">
         <v>17</v>
@@ -5060,27 +5088,27 @@
         <v>14</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s">
+        <v>349</v>
+      </c>
+      <c r="F92" t="s">
+        <v>350</v>
+      </c>
+      <c r="G92" t="s">
         <v>351</v>
       </c>
-      <c r="F92" t="s">
+      <c r="H92" t="s">
         <v>352</v>
       </c>
-      <c r="G92" t="s">
+      <c r="I92" t="s">
         <v>353</v>
-      </c>
-      <c r="H92" t="s">
-        <v>354</v>
-      </c>
-      <c r="I92" t="s">
-        <v>355</v>
       </c>
       <c r="J92" s="9"/>
       <c r="K92" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L92" s="4" t="s">
         <v>17</v>
@@ -5097,32 +5125,34 @@
         <v>14</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s">
+        <v>354</v>
+      </c>
+      <c r="F93" t="s">
+        <v>355</v>
+      </c>
+      <c r="G93" t="s">
         <v>356</v>
       </c>
-      <c r="F93" t="s">
+      <c r="H93" t="s">
         <v>357</v>
       </c>
-      <c r="G93" t="s">
+      <c r="I93" t="s">
         <v>358</v>
-      </c>
-      <c r="H93" t="s">
-        <v>359</v>
-      </c>
-      <c r="I93" t="s">
-        <v>360</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L93" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M93" s="4"/>
+      <c r="M93" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
@@ -5132,27 +5162,27 @@
         <v>14</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F94" t="s">
+        <v>359</v>
+      </c>
+      <c r="G94" t="s">
+        <v>360</v>
+      </c>
+      <c r="H94" t="s">
         <v>361</v>
       </c>
-      <c r="G94" t="s">
+      <c r="I94" t="s">
         <v>362</v>
-      </c>
-      <c r="H94" t="s">
-        <v>363</v>
-      </c>
-      <c r="I94" t="s">
-        <v>364</v>
       </c>
       <c r="J94" s="9"/>
       <c r="K94" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L94" s="4" t="s">
         <v>17</v>
@@ -5169,27 +5199,27 @@
         <v>14</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s">
+        <v>363</v>
+      </c>
+      <c r="F95" t="s">
+        <v>364</v>
+      </c>
+      <c r="G95" t="s">
         <v>365</v>
       </c>
-      <c r="F95" t="s">
-        <v>366</v>
-      </c>
-      <c r="G95" t="s">
-        <v>367</v>
-      </c>
       <c r="H95" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I95" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J95" s="9"/>
       <c r="K95" s="4" t="s">
-        <v>15</v>
+        <v>495</v>
       </c>
       <c r="L95" s="4" t="s">
         <v>17</v>

--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6314C4-0FBE-40A0-8FEB-D081C59B33AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEAD3B3-C521-437E-B6B5-C414DD4C157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1648,9 +1648,6 @@
     <t>A : $ \cos(\frac{a-b}{2}) e^{i(a+b)}$.</t>
   </si>
   <si>
-    <t>Les nombres complexes $sin(\theta) + i cos(2.\theta)$ et $cos(\theta) - i sin(2.\theta) sont conjugués l’un à l’autre pour $\theta$ égale à :</t>
-  </si>
-  <si>
     <t>E : aucune valeur de $\theta$.</t>
   </si>
   <si>
@@ -1660,10 +1657,13 @@
     <t>La primitive $F$ de la fonction $f$ définie sur l’intervalle $I=]0,+\infty[$ par $f(x) = \frac{2x^3 + 3 - x}{x}$, telle que : $F(1)=1$ vérifiée est :</t>
   </si>
   <si>
-    <t>On a pour $n \in \mathbb{N}^*$, $x \in \mathbb{R}$, $\lim_{x \to +\infty}$ $(\frac{\ln(nx)}{e^{nx})^2$ est égale à :</t>
-  </si>
-  <si>
     <t>Si $(\forall x \in \mathbb{R}^+)$, $f(x) = (e^{\sqrt{x}} - 1)(\sqrt{x} + e^x)(e^{2x} + 1)(x - 1)$, alors $f'(1)$ est égal à :</t>
+  </si>
+  <si>
+    <t>On a pour $n \in \mathbb{N}^*$, $x \in \mathbb{R}$, $\lim_{x \to +\infty} (\frac{\ln(nx)}{e^{nx}})^2$ est égale à :</t>
+  </si>
+  <si>
+    <t>Les nombres complexes $\sin(\theta) + i \cos(2\theta)$ et $\cos(\theta) - i \sin(2\theta)$ sont conjugués l'un à l'autre pour $\theta$ égal à :</t>
   </si>
 </sst>
 </file>
@@ -4533,7 +4533,7 @@
         <v>14</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s">
@@ -4549,7 +4549,7 @@
         <v>299</v>
       </c>
       <c r="I77" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="4" t="s">
@@ -4607,7 +4607,7 @@
         <v>14</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s">
@@ -4681,7 +4681,7 @@
         <v>14</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s">
@@ -4829,7 +4829,7 @@
         <v>14</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s">

--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEAD3B3-C521-437E-B6B5-C414DD4C157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8DB415-E5F2-4C9B-880F-F4E8E5557A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1651,9 +1651,6 @@
     <t>E : aucune valeur de $\theta$.</t>
   </si>
   <si>
-    <t>Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour $\ln(3x)&gt;\ln(2-5x)$ est:</t>
-  </si>
-  <si>
     <t>La primitive $F$ de la fonction $f$ définie sur l’intervalle $I=]0,+\infty[$ par $f(x) = \frac{2x^3 + 3 - x}{x}$, telle que : $F(1)=1$ vérifiée est :</t>
   </si>
   <si>
@@ -1664,6 +1661,9 @@
   </si>
   <si>
     <t>Les nombres complexes $\sin(\theta) + i \cos(2\theta)$ et $\cos(\theta) - i \sin(2\theta)$ sont conjugués l'un à l'autre pour $\theta$ égal à :</t>
+  </si>
+  <si>
+    <t>Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour $\ln(3x) &gt; \ln(2-5x)$ est:</t>
   </si>
 </sst>
 </file>
@@ -4533,7 +4533,7 @@
         <v>14</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s">
@@ -4607,7 +4607,7 @@
         <v>14</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s">
@@ -4681,7 +4681,7 @@
         <v>14</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s">
@@ -4755,7 +4755,7 @@
         <v>14</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s">
@@ -4829,7 +4829,7 @@
         <v>14</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s">

--- a/Concours_Blanc_1.xlsx
+++ b/Concours_Blanc_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8DB415-E5F2-4C9B-880F-F4E8E5557A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEC5289-A4DB-4151-A4D4-49702890D66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1663,7 +1663,7 @@
     <t>Les nombres complexes $\sin(\theta) + i \cos(2\theta)$ et $\cos(\theta) - i \sin(2\theta)$ sont conjugués l'un à l'autre pour $\theta$ égal à :</t>
   </si>
   <si>
-    <t>Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour $\ln(3x) &gt; \ln(2-5x)$ est:</t>
+    <t>Soit $x \in ]0, \frac{2}{5}[$ , l’ensemble des solutions pour \( \ln(3x) &gt; \ln(2-5x) \) est:</t>
   </si>
 </sst>
 </file>
